--- a/research/traditional_assets/database/data/netherlands/netherlands_semiconductor.xlsx
+++ b/research/traditional_assets/database/data/netherlands/netherlands_semiconductor.xlsx
@@ -650,10 +650,10 @@
         <v>0.3195098963242224</v>
       </c>
       <c r="X2">
-        <v>0.1280432881407793</v>
+        <v>0.1279904130187993</v>
       </c>
       <c r="Y2">
-        <v>0.1914666081834431</v>
+        <v>0.1915194833054232</v>
       </c>
       <c r="Z2">
         <v>2.18043983062402</v>
@@ -662,10 +662,10 @@
         <v>0.5198993040110502</v>
       </c>
       <c r="AB2">
-        <v>0.113832583776476</v>
+        <v>0.1137884260648883</v>
       </c>
       <c r="AC2">
-        <v>0.4060667202345742</v>
+        <v>0.4061108779461619</v>
       </c>
       <c r="AD2">
         <v>10182</v>
@@ -787,10 +787,10 @@
         <v>0.3195098963242224</v>
       </c>
       <c r="X3">
-        <v>0.1280432881407793</v>
+        <v>0.1279904130187993</v>
       </c>
       <c r="Y3">
-        <v>0.1914666081834431</v>
+        <v>0.1915194833054232</v>
       </c>
       <c r="Z3">
         <v>2.18043983062402</v>
@@ -799,10 +799,10 @@
         <v>0.5198993040110502</v>
       </c>
       <c r="AB3">
-        <v>0.113832583776476</v>
+        <v>0.1137884260648883</v>
       </c>
       <c r="AC3">
-        <v>0.4060667202345742</v>
+        <v>0.4061108779461619</v>
       </c>
       <c r="AD3">
         <v>10182</v>
@@ -1139,49 +1139,49 @@
         <v>11.1375921375921</v>
       </c>
       <c r="F2">
-        <v>2.52021905869941</v>
+        <v>2.5302743073977</v>
       </c>
       <c r="G2">
         <v>2.21698620875412</v>
       </c>
       <c r="H2">
-        <v>6.32011149430492</v>
+        <v>6.58905240895619</v>
       </c>
       <c r="I2">
         <v>0.164867901310503</v>
       </c>
       <c r="J2">
-        <v>0.47</v>
+        <v>0.49</v>
       </c>
       <c r="K2">
         <v>52826.2</v>
       </c>
       <c r="L2">
-        <v>38766.0802994464</v>
+        <v>38972.4346191598</v>
       </c>
       <c r="M2">
         <v>60506.9031259794</v>
       </c>
       <c r="N2">
-        <v>65747.8847686567</v>
+        <v>67219.3371508897</v>
       </c>
       <c r="O2">
         <v>10428.7031259794</v>
       </c>
       <c r="P2">
-        <v>29729.8044692103</v>
+        <v>30994.9025317299</v>
       </c>
       <c r="Q2">
-        <v>0.113832583776476</v>
+        <v>0.113788426064888</v>
       </c>
       <c r="R2">
-        <v>0.108409481209283</v>
+        <v>0.106999191839123</v>
       </c>
       <c r="S2">
         <v>0.0418488</v>
       </c>
       <c r="T2">
-        <v>0.044891</v>
+        <v>0.0428876</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -1194,16 +1194,16 @@
         </is>
       </c>
       <c r="W2">
-        <v>0.128043288140779</v>
+        <v>0.127990413018799</v>
       </c>
       <c r="X2">
-        <v>0.164737190960911</v>
+        <v>0.168596603606124</v>
       </c>
       <c r="Y2">
         <v>1.89816196348266</v>
       </c>
       <c r="Z2">
-        <v>2.74505138387742</v>
+        <v>2.83594927496823</v>
       </c>
       <c r="AA2">
         <v>10182</v>
@@ -1236,7 +1236,7 @@
         <v>52826.2</v>
       </c>
       <c r="AK2">
-        <v>0.043327855959079</v>
+        <v>0.0433</v>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
@@ -1424,13 +1424,13 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>0.1175353383358934</v>
+        <v>0.1174892188913704</v>
       </c>
       <c r="C2">
-        <v>60131.72539205848</v>
+        <v>60131.37191021068</v>
       </c>
       <c r="D2">
-        <v>57383.72539205848</v>
+        <v>57383.37191021068</v>
       </c>
       <c r="E2">
         <v>-10428.7031259794</v>
@@ -1475,19 +1475,19 @@
         <v>0</v>
       </c>
       <c r="S2">
-        <v>0.1175353383358934</v>
+        <v>0.1174892188913704</v>
       </c>
       <c r="T2">
         <v>1.655640159154051</v>
       </c>
       <c r="U2">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V2">
         <v>0.258</v>
       </c>
       <c r="W2">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -1506,13 +1506,13 @@
         <v>0.01</v>
       </c>
       <c r="B3">
-        <v>0.1172758751629868</v>
+        <v>0.1172194867066307</v>
       </c>
       <c r="C3">
-        <v>59707.48389714537</v>
+        <v>59715.54443474495</v>
       </c>
       <c r="D3">
-        <v>57592.03292840517</v>
+        <v>57600.09346600475</v>
       </c>
       <c r="E3">
         <v>-9796.154094719608</v>
@@ -1539,37 +1539,37 @@
         <v>4533</v>
       </c>
       <c r="M3">
-        <v>32.70278491613135</v>
+        <v>31.81721627236764</v>
       </c>
       <c r="N3">
-        <v>4500.297215083869</v>
+        <v>4501.182783727632</v>
       </c>
       <c r="O3">
-        <v>1161.076681491638</v>
+        <v>1161.305158201729</v>
       </c>
       <c r="P3">
-        <v>3339.220533592231</v>
+        <v>3339.877625525903</v>
       </c>
       <c r="Q3">
-        <v>3510.220533592231</v>
+        <v>3510.877625525903</v>
       </c>
       <c r="R3">
         <v>0.0101010101010101</v>
       </c>
       <c r="S3">
-        <v>0.118072991073724</v>
+        <v>0.1180265259662936</v>
       </c>
       <c r="T3">
         <v>1.668049098528721</v>
       </c>
       <c r="U3">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V3">
         <v>0.258</v>
       </c>
       <c r="W3">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>138.6120482284676</v>
+        <v>142.4700376423812</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1588,13 +1588,13 @@
         <v>0.02</v>
       </c>
       <c r="B4">
-        <v>0.1170164119900802</v>
+        <v>0.116949754521891</v>
       </c>
       <c r="C4">
-        <v>59284.76025837837</v>
+        <v>59301.36016322607</v>
       </c>
       <c r="D4">
-        <v>57801.85832089795</v>
+        <v>57818.45822574566</v>
       </c>
       <c r="E4">
         <v>-9163.605063459814</v>
@@ -1621,37 +1621,37 @@
         <v>4533</v>
       </c>
       <c r="M4">
-        <v>65.4055698322627</v>
+        <v>63.63443254473528</v>
       </c>
       <c r="N4">
-        <v>4467.594430167737</v>
+        <v>4469.365567455265</v>
       </c>
       <c r="O4">
-        <v>1152.639362983276</v>
+        <v>1153.096316403458</v>
       </c>
       <c r="P4">
-        <v>3314.955067184461</v>
+        <v>3316.269251051806</v>
       </c>
       <c r="Q4">
-        <v>3485.955067184461</v>
+        <v>3487.269251051806</v>
       </c>
       <c r="R4">
         <v>0.02040816326530612</v>
       </c>
       <c r="S4">
-        <v>0.1186216163164083</v>
+        <v>0.1185747984917255</v>
       </c>
       <c r="T4">
         <v>1.680711281564099</v>
       </c>
       <c r="U4">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V4">
         <v>0.258</v>
       </c>
       <c r="W4">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>69.30602411423378</v>
+        <v>71.23501882119058</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1670,13 +1670,13 @@
         <v>0.03</v>
       </c>
       <c r="B5">
-        <v>0.1167569488171736</v>
+        <v>0.1166800223371512</v>
       </c>
       <c r="C5">
-        <v>58863.57112646375</v>
+        <v>58888.8378551709</v>
       </c>
       <c r="D5">
-        <v>58013.21822024313</v>
+        <v>58038.48494895028</v>
       </c>
       <c r="E5">
         <v>-8531.05603220002</v>
@@ -1703,37 +1703,37 @@
         <v>4533</v>
       </c>
       <c r="M5">
-        <v>98.10835474839405</v>
+        <v>95.45164881710291</v>
       </c>
       <c r="N5">
-        <v>4434.891645251606</v>
+        <v>4437.548351182897</v>
       </c>
       <c r="O5">
-        <v>1144.202044474914</v>
+        <v>1144.887474605187</v>
       </c>
       <c r="P5">
-        <v>3290.689600776692</v>
+        <v>3292.66087657771</v>
       </c>
       <c r="Q5">
-        <v>3461.689600776692</v>
+        <v>3463.66087657771</v>
       </c>
       <c r="R5">
         <v>0.03092783505154639</v>
       </c>
       <c r="S5">
-        <v>0.1191815534197666</v>
+        <v>0.1191343756053105</v>
       </c>
       <c r="T5">
         <v>1.693634540538349</v>
       </c>
       <c r="U5">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V5">
         <v>0.258</v>
       </c>
       <c r="W5">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>46.20401607615585</v>
+        <v>47.4900125474604</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1752,13 +1752,13 @@
         <v>0.04</v>
       </c>
       <c r="B6">
-        <v>0.116497485644267</v>
+        <v>0.1164102901524115</v>
       </c>
       <c r="C6">
-        <v>58443.93339654338</v>
+        <v>58477.99655674259</v>
       </c>
       <c r="D6">
-        <v>58226.12952158255</v>
+        <v>58260.19268178177</v>
       </c>
       <c r="E6">
         <v>-7898.507000940226</v>
@@ -1785,37 +1785,37 @@
         <v>4533</v>
       </c>
       <c r="M6">
-        <v>130.8111396645254</v>
+        <v>127.2688650894706</v>
       </c>
       <c r="N6">
-        <v>4402.188860335475</v>
+        <v>4405.731134910529</v>
       </c>
       <c r="O6">
-        <v>1135.764725966553</v>
+        <v>1136.678632806917</v>
       </c>
       <c r="P6">
-        <v>3266.424134368922</v>
+        <v>3269.052502103613</v>
       </c>
       <c r="Q6">
-        <v>3437.424134368922</v>
+        <v>3440.052502103613</v>
       </c>
       <c r="R6">
         <v>0.04166666666666667</v>
       </c>
       <c r="S6">
-        <v>0.1197531558794448</v>
+        <v>0.1197056105754286</v>
       </c>
       <c r="T6">
         <v>1.706827034074564</v>
       </c>
       <c r="U6">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V6">
         <v>0.258</v>
       </c>
       <c r="W6">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>34.65301205711689</v>
+        <v>35.61750941059529</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1834,13 +1834,13 @@
         <v>0.05</v>
       </c>
       <c r="B7">
-        <v>0.1162380224713603</v>
+        <v>0.1161405579676717</v>
       </c>
       <c r="C7">
-        <v>58025.86421269675</v>
+        <v>58068.85560624664</v>
       </c>
       <c r="D7">
-        <v>58440.60936899572</v>
+        <v>58483.60076254561</v>
       </c>
       <c r="E7">
         <v>-7265.957969680432</v>
@@ -1867,37 +1867,37 @@
         <v>4533</v>
       </c>
       <c r="M7">
-        <v>163.5139245806567</v>
+        <v>159.0860813618382</v>
       </c>
       <c r="N7">
-        <v>4369.486075419343</v>
+        <v>4373.913918638162</v>
       </c>
       <c r="O7">
-        <v>1127.327407458191</v>
+        <v>1128.469791008646</v>
       </c>
       <c r="P7">
-        <v>3242.158667961153</v>
+        <v>3245.444127629516</v>
       </c>
       <c r="Q7">
-        <v>3413.158667961153</v>
+        <v>3416.444127629516</v>
       </c>
       <c r="R7">
         <v>0.05263157894736843</v>
       </c>
       <c r="S7">
-        <v>0.1203367920751162</v>
+        <v>0.1202888715449176</v>
       </c>
       <c r="T7">
         <v>1.720297264316805</v>
       </c>
       <c r="U7">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V7">
         <v>0.258</v>
       </c>
       <c r="W7">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>27.72240964569351</v>
+        <v>28.49400752847624</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1916,13 +1916,13 @@
         <v>0.06</v>
       </c>
       <c r="B8">
-        <v>0.1159785592984538</v>
+        <v>0.115870825782932</v>
       </c>
       <c r="C8">
-        <v>57609.38097254258</v>
+        <v>57661.43463975373</v>
       </c>
       <c r="D8">
-        <v>58656.67516010135</v>
+        <v>58708.72882731249</v>
       </c>
       <c r="E8">
         <v>-6633.408938420638</v>
@@ -1949,37 +1949,37 @@
         <v>4533</v>
       </c>
       <c r="M8">
-        <v>196.2167094967881</v>
+        <v>190.9032976342058</v>
       </c>
       <c r="N8">
-        <v>4336.783290503212</v>
+        <v>4342.096702365794</v>
       </c>
       <c r="O8">
-        <v>1118.890088949829</v>
+        <v>1120.260949210375</v>
       </c>
       <c r="P8">
-        <v>3217.893201553383</v>
+        <v>3221.835753155419</v>
       </c>
       <c r="Q8">
-        <v>3388.893201553383</v>
+        <v>3392.835753155419</v>
       </c>
       <c r="R8">
         <v>0.06382978723404255</v>
       </c>
       <c r="S8">
-        <v>0.1209328460621849</v>
+        <v>0.1208845423222681</v>
       </c>
       <c r="T8">
         <v>1.734054095202497</v>
       </c>
       <c r="U8">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V8">
         <v>0.258</v>
       </c>
       <c r="W8">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>23.10200803807793</v>
+        <v>23.74500627373019</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1998,13 +1998,13 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="B9">
-        <v>0.1157190961255471</v>
+        <v>0.1156010935981923</v>
       </c>
       <c r="C9">
-        <v>57194.50133194347</v>
+        <v>57255.75359685298</v>
       </c>
       <c r="D9">
-        <v>58874.34455076202</v>
+        <v>58935.59681567154</v>
       </c>
       <c r="E9">
         <v>-6000.859907160844</v>
@@ -2031,37 +2031,37 @@
         <v>4533</v>
       </c>
       <c r="M9">
-        <v>228.9194944129194</v>
+        <v>222.7205139065734</v>
       </c>
       <c r="N9">
-        <v>4304.080505587081</v>
+        <v>4310.279486093426</v>
       </c>
       <c r="O9">
-        <v>1110.452770441467</v>
+        <v>1112.052107412104</v>
       </c>
       <c r="P9">
-        <v>3193.627735145614</v>
+        <v>3198.227378681322</v>
       </c>
       <c r="Q9">
-        <v>3364.627735145614</v>
+        <v>3369.227378681322</v>
       </c>
       <c r="R9">
         <v>0.07526881720430109</v>
       </c>
       <c r="S9">
-        <v>0.1215417184145668</v>
+        <v>0.1214930232238627</v>
       </c>
       <c r="T9">
         <v>1.748106771913687</v>
       </c>
       <c r="U9">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V9">
         <v>0.258</v>
       </c>
       <c r="W9">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>19.80172117549537</v>
+        <v>20.35286252034017</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2080,13 +2080,13 @@
         <v>0.08</v>
       </c>
       <c r="B10">
-        <v>0.1154596329526406</v>
+        <v>0.1153313614134525</v>
       </c>
       <c r="C10">
-        <v>56781.24320981495</v>
+        <v>56851.8327265392</v>
       </c>
       <c r="D10">
-        <v>59093.6354598933</v>
+        <v>59164.22497661755</v>
       </c>
       <c r="E10">
         <v>-5368.31087590105</v>
@@ -2113,37 +2113,37 @@
         <v>4533</v>
       </c>
       <c r="M10">
-        <v>261.6222793290508</v>
+        <v>254.5377301789411</v>
       </c>
       <c r="N10">
-        <v>4271.377720670949</v>
+        <v>4278.462269821059</v>
       </c>
       <c r="O10">
-        <v>1102.015451933105</v>
+        <v>1103.843265613833</v>
       </c>
       <c r="P10">
-        <v>3169.362268737844</v>
+        <v>3174.619004207226</v>
       </c>
       <c r="Q10">
-        <v>3340.362268737844</v>
+        <v>3345.619004207226</v>
       </c>
       <c r="R10">
         <v>0.08695652173913043</v>
       </c>
       <c r="S10">
-        <v>0.1221638271224354</v>
+        <v>0.1221147319711441</v>
       </c>
       <c r="T10">
         <v>1.762464941596861</v>
       </c>
       <c r="U10">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V10">
         <v>0.258</v>
       </c>
       <c r="W10">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>17.32650602855844</v>
+        <v>17.80875470529764</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2162,13 +2162,13 @@
         <v>0.09</v>
       </c>
       <c r="B11">
-        <v>0.1152001697797339</v>
+        <v>0.1150616292287128</v>
       </c>
       <c r="C11">
-        <v>56369.6247930432</v>
+        <v>56449.6925932376</v>
       </c>
       <c r="D11">
-        <v>59314.56607438134</v>
+        <v>59394.63387457575</v>
       </c>
       <c r="E11">
         <v>-4735.761844641256</v>
@@ -2195,37 +2195,37 @@
         <v>4533</v>
       </c>
       <c r="M11">
-        <v>294.3250642451821</v>
+        <v>286.3549464513087</v>
       </c>
       <c r="N11">
-        <v>4238.674935754818</v>
+        <v>4246.645053548691</v>
       </c>
       <c r="O11">
-        <v>1093.578133424743</v>
+        <v>1095.634423815562</v>
       </c>
       <c r="P11">
-        <v>3145.096802330075</v>
+        <v>3151.010629733129</v>
       </c>
       <c r="Q11">
-        <v>3316.096802330075</v>
+        <v>3322.010629733129</v>
       </c>
       <c r="R11">
         <v>0.0989010989010989</v>
       </c>
       <c r="S11">
-        <v>0.1227996085491582</v>
+        <v>0.1227501046469371</v>
       </c>
       <c r="T11">
         <v>1.777138675448895</v>
       </c>
       <c r="U11">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V11">
         <v>0.258</v>
       </c>
       <c r="W11">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>15.40133869205195</v>
+        <v>15.8300041824868</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2244,13 +2244,13 @@
         <v>0.1</v>
       </c>
       <c r="B12">
-        <v>0.1149407066068273</v>
+        <v>0.1147918970439731</v>
       </c>
       <c r="C12">
-        <v>55959.66454151274</v>
+        <v>56049.35408296977</v>
       </c>
       <c r="D12">
-        <v>59537.15485411067</v>
+        <v>59626.84439556771</v>
       </c>
       <c r="E12">
         <v>-4103.212813381462</v>
@@ -2277,37 +2277,37 @@
         <v>4533</v>
       </c>
       <c r="M12">
-        <v>327.0278491613135</v>
+        <v>318.1721627236764</v>
       </c>
       <c r="N12">
-        <v>4205.972150838687</v>
+        <v>4214.827837276323</v>
       </c>
       <c r="O12">
-        <v>1085.140814916381</v>
+        <v>1087.425582017291</v>
       </c>
       <c r="P12">
-        <v>3120.831335922305</v>
+        <v>3127.402255259032</v>
       </c>
       <c r="Q12">
-        <v>3291.831335922305</v>
+        <v>3298.402255259032</v>
       </c>
       <c r="R12">
         <v>0.1111111111111111</v>
       </c>
       <c r="S12">
-        <v>0.1234495184520304</v>
+        <v>0.1233995967155256</v>
       </c>
       <c r="T12">
         <v>1.792138492275419</v>
       </c>
       <c r="U12">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V12">
         <v>0.258</v>
       </c>
       <c r="W12">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>13.86120482284676</v>
+        <v>14.24700376423812</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2326,13 +2326,13 @@
         <v>0.11</v>
       </c>
       <c r="B13">
-        <v>0.1146812434339207</v>
+        <v>0.1145221648592333</v>
       </c>
       <c r="C13">
-        <v>55551.38119324832</v>
+        <v>55650.83840966513</v>
       </c>
       <c r="D13">
-        <v>59761.42053710606</v>
+        <v>59860.87775352286</v>
       </c>
       <c r="E13">
         <v>-3470.663782121668</v>
@@ -2359,37 +2359,37 @@
         <v>4533</v>
       </c>
       <c r="M13">
-        <v>359.7306340774448</v>
+        <v>349.989378996044</v>
       </c>
       <c r="N13">
-        <v>4173.269365922555</v>
+        <v>4183.010621003956</v>
       </c>
       <c r="O13">
-        <v>1076.703496408019</v>
+        <v>1079.216740219021</v>
       </c>
       <c r="P13">
-        <v>3096.565869514536</v>
+        <v>3103.793880784935</v>
       </c>
       <c r="Q13">
-        <v>3267.565869514536</v>
+        <v>3274.793880784935</v>
       </c>
       <c r="R13">
         <v>0.1235955056179775</v>
       </c>
       <c r="S13">
-        <v>0.124114033071821</v>
+        <v>0.1240636841114981</v>
       </c>
       <c r="T13">
         <v>1.80747538363737</v>
       </c>
       <c r="U13">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V13">
         <v>0.258</v>
       </c>
       <c r="W13">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>12.60109529349705</v>
+        <v>12.95182160385283</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2408,13 +2408,13 @@
         <v>0.12</v>
       </c>
       <c r="B14">
-        <v>0.1144217802610141</v>
+        <v>0.1142524326744936</v>
       </c>
       <c r="C14">
-        <v>55144.7937696732</v>
+        <v>55254.1671216212</v>
       </c>
       <c r="D14">
-        <v>59987.38214479072</v>
+        <v>60096.75549673873</v>
       </c>
       <c r="E14">
         <v>-2838.114750861874</v>
@@ -2441,37 +2441,37 @@
         <v>4533</v>
       </c>
       <c r="M14">
-        <v>392.4334189935762</v>
+        <v>381.8065952684116</v>
       </c>
       <c r="N14">
-        <v>4140.566581006424</v>
+        <v>4151.193404731588</v>
       </c>
       <c r="O14">
-        <v>1068.266177899657</v>
+        <v>1071.00789842075</v>
       </c>
       <c r="P14">
-        <v>3072.300403106767</v>
+        <v>3080.185506310838</v>
       </c>
       <c r="Q14">
-        <v>3243.300403106767</v>
+        <v>3251.185506310838</v>
       </c>
       <c r="R14">
         <v>0.1363636363636364</v>
       </c>
       <c r="S14">
-        <v>0.124793650296607</v>
+        <v>0.1247428644028336</v>
       </c>
       <c r="T14">
         <v>1.823160840712093</v>
       </c>
       <c r="U14">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V14">
         <v>0.258</v>
       </c>
       <c r="W14">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>11.55100401903896</v>
+        <v>11.8725031368651</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2490,13 +2490,13 @@
         <v>0.13</v>
       </c>
       <c r="B15">
-        <v>0.1141623170881075</v>
+        <v>0.1139827004897539</v>
       </c>
       <c r="C15">
-        <v>54739.92158098721</v>
+        <v>54859.36210811765</v>
       </c>
       <c r="D15">
-        <v>60215.05898736453</v>
+        <v>60334.49951449497</v>
       </c>
       <c r="E15">
         <v>-2205.56571960208</v>
@@ -2523,37 +2523,37 @@
         <v>4533</v>
       </c>
       <c r="M15">
-        <v>425.1362039097075</v>
+        <v>413.6238115407793</v>
       </c>
       <c r="N15">
-        <v>4107.863796090292</v>
+        <v>4119.37618845922</v>
       </c>
       <c r="O15">
-        <v>1059.828859391296</v>
+        <v>1062.799056622479</v>
       </c>
       <c r="P15">
-        <v>3048.034936698997</v>
+        <v>3056.577131836742</v>
       </c>
       <c r="Q15">
-        <v>3219.034936698997</v>
+        <v>3227.577131836742</v>
       </c>
       <c r="R15">
         <v>0.1494252873563219</v>
       </c>
       <c r="S15">
-        <v>0.1254888909058707</v>
+        <v>0.1254376580341998</v>
       </c>
       <c r="T15">
         <v>1.839206883006925</v>
       </c>
       <c r="U15">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V15">
         <v>0.258</v>
       </c>
       <c r="W15">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2561,7 +2561,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>10.66246524834366</v>
+        <v>10.95923366479855</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2572,13 +2572,13 @@
         <v>0.14</v>
       </c>
       <c r="B16">
-        <v>0.1139028539152009</v>
+        <v>0.1137129683050141</v>
       </c>
       <c r="C16">
-        <v>54336.78423166768</v>
+        <v>54466.44560618763</v>
       </c>
       <c r="D16">
-        <v>60444.47066930479</v>
+        <v>60574.13204382474</v>
       </c>
       <c r="E16">
         <v>-1573.016688342286</v>
@@ -2605,37 +2605,37 @@
         <v>4533</v>
       </c>
       <c r="M16">
-        <v>457.8389888258389</v>
+        <v>445.4410278131469</v>
       </c>
       <c r="N16">
-        <v>4075.161011174161</v>
+        <v>4087.558972186853</v>
       </c>
       <c r="O16">
-        <v>1051.391540882934</v>
+        <v>1054.590214824208</v>
       </c>
       <c r="P16">
-        <v>3023.769470291228</v>
+        <v>3032.968757362645</v>
       </c>
       <c r="Q16">
-        <v>3194.769470291228</v>
+        <v>3203.968757362645</v>
       </c>
       <c r="R16">
         <v>0.1627906976744186</v>
       </c>
       <c r="S16">
-        <v>0.1262002999013964</v>
+        <v>0.1261486096569932</v>
       </c>
       <c r="T16">
         <v>1.855626089076055</v>
       </c>
       <c r="U16">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V16">
         <v>0.258</v>
       </c>
       <c r="W16">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>9.900860587747683</v>
+        <v>10.17643126017009</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2654,13 +2654,13 @@
         <v>0.15</v>
       </c>
       <c r="B17">
-        <v>0.1136433907422943</v>
+        <v>0.1134432361202744</v>
       </c>
       <c r="C17">
-        <v>53935.40162609691</v>
+        <v>54075.44020755125</v>
       </c>
       <c r="D17">
-        <v>60675.63709499382</v>
+        <v>60815.67567644816</v>
       </c>
       <c r="E17">
         <v>-940.4676570824922</v>
@@ -2687,37 +2687,37 @@
         <v>4533</v>
       </c>
       <c r="M17">
-        <v>490.5417737419702</v>
+        <v>477.2582440855145</v>
       </c>
       <c r="N17">
-        <v>4042.45822625803</v>
+        <v>4055.741755914486</v>
       </c>
       <c r="O17">
-        <v>1042.954222374572</v>
+        <v>1046.381373025937</v>
       </c>
       <c r="P17">
-        <v>2999.504003883458</v>
+        <v>3009.360382888548</v>
       </c>
       <c r="Q17">
-        <v>3170.504003883458</v>
+        <v>3180.360382888548</v>
       </c>
       <c r="R17">
         <v>0.1764705882352941</v>
       </c>
       <c r="S17">
-        <v>0.1269284479321109</v>
+        <v>0.126876289553264</v>
       </c>
       <c r="T17">
         <v>1.872431629405635</v>
       </c>
       <c r="U17">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V17">
         <v>0.258</v>
       </c>
       <c r="W17">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>9.240803215231171</v>
+        <v>9.498002509492078</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2736,13 +2736,13 @@
         <v>0.16</v>
       </c>
       <c r="B18">
-        <v>0.1135145195693877</v>
+        <v>0.1131735039355347</v>
       </c>
       <c r="C18">
-        <v>53418.32768893823</v>
+        <v>53686.36886571559</v>
       </c>
       <c r="D18">
-        <v>60791.11218909494</v>
+        <v>61059.15336587229</v>
       </c>
       <c r="E18">
         <v>-307.9186258226982</v>
@@ -2769,45 +2769,45 @@
         <v>4533</v>
       </c>
       <c r="M18">
-        <v>534.3774216082739</v>
+        <v>509.0754603578822</v>
       </c>
       <c r="N18">
-        <v>3998.622578391726</v>
+        <v>4023.924539642118</v>
       </c>
       <c r="O18">
-        <v>1031.644625225065</v>
+        <v>1038.172531227666</v>
       </c>
       <c r="P18">
-        <v>2966.977953166661</v>
+        <v>2985.752008414452</v>
       </c>
       <c r="Q18">
-        <v>3137.977953166661</v>
+        <v>3156.752008414452</v>
       </c>
       <c r="R18">
         <v>0.1904761904761905</v>
       </c>
       <c r="S18">
-        <v>0.1276739328206996</v>
+        <v>0.1276212951613508</v>
       </c>
       <c r="T18">
         <v>1.889637301647824</v>
       </c>
       <c r="U18">
-        <v>0.0528</v>
+        <v>0.0503</v>
       </c>
       <c r="V18">
         <v>0.258</v>
       </c>
       <c r="W18">
-        <v>0.0391776</v>
+        <v>0.0373226</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>Aaa/AAA</t>
         </is>
       </c>
       <c r="Y18">
-        <v>8.482768576481739</v>
+        <v>8.904377352648822</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2818,13 +2818,13 @@
         <v>0.17</v>
       </c>
       <c r="B19">
-        <v>0.1132632183964811</v>
+        <v>0.1130929817507949</v>
       </c>
       <c r="C19">
-        <v>53012.22616727743</v>
+        <v>53126.88267547516</v>
       </c>
       <c r="D19">
-        <v>61017.55969869393</v>
+        <v>61132.21620689167</v>
       </c>
       <c r="E19">
         <v>324.6304054370958</v>
@@ -2851,37 +2851,37 @@
         <v>4533</v>
       </c>
       <c r="M19">
-        <v>567.7760104587911</v>
+        <v>557.0226769273746</v>
       </c>
       <c r="N19">
-        <v>3965.223989541209</v>
+        <v>3975.977323072625</v>
       </c>
       <c r="O19">
-        <v>1023.027789301632</v>
+        <v>1025.802149352737</v>
       </c>
       <c r="P19">
-        <v>2942.196200239577</v>
+        <v>2950.175173719888</v>
       </c>
       <c r="Q19">
-        <v>3113.196200239577</v>
+        <v>3121.175173719888</v>
       </c>
       <c r="R19">
         <v>0.2048192771084338</v>
       </c>
       <c r="S19">
-        <v>0.1284373812005796</v>
+        <v>0.1283842527118011</v>
       </c>
       <c r="T19">
         <v>1.907257568401873</v>
       </c>
       <c r="U19">
-        <v>0.0528</v>
+        <v>0.0518</v>
       </c>
       <c r="V19">
         <v>0.258</v>
       </c>
       <c r="W19">
-        <v>0.0391776</v>
+        <v>0.0384356</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>7.983782189629872</v>
+        <v>8.137909258927746</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2900,13 +2900,13 @@
         <v>0.18</v>
       </c>
       <c r="B20">
-        <v>0.1130119172235745</v>
+        <v>0.1128343795660552</v>
       </c>
       <c r="C20">
-        <v>52607.81799188958</v>
+        <v>52730.16673122868</v>
       </c>
       <c r="D20">
-        <v>61245.70055456587</v>
+        <v>61368.04929390497</v>
       </c>
       <c r="E20">
         <v>957.1794366968898</v>
@@ -2933,37 +2933,37 @@
         <v>4533</v>
       </c>
       <c r="M20">
-        <v>601.1745993093082</v>
+        <v>589.7887167466318</v>
       </c>
       <c r="N20">
-        <v>3931.825400690692</v>
+        <v>3943.211283253368</v>
       </c>
       <c r="O20">
-        <v>1014.410953378199</v>
+        <v>1017.348511079369</v>
       </c>
       <c r="P20">
-        <v>2917.414447312493</v>
+        <v>2925.862772173999</v>
       </c>
       <c r="Q20">
-        <v>3088.414447312493</v>
+        <v>3096.862772173999</v>
       </c>
       <c r="R20">
         <v>0.2195121951219512</v>
       </c>
       <c r="S20">
-        <v>0.1292194502726518</v>
+        <v>0.1291658189829941</v>
       </c>
       <c r="T20">
         <v>1.92530759775968</v>
       </c>
       <c r="U20">
-        <v>0.0528</v>
+        <v>0.0518</v>
       </c>
       <c r="V20">
         <v>0.258</v>
       </c>
       <c r="W20">
-        <v>0.0391776</v>
+        <v>0.0384356</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>7.540238734650435</v>
+        <v>7.685803188987316</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2982,13 +2982,13 @@
         <v>0.19</v>
       </c>
       <c r="B21">
-        <v>0.1127606160506679</v>
+        <v>0.1125757773813155</v>
       </c>
       <c r="C21">
-        <v>52205.12222800718</v>
+        <v>52335.27740597269</v>
       </c>
       <c r="D21">
-        <v>61475.55382194326</v>
+        <v>61605.70899990878</v>
       </c>
       <c r="E21">
         <v>1589.728467956684</v>
@@ -3015,37 +3015,37 @@
         <v>4533</v>
       </c>
       <c r="M21">
-        <v>634.5731881598253</v>
+        <v>622.5547565658892</v>
       </c>
       <c r="N21">
-        <v>3898.426811840175</v>
+        <v>3910.445243434111</v>
       </c>
       <c r="O21">
-        <v>1005.794117454765</v>
+        <v>1008.894872806001</v>
       </c>
       <c r="P21">
-        <v>2892.63269438541</v>
+        <v>2901.550370628111</v>
       </c>
       <c r="Q21">
-        <v>3063.63269438541</v>
+        <v>3072.550370628111</v>
       </c>
       <c r="R21">
         <v>0.2345679012345679</v>
       </c>
       <c r="S21">
-        <v>0.1300208296921826</v>
+        <v>0.1299666831868092</v>
       </c>
       <c r="T21">
         <v>1.943803306854716</v>
       </c>
       <c r="U21">
-        <v>0.0528</v>
+        <v>0.0518</v>
       </c>
       <c r="V21">
         <v>0.258</v>
       </c>
       <c r="W21">
-        <v>0.0391776</v>
+        <v>0.0384356</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>7.143384064405675</v>
+        <v>7.281287231672194</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3064,13 +3064,13 @@
         <v>0.2</v>
       </c>
       <c r="B22">
-        <v>0.1125093148777613</v>
+        <v>0.1123171751965757</v>
       </c>
       <c r="C22">
-        <v>51804.15822814586</v>
+        <v>51942.23600402421</v>
       </c>
       <c r="D22">
-        <v>61707.13885334174</v>
+        <v>61845.21662922009</v>
       </c>
       <c r="E22">
         <v>2222.277499216478</v>
@@ -3097,37 +3097,37 @@
         <v>4533</v>
       </c>
       <c r="M22">
-        <v>667.9717770103424</v>
+        <v>655.3207963851465</v>
       </c>
       <c r="N22">
-        <v>3865.028222989657</v>
+        <v>3877.679203614854</v>
       </c>
       <c r="O22">
-        <v>997.1772815313317</v>
+        <v>1000.441234532632</v>
       </c>
       <c r="P22">
-        <v>2867.850941458326</v>
+        <v>2877.237969082221</v>
       </c>
       <c r="Q22">
-        <v>3038.850941458326</v>
+        <v>3048.237969082221</v>
       </c>
       <c r="R22">
         <v>0.25</v>
       </c>
       <c r="S22">
-        <v>0.1308422435972016</v>
+        <v>0.1307875689957196</v>
       </c>
       <c r="T22">
         <v>1.962761408677128</v>
       </c>
       <c r="U22">
-        <v>0.0528</v>
+        <v>0.0518</v>
       </c>
       <c r="V22">
         <v>0.258</v>
       </c>
       <c r="W22">
-        <v>0.0391776</v>
+        <v>0.0384356</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>6.786214861185392</v>
+        <v>6.917222870088584</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3146,13 +3146,13 @@
         <v>0.21</v>
       </c>
       <c r="B23">
-        <v>0.1126008177048547</v>
+        <v>0.112323467011836</v>
       </c>
       <c r="C23">
-        <v>51087.08361994069</v>
+        <v>51303.83762823623</v>
       </c>
       <c r="D23">
-        <v>61622.61327639637</v>
+        <v>61839.36728469191</v>
       </c>
       <c r="E23">
         <v>2854.826530476272</v>
@@ -3179,37 +3179,37 @@
         <v>4533</v>
       </c>
       <c r="M23">
-        <v>730.594131105062</v>
+        <v>710.6688366203786</v>
       </c>
       <c r="N23">
-        <v>3802.405868894938</v>
+        <v>3822.331163379622</v>
       </c>
       <c r="O23">
-        <v>981.020714174894</v>
+        <v>986.1614401519424</v>
       </c>
       <c r="P23">
-        <v>2821.385154720044</v>
+        <v>2836.169723227679</v>
       </c>
       <c r="Q23">
-        <v>2992.385154720044</v>
+        <v>3007.169723227679</v>
       </c>
       <c r="R23">
         <v>0.2658227848101266</v>
       </c>
       <c r="S23">
-        <v>0.1316844527909553</v>
+        <v>0.131629236723843</v>
       </c>
       <c r="T23">
         <v>1.982199462444411</v>
       </c>
       <c r="U23">
-        <v>0.055</v>
+        <v>0.0535</v>
       </c>
       <c r="V23">
         <v>0.258</v>
       </c>
       <c r="W23">
-        <v>0.04081</v>
+        <v>0.039697</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3217,7 +3217,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>6.204539301655215</v>
+        <v>6.378498347496015</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3228,13 +3228,13 @@
         <v>0.22</v>
       </c>
       <c r="B24">
-        <v>0.1123658405319481</v>
+        <v>0.1120774788270962</v>
       </c>
       <c r="C24">
-        <v>50672.06218750773</v>
+        <v>50900.80477612229</v>
       </c>
       <c r="D24">
-        <v>61840.1408752232</v>
+        <v>62068.88346383776</v>
       </c>
       <c r="E24">
         <v>3487.375561736066</v>
@@ -3261,37 +3261,37 @@
         <v>4533</v>
       </c>
       <c r="M24">
-        <v>765.3843278243507</v>
+        <v>744.5102097927775</v>
       </c>
       <c r="N24">
-        <v>3767.615672175649</v>
+        <v>3788.489790207223</v>
       </c>
       <c r="O24">
-        <v>972.0448434213175</v>
+        <v>977.4303658734634</v>
       </c>
       <c r="P24">
-        <v>2795.570828754332</v>
+        <v>2811.059424333759</v>
       </c>
       <c r="Q24">
-        <v>2966.570828754332</v>
+        <v>2982.059424333759</v>
       </c>
       <c r="R24">
         <v>0.282051282051282</v>
       </c>
       <c r="S24">
-        <v>0.1325482570922411</v>
+        <v>0.1324924856757644</v>
       </c>
       <c r="T24">
         <v>2.002135927846753</v>
       </c>
       <c r="U24">
-        <v>0.055</v>
+        <v>0.0535</v>
       </c>
       <c r="V24">
         <v>0.258</v>
       </c>
       <c r="W24">
-        <v>0.04081</v>
+        <v>0.039697</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>5.922514787943614</v>
+        <v>6.088566604428014</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3310,13 +3310,13 @@
         <v>0.23</v>
       </c>
       <c r="B25">
-        <v>0.1121308633590415</v>
+        <v>0.1118314906423565</v>
       </c>
       <c r="C25">
-        <v>50258.58193869919</v>
+        <v>50499.48196470946</v>
       </c>
       <c r="D25">
-        <v>62059.20965767446</v>
+        <v>62300.10968368471</v>
       </c>
       <c r="E25">
         <v>4119.92459299586</v>
@@ -3343,37 +3343,37 @@
         <v>4533</v>
       </c>
       <c r="M25">
-        <v>800.1745245436394</v>
+        <v>778.3515829651765</v>
       </c>
       <c r="N25">
-        <v>3732.82547545636</v>
+        <v>3754.648417034824</v>
       </c>
       <c r="O25">
-        <v>963.068972667741</v>
+        <v>968.6992915949845</v>
       </c>
       <c r="P25">
-        <v>2769.756502788619</v>
+        <v>2785.949125439839</v>
       </c>
       <c r="Q25">
-        <v>2940.756502788619</v>
+        <v>2956.949125439839</v>
       </c>
       <c r="R25">
         <v>0.2987012987012987</v>
       </c>
       <c r="S25">
-        <v>0.133434497868885</v>
+        <v>0.1333781566783851</v>
       </c>
       <c r="T25">
         <v>2.022590223519286</v>
       </c>
       <c r="U25">
-        <v>0.055</v>
+        <v>0.0535</v>
       </c>
       <c r="V25">
         <v>0.258</v>
       </c>
       <c r="W25">
-        <v>0.04081</v>
+        <v>0.039697</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>5.665014144989543</v>
+        <v>5.823846317278971</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3392,13 +3392,13 @@
         <v>0.24</v>
       </c>
       <c r="B26">
-        <v>0.1121630061861349</v>
+        <v>0.1117279664576168</v>
       </c>
       <c r="C26">
-        <v>49595.97461803667</v>
+        <v>49964.76043232066</v>
       </c>
       <c r="D26">
-        <v>62029.15136827173</v>
+        <v>62397.93718255572</v>
       </c>
       <c r="E26">
         <v>4752.473624255654</v>
@@ -3425,37 +3425,37 @@
         <v>4533</v>
       </c>
       <c r="M26">
-        <v>857.7364863882807</v>
+        <v>824.3378975377635</v>
       </c>
       <c r="N26">
-        <v>3675.263513611719</v>
+        <v>3708.662102462236</v>
       </c>
       <c r="O26">
-        <v>948.2179865118236</v>
+        <v>956.834822435257</v>
       </c>
       <c r="P26">
-        <v>2727.045527099895</v>
+        <v>2751.827280026979</v>
       </c>
       <c r="Q26">
-        <v>2898.045527099895</v>
+        <v>2922.827280026979</v>
       </c>
       <c r="R26">
         <v>0.3157894736842105</v>
       </c>
       <c r="S26">
-        <v>0.1343440607712301</v>
+        <v>0.1342871348126536</v>
       </c>
       <c r="T26">
         <v>2.043582790130569</v>
       </c>
       <c r="U26">
-        <v>0.0565</v>
+        <v>0.0543</v>
       </c>
       <c r="V26">
         <v>0.258</v>
       </c>
       <c r="W26">
-        <v>0.041923</v>
+        <v>0.0402906</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>5.284839891896588</v>
+        <v>5.498958635214681</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3474,13 +3474,13 @@
         <v>0.25</v>
       </c>
       <c r="B27">
-        <v>0.1119391590132283</v>
+        <v>0.111487914272877</v>
       </c>
       <c r="C27">
-        <v>49173.36248919206</v>
+        <v>49560.24057978771</v>
       </c>
       <c r="D27">
-        <v>62239.08827068691</v>
+        <v>62625.96636128257</v>
       </c>
       <c r="E27">
         <v>5385.022655515448</v>
@@ -3507,37 +3507,37 @@
         <v>4533</v>
       </c>
       <c r="M27">
-        <v>893.4755066544591</v>
+        <v>858.6853099351704</v>
       </c>
       <c r="N27">
-        <v>3639.524493345541</v>
+        <v>3674.31469006483</v>
       </c>
       <c r="O27">
-        <v>938.9973192831496</v>
+        <v>947.9731900367261</v>
       </c>
       <c r="P27">
-        <v>2700.527174062391</v>
+        <v>2726.341500028104</v>
       </c>
       <c r="Q27">
-        <v>2871.527174062391</v>
+        <v>2897.341500028104</v>
       </c>
       <c r="R27">
         <v>0.3333333333333333</v>
       </c>
       <c r="S27">
-        <v>0.1352778786843044</v>
+        <v>0.1352203523638361</v>
       </c>
       <c r="T27">
         <v>2.065135158518154</v>
       </c>
       <c r="U27">
-        <v>0.0565</v>
+        <v>0.0543</v>
       </c>
       <c r="V27">
         <v>0.258</v>
       </c>
       <c r="W27">
-        <v>0.041923</v>
+        <v>0.0402906</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3545,7 +3545,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>5.073446296220724</v>
+        <v>5.279000289806095</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3556,13 +3556,13 @@
         <v>0.26</v>
       </c>
       <c r="B28">
-        <v>0.1117153118403216</v>
+        <v>0.1112478620881373</v>
       </c>
       <c r="C28">
-        <v>48752.17624397853</v>
+        <v>49157.39347563167</v>
       </c>
       <c r="D28">
-        <v>62450.45105673317</v>
+        <v>62855.6682883863</v>
       </c>
       <c r="E28">
         <v>6017.571686775242</v>
@@ -3589,37 +3589,37 @@
         <v>4533</v>
       </c>
       <c r="M28">
-        <v>929.2145269206374</v>
+        <v>893.0327223325771</v>
       </c>
       <c r="N28">
-        <v>3603.785473079362</v>
+        <v>3639.967277667423</v>
       </c>
       <c r="O28">
-        <v>929.7766520544756</v>
+        <v>939.1115576381951</v>
       </c>
       <c r="P28">
-        <v>2674.008821024887</v>
+        <v>2700.855720029228</v>
       </c>
       <c r="Q28">
-        <v>2845.008821024887</v>
+        <v>2871.855720029228</v>
       </c>
       <c r="R28">
         <v>0.3513513513513514</v>
       </c>
       <c r="S28">
-        <v>0.1362369349193536</v>
+        <v>0.1361787920109963</v>
       </c>
       <c r="T28">
         <v>2.087270023348645</v>
       </c>
       <c r="U28">
-        <v>0.0565</v>
+        <v>0.0543</v>
       </c>
       <c r="V28">
         <v>0.258</v>
       </c>
       <c r="W28">
-        <v>0.041923</v>
+        <v>0.0402906</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3627,7 +3627,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>4.87831374636608</v>
+        <v>5.075961817121245</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3638,13 +3638,13 @@
         <v>0.27</v>
       </c>
       <c r="B29">
-        <v>0.1114914646674151</v>
+        <v>0.1110078099033976</v>
       </c>
       <c r="C29">
-        <v>48332.43045871981</v>
+        <v>48756.23759372398</v>
       </c>
       <c r="D29">
-        <v>62663.25430273425</v>
+        <v>63087.06143773843</v>
       </c>
       <c r="E29">
         <v>6650.120718035036</v>
@@ -3671,37 +3671,37 @@
         <v>4533</v>
       </c>
       <c r="M29">
-        <v>964.9535471868157</v>
+        <v>927.380134729984</v>
       </c>
       <c r="N29">
-        <v>3568.046452813184</v>
+        <v>3605.619865270016</v>
       </c>
       <c r="O29">
-        <v>920.5559848258016</v>
+        <v>930.2499252396641</v>
       </c>
       <c r="P29">
-        <v>2647.490467987383</v>
+        <v>2675.369940030352</v>
       </c>
       <c r="Q29">
-        <v>2818.490467987383</v>
+        <v>2846.369940030352</v>
       </c>
       <c r="R29">
         <v>0.3698630136986302</v>
       </c>
       <c r="S29">
-        <v>0.1372222666676919</v>
+        <v>0.1371634902786268</v>
       </c>
       <c r="T29">
         <v>2.110011322832028</v>
       </c>
       <c r="U29">
-        <v>0.0565</v>
+        <v>0.0543</v>
       </c>
       <c r="V29">
         <v>0.258</v>
       </c>
       <c r="W29">
-        <v>0.041923</v>
+        <v>0.0402906</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>4.697635459463633</v>
+        <v>4.887963231301939</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3720,13 +3720,13 @@
         <v>0.28</v>
       </c>
       <c r="B30">
-        <v>0.1112676174945084</v>
+        <v>0.1107677577186578</v>
       </c>
       <c r="C30">
-        <v>47914.13990909747</v>
+        <v>48356.79168097601</v>
       </c>
       <c r="D30">
-        <v>62877.51278437171</v>
+        <v>63320.16455625024</v>
       </c>
       <c r="E30">
         <v>7282.66974929483</v>
@@ -3753,37 +3753,37 @@
         <v>4533</v>
       </c>
       <c r="M30">
-        <v>1000.692567452994</v>
+        <v>961.7275471273908</v>
       </c>
       <c r="N30">
-        <v>3532.307432547006</v>
+        <v>3571.272452872609</v>
       </c>
       <c r="O30">
-        <v>911.3353175971276</v>
+        <v>921.3882928411332</v>
       </c>
       <c r="P30">
-        <v>2620.972114949878</v>
+        <v>2649.884160031476</v>
       </c>
       <c r="Q30">
-        <v>2791.972114949878</v>
+        <v>2820.884160031476</v>
       </c>
       <c r="R30">
         <v>0.388888888888889</v>
       </c>
       <c r="S30">
-        <v>0.1382349687423728</v>
+        <v>0.1381755412759137</v>
       </c>
       <c r="T30">
         <v>2.133384325078838</v>
       </c>
       <c r="U30">
-        <v>0.0565</v>
+        <v>0.0543</v>
       </c>
       <c r="V30">
         <v>0.258</v>
       </c>
       <c r="W30">
-        <v>0.041923</v>
+        <v>0.0402906</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>4.52986276448279</v>
+        <v>4.713393115898299</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3802,13 +3802,13 @@
         <v>0.29</v>
       </c>
       <c r="B31">
-        <v>0.1110437703216018</v>
+        <v>0.1105277055339181</v>
       </c>
       <c r="C31">
-        <v>47497.31957357065</v>
+        <v>47959.07476240161</v>
       </c>
       <c r="D31">
-        <v>63093.24148010468</v>
+        <v>63554.99666893564</v>
       </c>
       <c r="E31">
         <v>7915.218780554624</v>
@@ -3835,37 +3835,37 @@
         <v>4533</v>
       </c>
       <c r="M31">
-        <v>1036.431587719173</v>
+        <v>996.0749595247976</v>
       </c>
       <c r="N31">
-        <v>3496.568412280827</v>
+        <v>3536.925040475202</v>
       </c>
       <c r="O31">
-        <v>902.1146503684536</v>
+        <v>912.5266604426023</v>
       </c>
       <c r="P31">
-        <v>2594.453761912374</v>
+        <v>2624.3983800326</v>
       </c>
       <c r="Q31">
-        <v>2765.453761912374</v>
+        <v>2795.3983800326</v>
       </c>
       <c r="R31">
         <v>0.4084507042253521</v>
       </c>
       <c r="S31">
-        <v>0.1392761976360589</v>
+        <v>0.1392161007519973</v>
       </c>
       <c r="T31">
         <v>2.157415721755134</v>
       </c>
       <c r="U31">
-        <v>0.0565</v>
+        <v>0.0543</v>
       </c>
       <c r="V31">
         <v>0.258</v>
       </c>
       <c r="W31">
-        <v>0.041923</v>
+        <v>0.0402906</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3873,7 +3873,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>4.373660600190279</v>
+        <v>4.550862318798357</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3884,13 +3884,13 @@
         <v>0.3</v>
       </c>
       <c r="B32">
-        <v>0.1111315631486952</v>
+        <v>0.1102876533491784</v>
       </c>
       <c r="C32">
-        <v>46779.98558121299</v>
+        <v>47563.10614629348</v>
       </c>
       <c r="D32">
-        <v>63008.4565190068</v>
+        <v>63791.57708408729</v>
       </c>
       <c r="E32">
         <v>8547.767811814418</v>
@@ -3917,45 +3917,45 @@
         <v>4533</v>
       </c>
       <c r="M32">
-        <v>1098.737667298262</v>
+        <v>1030.422371922204</v>
       </c>
       <c r="N32">
-        <v>3434.262332701738</v>
+        <v>3502.577628077795</v>
       </c>
       <c r="O32">
-        <v>886.0396818370484</v>
+        <v>903.6650280440713</v>
       </c>
       <c r="P32">
-        <v>2548.22265086469</v>
+        <v>2598.912600033724</v>
       </c>
       <c r="Q32">
-        <v>2719.22265086469</v>
+        <v>2769.912600033724</v>
       </c>
       <c r="R32">
         <v>0.4285714285714286</v>
       </c>
       <c r="S32">
-        <v>0.1403471759267075</v>
+        <v>0.1402863904988262</v>
       </c>
       <c r="T32">
         <v>2.18213372976504</v>
       </c>
       <c r="U32">
-        <v>0.0579</v>
+        <v>0.0543</v>
       </c>
       <c r="V32">
         <v>0.258</v>
       </c>
       <c r="W32">
-        <v>0.0429618</v>
+        <v>0.0402906</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y32">
-        <v>4.12564357709371</v>
+        <v>4.399166908171745</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3966,13 +3966,13 @@
         <v>0.31</v>
       </c>
       <c r="B33">
-        <v>0.1109181039757886</v>
+        <v>0.1100476011644386</v>
       </c>
       <c r="C33">
-        <v>46353.98023279247</v>
+        <v>47168.90542951525</v>
       </c>
       <c r="D33">
-        <v>63215.00020184608</v>
+        <v>64029.92539856886</v>
       </c>
       <c r="E33">
         <v>9180.316843074212</v>
@@ -3999,45 +3999,45 @@
         <v>4533</v>
       </c>
       <c r="M33">
-        <v>1135.362256208204</v>
+        <v>1064.769784319611</v>
       </c>
       <c r="N33">
-        <v>3397.637743791796</v>
+        <v>3468.230215680389</v>
       </c>
       <c r="O33">
-        <v>876.5905378982834</v>
+        <v>894.8033956455404</v>
       </c>
       <c r="P33">
-        <v>2521.047205893512</v>
+        <v>2573.426820034849</v>
       </c>
       <c r="Q33">
-        <v>2692.047205893512</v>
+        <v>2744.426820034849</v>
       </c>
       <c r="R33">
         <v>0.4492753623188406</v>
       </c>
       <c r="S33">
-        <v>0.1414491970663603</v>
+        <v>0.1413877031368676</v>
       </c>
       <c r="T33">
         <v>2.207568201775233</v>
       </c>
       <c r="U33">
-        <v>0.0579</v>
+        <v>0.0543</v>
       </c>
       <c r="V33">
         <v>0.258</v>
       </c>
       <c r="W33">
-        <v>0.0429618</v>
+        <v>0.0402906</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y33">
-        <v>3.992558300413267</v>
+        <v>4.257258298230721</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4048,13 +4048,13 @@
         <v>0.32</v>
       </c>
       <c r="B34">
-        <v>0.110704644802882</v>
+        <v>0.1100449889796989</v>
       </c>
       <c r="C34">
-        <v>45929.33345104591</v>
+        <v>46538.95983856526</v>
       </c>
       <c r="D34">
-        <v>63422.90245135931</v>
+        <v>64032.52883887868</v>
       </c>
       <c r="E34">
         <v>9812.865874334006</v>
@@ -4081,37 +4081,37 @@
         <v>4533</v>
       </c>
       <c r="M34">
-        <v>1171.986845118146</v>
+        <v>1119.358765717331</v>
       </c>
       <c r="N34">
-        <v>3361.013154881854</v>
+        <v>3413.641234282669</v>
       </c>
       <c r="O34">
-        <v>867.1413939595183</v>
+        <v>880.7194384449286</v>
       </c>
       <c r="P34">
-        <v>2493.871760922335</v>
+        <v>2532.92179583774</v>
       </c>
       <c r="Q34">
-        <v>2664.871760922335</v>
+        <v>2703.92179583774</v>
       </c>
       <c r="R34">
         <v>0.4705882352941177</v>
       </c>
       <c r="S34">
-        <v>0.1425836305924736</v>
+        <v>0.1425214073230866</v>
       </c>
       <c r="T34">
         <v>2.233750746491608</v>
       </c>
       <c r="U34">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V34">
         <v>0.258</v>
       </c>
       <c r="W34">
-        <v>0.0429618</v>
+        <v>0.0410326</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>3.867790853525352</v>
+        <v>4.049639971412621</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4130,13 +4130,13 @@
         <v>0.33</v>
       </c>
       <c r="B35">
-        <v>0.1104911856299754</v>
+        <v>0.1098123567949592</v>
       </c>
       <c r="C35">
-        <v>45506.05868441374</v>
+        <v>46139.11630080749</v>
       </c>
       <c r="D35">
-        <v>63632.17671598696</v>
+        <v>64265.23433238069</v>
       </c>
       <c r="E35">
         <v>10445.4149055938</v>
@@ -4163,37 +4163,37 @@
         <v>4533</v>
       </c>
       <c r="M35">
-        <v>1208.611434028088</v>
+        <v>1154.338727145998</v>
       </c>
       <c r="N35">
-        <v>3324.388565971912</v>
+        <v>3378.661272854002</v>
       </c>
       <c r="O35">
-        <v>857.6922500207532</v>
+        <v>871.6946083963326</v>
       </c>
       <c r="P35">
-        <v>2466.696315951158</v>
+        <v>2506.96666445767</v>
       </c>
       <c r="Q35">
-        <v>2637.696315951158</v>
+        <v>2677.96666445767</v>
       </c>
       <c r="R35">
         <v>0.4925373134328359</v>
       </c>
       <c r="S35">
-        <v>0.1437519278059335</v>
+        <v>0.1436889534253122</v>
       </c>
       <c r="T35">
         <v>2.260714859706979</v>
       </c>
       <c r="U35">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V35">
         <v>0.258</v>
       </c>
       <c r="W35">
-        <v>0.0429618</v>
+        <v>0.0410326</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>3.750585070085191</v>
+        <v>3.926923608642541</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4212,13 +4212,13 @@
         <v>0.34</v>
       </c>
       <c r="B36">
-        <v>0.1102777264570688</v>
+        <v>0.1095797246102194</v>
       </c>
       <c r="C36">
-        <v>45084.16955942539</v>
+        <v>45740.97031780353</v>
       </c>
       <c r="D36">
-        <v>63842.83662225838</v>
+        <v>64499.63738063653</v>
       </c>
       <c r="E36">
         <v>11077.96393685359</v>
@@ -4245,37 +4245,37 @@
         <v>4533</v>
       </c>
       <c r="M36">
-        <v>1245.23602293803</v>
+        <v>1189.318688574665</v>
       </c>
       <c r="N36">
-        <v>3287.76397706197</v>
+        <v>3343.681311425335</v>
       </c>
       <c r="O36">
-        <v>848.2431060819882</v>
+        <v>862.6697783477366</v>
       </c>
       <c r="P36">
-        <v>2439.520870979982</v>
+        <v>2481.011533077599</v>
       </c>
       <c r="Q36">
-        <v>2610.520870979982</v>
+        <v>2652.011533077599</v>
       </c>
       <c r="R36">
         <v>0.5151515151515152</v>
       </c>
       <c r="S36">
-        <v>0.1449556279652558</v>
+        <v>0.1448918797124537</v>
       </c>
       <c r="T36">
         <v>2.288496067262209</v>
       </c>
       <c r="U36">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V36">
         <v>0.258</v>
       </c>
       <c r="W36">
-        <v>0.0429618</v>
+        <v>0.0410326</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4283,7 +4283,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>3.64027374449445</v>
+        <v>3.811425855447172</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4294,13 +4294,13 @@
         <v>0.35</v>
       </c>
       <c r="B37">
-        <v>0.1100642672841622</v>
+        <v>0.1093470924254797</v>
       </c>
       <c r="C37">
-        <v>44663.6798836569</v>
+        <v>45344.54053269765</v>
       </c>
       <c r="D37">
-        <v>64054.8959777497</v>
+        <v>64735.75662679045</v>
       </c>
       <c r="E37">
         <v>11710.51296811339</v>
@@ -4327,37 +4327,37 @@
         <v>4533</v>
       </c>
       <c r="M37">
-        <v>1281.860611847973</v>
+        <v>1224.298650003331</v>
       </c>
       <c r="N37">
-        <v>3251.139388152027</v>
+        <v>3308.701349996669</v>
       </c>
       <c r="O37">
-        <v>838.793962143223</v>
+        <v>853.6449482991405</v>
       </c>
       <c r="P37">
-        <v>2412.345426008804</v>
+        <v>2455.056401697528</v>
       </c>
       <c r="Q37">
-        <v>2583.345426008804</v>
+        <v>2626.056401697528</v>
       </c>
       <c r="R37">
         <v>0.5384615384615385</v>
       </c>
       <c r="S37">
-        <v>0.1461963650525572</v>
+        <v>0.1461318191161226</v>
       </c>
       <c r="T37">
         <v>2.317132081203755</v>
       </c>
       <c r="U37">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V37">
         <v>0.258</v>
       </c>
       <c r="W37">
-        <v>0.0429618</v>
+        <v>0.0410326</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4365,7 +4365,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>3.536265923223179</v>
+        <v>3.702527973862967</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4376,13 +4376,13 @@
         <v>0.36</v>
       </c>
       <c r="B38">
-        <v>0.1098508081112556</v>
+        <v>0.10911446024074</v>
       </c>
       <c r="C38">
-        <v>44244.60364874775</v>
+        <v>44949.84586263132</v>
       </c>
       <c r="D38">
-        <v>64268.36877410034</v>
+        <v>64973.6109879839</v>
       </c>
       <c r="E38">
         <v>12343.06199937318</v>
@@ -4409,37 +4409,37 @@
         <v>4533</v>
       </c>
       <c r="M38">
-        <v>1318.485200757915</v>
+        <v>1259.278611431998</v>
       </c>
       <c r="N38">
-        <v>3214.514799242085</v>
+        <v>3273.721388568002</v>
       </c>
       <c r="O38">
-        <v>829.344818204458</v>
+        <v>844.6201182505446</v>
       </c>
       <c r="P38">
-        <v>2385.169981037627</v>
+        <v>2429.101270317457</v>
       </c>
       <c r="Q38">
-        <v>2556.169981037627</v>
+        <v>2600.101270317457</v>
       </c>
       <c r="R38">
         <v>0.5625</v>
       </c>
       <c r="S38">
-        <v>0.1474758751738369</v>
+        <v>0.1474105066261562</v>
       </c>
       <c r="T38">
         <v>2.346662970580974</v>
       </c>
       <c r="U38">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V38">
         <v>0.258</v>
       </c>
       <c r="W38">
-        <v>0.0429618</v>
+        <v>0.0410326</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4447,7 +4447,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>3.438036314244758</v>
+        <v>3.599679974588996</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4458,13 +4458,13 @@
         <v>0.37</v>
       </c>
       <c r="B39">
-        <v>0.109637348938349</v>
+        <v>0.1088818280560002</v>
       </c>
       <c r="C39">
-        <v>43826.95503347836</v>
+        <v>44556.90550379531</v>
       </c>
       <c r="D39">
-        <v>64483.26919009073</v>
+        <v>65213.21966040769</v>
       </c>
       <c r="E39">
         <v>12975.61103063298</v>
@@ -4491,37 +4491,37 @@
         <v>4533</v>
       </c>
       <c r="M39">
-        <v>1355.109789667857</v>
+        <v>1294.258572860665</v>
       </c>
       <c r="N39">
-        <v>3177.890210332143</v>
+        <v>3238.741427139335</v>
       </c>
       <c r="O39">
-        <v>819.8956742656931</v>
+        <v>835.5952882019486</v>
       </c>
       <c r="P39">
-        <v>2357.994536066451</v>
+        <v>2403.146138937387</v>
       </c>
       <c r="Q39">
-        <v>2528.994536066451</v>
+        <v>2574.146138937387</v>
       </c>
       <c r="R39">
         <v>0.5873015873015873</v>
       </c>
       <c r="S39">
-        <v>0.148796004664046</v>
+        <v>0.1487297873904765</v>
       </c>
       <c r="T39">
         <v>2.377131348509851</v>
       </c>
       <c r="U39">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V39">
         <v>0.258</v>
       </c>
       <c r="W39">
-        <v>0.0429618</v>
+        <v>0.0410326</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>3.345116413859764</v>
+        <v>3.502391326627131</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4540,13 +4540,13 @@
         <v>0.38</v>
       </c>
       <c r="B40">
-        <v>0.1094238897654424</v>
+        <v>0.1086491958712605</v>
       </c>
       <c r="C40">
-        <v>43410.74840690925</v>
+        <v>44165.73893659421</v>
       </c>
       <c r="D40">
-        <v>64699.61159478142</v>
+        <v>65454.60212446639</v>
       </c>
       <c r="E40">
         <v>13608.16006189277</v>
@@ -4573,37 +4573,37 @@
         <v>4533</v>
       </c>
       <c r="M40">
-        <v>1391.734378577799</v>
+        <v>1329.238534289331</v>
       </c>
       <c r="N40">
-        <v>3141.265621422202</v>
+        <v>3203.761465710669</v>
       </c>
       <c r="O40">
-        <v>810.446530326928</v>
+        <v>826.5704581533525</v>
       </c>
       <c r="P40">
-        <v>2330.819091095274</v>
+        <v>2377.191007557316</v>
       </c>
       <c r="Q40">
-        <v>2501.819091095274</v>
+        <v>2548.191007557316</v>
       </c>
       <c r="R40">
         <v>0.6129032258064516</v>
       </c>
       <c r="S40">
-        <v>0.15015871897652</v>
+        <v>0.1500916255988072</v>
       </c>
       <c r="T40">
         <v>2.408582577339659</v>
       </c>
       <c r="U40">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V40">
         <v>0.258</v>
       </c>
       <c r="W40">
-        <v>0.0429618</v>
+        <v>0.0410326</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>3.257087034547665</v>
+        <v>3.410223133821154</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4622,13 +4622,13 @@
         <v>0.39</v>
       </c>
       <c r="B41">
-        <v>0.1092104305925358</v>
+        <v>0.1084165636865207</v>
       </c>
       <c r="C41">
-        <v>42995.99833158379</v>
+        <v>43776.36593092595</v>
       </c>
       <c r="D41">
-        <v>64917.41055071574</v>
+        <v>65697.77815005791</v>
       </c>
       <c r="E41">
         <v>14240.70909315256</v>
@@ -4655,37 +4655,37 @@
         <v>4533</v>
       </c>
       <c r="M41">
-        <v>1428.358967487741</v>
+        <v>1364.218495717998</v>
       </c>
       <c r="N41">
-        <v>3104.641032512259</v>
+        <v>3168.781504282002</v>
       </c>
       <c r="O41">
-        <v>800.9973863881629</v>
+        <v>817.5456281047566</v>
       </c>
       <c r="P41">
-        <v>2303.643646124096</v>
+        <v>2351.235876177246</v>
       </c>
       <c r="Q41">
-        <v>2474.643646124096</v>
+        <v>2522.235876177246</v>
       </c>
       <c r="R41">
         <v>0.639344262295082</v>
       </c>
       <c r="S41">
-        <v>0.15156611244678</v>
+        <v>0.1514981142401979</v>
       </c>
       <c r="T41">
         <v>2.441064993999952</v>
       </c>
       <c r="U41">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V41">
         <v>0.258</v>
       </c>
       <c r="W41">
-        <v>0.0429618</v>
+        <v>0.0410326</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>3.173571982379777</v>
+        <v>3.322781515005227</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4704,13 +4704,13 @@
         <v>0.4</v>
       </c>
       <c r="B42">
-        <v>0.1089969714196292</v>
+        <v>0.108183931501781</v>
       </c>
       <c r="C42">
-        <v>42582.7195667958</v>
+        <v>43388.80655157926</v>
       </c>
       <c r="D42">
-        <v>65136.68081718757</v>
+        <v>65942.76780197101</v>
       </c>
       <c r="E42">
         <v>14873.25812441236</v>
@@ -4737,37 +4737,37 @@
         <v>4533</v>
       </c>
       <c r="M42">
-        <v>1464.983556397683</v>
+        <v>1399.198457146664</v>
       </c>
       <c r="N42">
-        <v>3068.016443602317</v>
+        <v>3133.801542853335</v>
       </c>
       <c r="O42">
-        <v>791.5482424493978</v>
+        <v>808.5207980561605</v>
       </c>
       <c r="P42">
-        <v>2276.468201152919</v>
+        <v>2325.280744797175</v>
       </c>
       <c r="Q42">
-        <v>2447.468201152919</v>
+        <v>2496.280744797175</v>
       </c>
       <c r="R42">
         <v>0.6666666666666667</v>
       </c>
       <c r="S42">
-        <v>0.1530204190327153</v>
+        <v>0.1529514858363017</v>
       </c>
       <c r="T42">
         <v>2.474630157882256</v>
       </c>
       <c r="U42">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V42">
         <v>0.258</v>
       </c>
       <c r="W42">
-        <v>0.0429618</v>
+        <v>0.0410326</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4775,7 +4775,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>3.094232682820282</v>
+        <v>3.239711977130096</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4786,13 +4786,13 @@
         <v>0.41</v>
       </c>
       <c r="B43">
-        <v>0.1087835122467226</v>
+        <v>0.1079512993170413</v>
       </c>
       <c r="C43">
-        <v>42170.92707192372</v>
+        <v>43003.08116375298</v>
       </c>
       <c r="D43">
-        <v>65357.43735357528</v>
+        <v>66189.59144540454</v>
       </c>
       <c r="E43">
         <v>15505.80715567216</v>
@@ -4819,37 +4819,37 @@
         <v>4533</v>
       </c>
       <c r="M43">
-        <v>1501.608145307625</v>
+        <v>1434.178418575331</v>
       </c>
       <c r="N43">
-        <v>3031.391854692375</v>
+        <v>3098.821581424669</v>
       </c>
       <c r="O43">
-        <v>782.0990985106328</v>
+        <v>799.4959680075646</v>
       </c>
       <c r="P43">
-        <v>2249.292756181742</v>
+        <v>2299.325613417104</v>
       </c>
       <c r="Q43">
-        <v>2420.292756181742</v>
+        <v>2470.325613417104</v>
       </c>
       <c r="R43">
         <v>0.6949152542372882</v>
       </c>
       <c r="S43">
-        <v>0.1545240241469874</v>
+        <v>0.1544541242661716</v>
       </c>
       <c r="T43">
         <v>2.509333123930061</v>
       </c>
       <c r="U43">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V43">
         <v>0.258</v>
       </c>
       <c r="W43">
-        <v>0.0429618</v>
+        <v>0.0410326</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4857,7 +4857,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>3.018763592995397</v>
+        <v>3.16069461183424</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4868,13 +4868,13 @@
         <v>0.42</v>
       </c>
       <c r="B44">
-        <v>0.109380317073816</v>
+        <v>0.1077186671323015</v>
       </c>
       <c r="C44">
-        <v>40924.89204540247</v>
+        <v>42619.21043869886</v>
       </c>
       <c r="D44">
-        <v>64743.95135831383</v>
+        <v>66438.26975161021</v>
       </c>
       <c r="E44">
         <v>16138.35618693195</v>
@@ -4901,45 +4901,45 @@
         <v>4533</v>
       </c>
       <c r="M44">
-        <v>1607.307088431136</v>
+        <v>1469.158380003998</v>
       </c>
       <c r="N44">
-        <v>2925.692911568864</v>
+        <v>3063.841619996002</v>
       </c>
       <c r="O44">
-        <v>754.8287711847668</v>
+        <v>790.4711379589687</v>
       </c>
       <c r="P44">
-        <v>2170.864140384097</v>
+        <v>2273.370482037034</v>
       </c>
       <c r="Q44">
-        <v>2341.864140384097</v>
+        <v>2444.370482037034</v>
       </c>
       <c r="R44">
         <v>0.7241379310344827</v>
       </c>
       <c r="S44">
-        <v>0.1560794777134758</v>
+        <v>0.156008577814313</v>
       </c>
       <c r="T44">
         <v>2.545232743979515</v>
       </c>
       <c r="U44">
-        <v>0.0605</v>
+        <v>0.0553</v>
       </c>
       <c r="V44">
         <v>0.258</v>
       </c>
       <c r="W44">
-        <v>0.044891</v>
+        <v>0.0410326</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y44">
-        <v>2.820245137116007</v>
+        <v>3.085439978219139</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4950,13 +4950,13 @@
         <v>0.43</v>
       </c>
       <c r="B45">
-        <v>0.1091861499009094</v>
+        <v>0.1074860349475618</v>
       </c>
       <c r="C45">
-        <v>40490.66946270752</v>
+        <v>42237.21535949296</v>
       </c>
       <c r="D45">
-        <v>64942.27780687866</v>
+        <v>66688.82370366409</v>
       </c>
       <c r="E45">
         <v>16770.90521819174</v>
@@ -4983,45 +4983,45 @@
         <v>4533</v>
       </c>
       <c r="M45">
-        <v>1645.576304822354</v>
+        <v>1504.138341432664</v>
       </c>
       <c r="N45">
-        <v>2887.423695177646</v>
+        <v>3028.861658567336</v>
       </c>
       <c r="O45">
-        <v>744.9553133558326</v>
+        <v>781.4463079103726</v>
       </c>
       <c r="P45">
-        <v>2142.468381821813</v>
+        <v>2247.415350656963</v>
       </c>
       <c r="Q45">
-        <v>2313.468381821813</v>
+        <v>2418.415350656963</v>
       </c>
       <c r="R45">
         <v>0.7543859649122806</v>
       </c>
       <c r="S45">
-        <v>0.1576895085980866</v>
+        <v>0.1576175735922137</v>
       </c>
       <c r="T45">
         <v>2.582391999820177</v>
       </c>
       <c r="U45">
-        <v>0.0605</v>
+        <v>0.0553</v>
       </c>
       <c r="V45">
         <v>0.258</v>
       </c>
       <c r="W45">
-        <v>0.044891</v>
+        <v>0.0410326</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y45">
-        <v>2.754658040904006</v>
+        <v>3.01368556012102</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5032,13 +5032,13 @@
         <v>0.44</v>
       </c>
       <c r="B46">
-        <v>0.1089919827280028</v>
+        <v>0.1080696027628221</v>
       </c>
       <c r="C46">
-        <v>40057.66565759065</v>
+        <v>40979.683199639</v>
       </c>
       <c r="D46">
-        <v>65141.82303302158</v>
+        <v>66063.84057506993</v>
       </c>
       <c r="E46">
         <v>17403.45424945153</v>
@@ -5065,37 +5065,37 @@
         <v>4533</v>
       </c>
       <c r="M46">
-        <v>1683.845521213572</v>
+        <v>1608.698696299908</v>
       </c>
       <c r="N46">
-        <v>2849.154478786429</v>
+        <v>2924.301303700092</v>
       </c>
       <c r="O46">
-        <v>735.0818555268986</v>
+        <v>754.4697363546237</v>
       </c>
       <c r="P46">
-        <v>2114.07262325953</v>
+        <v>2169.831567345468</v>
       </c>
       <c r="Q46">
-        <v>2285.07262325953</v>
+        <v>2340.831567345468</v>
       </c>
       <c r="R46">
         <v>0.7857142857142857</v>
       </c>
       <c r="S46">
-        <v>0.1593570405857192</v>
+        <v>0.1592840335050394</v>
       </c>
       <c r="T46">
         <v>2.620878371940863</v>
       </c>
       <c r="U46">
-        <v>0.0605</v>
+        <v>0.0578</v>
       </c>
       <c r="V46">
         <v>0.258</v>
       </c>
       <c r="W46">
-        <v>0.044891</v>
+        <v>0.0428876</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5103,7 +5103,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>2.692052176338007</v>
+        <v>2.817805478692896</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5114,13 +5114,13 @@
         <v>0.45</v>
       </c>
       <c r="B47">
-        <v>0.1087978155550962</v>
+        <v>0.1078555205780823</v>
       </c>
       <c r="C47">
-        <v>39625.89189932805</v>
+        <v>40575.04445244189</v>
       </c>
       <c r="D47">
-        <v>65342.59830601879</v>
+        <v>66291.75085913262</v>
       </c>
       <c r="E47">
         <v>18036.00328071133</v>
@@ -5147,37 +5147,37 @@
         <v>4533</v>
       </c>
       <c r="M47">
-        <v>1722.114737604789</v>
+        <v>1645.260030306724</v>
       </c>
       <c r="N47">
-        <v>2810.885262395211</v>
+        <v>2887.739969693276</v>
       </c>
       <c r="O47">
-        <v>725.2083976979644</v>
+        <v>745.0369121808651</v>
       </c>
       <c r="P47">
-        <v>2085.676864697246</v>
+        <v>2142.703057512411</v>
       </c>
       <c r="Q47">
-        <v>2256.676864697246</v>
+        <v>2313.703057512411</v>
       </c>
       <c r="R47">
         <v>0.8181818181818181</v>
       </c>
       <c r="S47">
-        <v>0.1610852101001748</v>
+        <v>0.1610110919601497</v>
       </c>
       <c r="T47">
         <v>2.660764248502302</v>
       </c>
       <c r="U47">
-        <v>0.0605</v>
+        <v>0.0578</v>
       </c>
       <c r="V47">
         <v>0.258</v>
       </c>
       <c r="W47">
-        <v>0.044891</v>
+        <v>0.0428876</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5185,7 +5185,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>2.632228794641606</v>
+        <v>2.755187579166387</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5196,13 +5196,13 @@
         <v>0.46</v>
       </c>
       <c r="B48">
-        <v>0.1086036483821896</v>
+        <v>0.1076414383933426</v>
       </c>
       <c r="C48">
-        <v>39195.35959655898</v>
+        <v>40171.98366115279</v>
       </c>
       <c r="D48">
-        <v>65544.61503450951</v>
+        <v>66521.23909910332</v>
       </c>
       <c r="E48">
         <v>18668.55231197112</v>
@@ -5229,37 +5229,37 @@
         <v>4533</v>
       </c>
       <c r="M48">
-        <v>1760.383953996007</v>
+        <v>1681.82136431354</v>
       </c>
       <c r="N48">
-        <v>2772.616046003994</v>
+        <v>2851.17863568646</v>
       </c>
       <c r="O48">
-        <v>715.3349398690303</v>
+        <v>735.6040880071066</v>
       </c>
       <c r="P48">
-        <v>2057.281106134963</v>
+        <v>2115.574547679353</v>
       </c>
       <c r="Q48">
-        <v>2228.281106134963</v>
+        <v>2286.574547679353</v>
       </c>
       <c r="R48">
         <v>0.8518518518518519</v>
       </c>
       <c r="S48">
-        <v>0.1628773858929436</v>
+        <v>0.162802115543227</v>
       </c>
       <c r="T48">
         <v>2.702127379751202</v>
       </c>
       <c r="U48">
-        <v>0.0605</v>
+        <v>0.0578</v>
       </c>
       <c r="V48">
         <v>0.258</v>
       </c>
       <c r="W48">
-        <v>0.044891</v>
+        <v>0.0428876</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5267,7 +5267,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>2.575006429540702</v>
+        <v>2.695292197010596</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5278,13 +5278,13 @@
         <v>0.47</v>
       </c>
       <c r="B49">
-        <v>0.108409481209283</v>
+        <v>0.1074273562086028</v>
       </c>
       <c r="C49">
-        <v>38766.08029944635</v>
+        <v>39770.51727036401</v>
       </c>
       <c r="D49">
-        <v>65747.88476865667</v>
+        <v>66752.32173957433</v>
       </c>
       <c r="E49">
         <v>19301.10134323092</v>
@@ -5311,37 +5311,37 @@
         <v>4533</v>
       </c>
       <c r="M49">
-        <v>1798.653170387224</v>
+        <v>1718.382698320357</v>
       </c>
       <c r="N49">
-        <v>2734.346829612776</v>
+        <v>2814.617301679643</v>
       </c>
       <c r="O49">
-        <v>705.4614820400961</v>
+        <v>726.171263833348</v>
       </c>
       <c r="P49">
-        <v>2028.88534757268</v>
+        <v>2088.446037846295</v>
       </c>
       <c r="Q49">
-        <v>2199.88534757268</v>
+        <v>2259.446037846295</v>
       </c>
       <c r="R49">
         <v>0.8867924528301887</v>
       </c>
       <c r="S49">
-        <v>0.1647371909609112</v>
+        <v>0.1646607249218922</v>
       </c>
       <c r="T49">
         <v>2.745051383877417</v>
       </c>
       <c r="U49">
-        <v>0.0605</v>
+        <v>0.0578</v>
       </c>
       <c r="V49">
         <v>0.258</v>
       </c>
       <c r="W49">
-        <v>0.044891</v>
+        <v>0.0428876</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5349,7 +5349,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>2.52021905869941</v>
+        <v>2.637945554521008</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5360,13 +5360,13 @@
         <v>0.48</v>
       </c>
       <c r="B50">
-        <v>0.1091769460363763</v>
+        <v>0.1072132740238631</v>
       </c>
       <c r="C50">
-        <v>37337.35549495238</v>
+        <v>39370.66195396634</v>
       </c>
       <c r="D50">
-        <v>64951.7089954225</v>
+        <v>66985.01545443645</v>
       </c>
       <c r="E50">
         <v>19933.65037449071</v>
@@ -5393,45 +5393,45 @@
         <v>4533</v>
       </c>
       <c r="M50">
-        <v>1918.900741229711</v>
+        <v>1754.944032327173</v>
       </c>
       <c r="N50">
-        <v>2614.099258770289</v>
+        <v>2778.055967672827</v>
       </c>
       <c r="O50">
-        <v>674.4376087627345</v>
+        <v>716.7384396595894</v>
       </c>
       <c r="P50">
-        <v>1939.661650007554</v>
+        <v>2061.317528013238</v>
       </c>
       <c r="Q50">
-        <v>2110.661650007554</v>
+        <v>2232.317528013238</v>
       </c>
       <c r="R50">
         <v>0.923076923076923</v>
       </c>
       <c r="S50">
-        <v>0.1666685269930314</v>
+        <v>0.1665908192766598</v>
       </c>
       <c r="T50">
         <v>2.789626311239257</v>
       </c>
       <c r="U50">
-        <v>0.06320000000000001</v>
+        <v>0.0578</v>
       </c>
       <c r="V50">
         <v>0.258</v>
       </c>
       <c r="W50">
-        <v>0.0468944</v>
+        <v>0.0428876</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y50">
-        <v>2.362289983324028</v>
+        <v>2.582988355468487</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5442,13 +5442,13 @@
         <v>0.49</v>
       </c>
       <c r="B51">
-        <v>0.1090028128634697</v>
+        <v>0.1069991918391234</v>
       </c>
       <c r="C51">
-        <v>36883.75810620116</v>
+        <v>38972.43461915976</v>
       </c>
       <c r="D51">
-        <v>65130.66063793107</v>
+        <v>67219.33715088967</v>
       </c>
       <c r="E51">
         <v>20566.1994057505</v>
@@ -5475,45 +5475,45 @@
         <v>4533</v>
       </c>
       <c r="M51">
-        <v>1958.87784000533</v>
+        <v>1791.505366333989</v>
       </c>
       <c r="N51">
-        <v>2574.12215999467</v>
+        <v>2741.494633666011</v>
       </c>
       <c r="O51">
-        <v>664.1235172786248</v>
+        <v>707.3056154858309</v>
       </c>
       <c r="P51">
-        <v>1909.998642716045</v>
+        <v>2034.18901818018</v>
       </c>
       <c r="Q51">
-        <v>2080.998642716045</v>
+        <v>2205.18901818018</v>
       </c>
       <c r="R51">
         <v>0.9607843137254901</v>
       </c>
       <c r="S51">
-        <v>0.1686756016930779</v>
+        <v>0.1685966036061243</v>
       </c>
       <c r="T51">
         <v>2.835949274968228</v>
       </c>
       <c r="U51">
-        <v>0.06320000000000001</v>
+        <v>0.0578</v>
       </c>
       <c r="V51">
         <v>0.258</v>
       </c>
       <c r="W51">
-        <v>0.0468944</v>
+        <v>0.0428876</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y51">
-        <v>2.314079983664354</v>
+        <v>2.530274307397702</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5524,13 +5524,13 @@
         <v>0.5</v>
       </c>
       <c r="B52">
-        <v>0.1088286796905631</v>
+        <v>0.1080836096543837</v>
       </c>
       <c r="C52">
-        <v>36431.14951865789</v>
+        <v>37169.53198859987</v>
       </c>
       <c r="D52">
-        <v>65310.60108164758</v>
+        <v>66048.98355158957</v>
       </c>
       <c r="E52">
         <v>21198.7484370103</v>
@@ -5557,37 +5557,37 @@
         <v>4533</v>
       </c>
       <c r="M52">
-        <v>1998.854938780949</v>
+        <v>1938.762780811269</v>
       </c>
       <c r="N52">
-        <v>2534.145061219051</v>
+        <v>2594.237219188732</v>
       </c>
       <c r="O52">
-        <v>653.8094257945152</v>
+        <v>669.3132025506927</v>
       </c>
       <c r="P52">
-        <v>1880.335635424536</v>
+        <v>1924.924016638039</v>
       </c>
       <c r="Q52">
-        <v>2051.335635424536</v>
+        <v>2095.924016638039</v>
       </c>
       <c r="R52">
         <v>1</v>
       </c>
       <c r="S52">
-        <v>0.1707629593811263</v>
+        <v>0.1706826193087673</v>
       </c>
       <c r="T52">
         <v>2.884125157246358</v>
       </c>
       <c r="U52">
-        <v>0.06320000000000001</v>
+        <v>0.0613</v>
       </c>
       <c r="V52">
         <v>0.258</v>
       </c>
       <c r="W52">
-        <v>0.0468944</v>
+        <v>0.0454846</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>2.267798383991067</v>
+        <v>2.338089035370889</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5606,13 +5606,13 @@
         <v>0.51</v>
       </c>
       <c r="B53">
-        <v>0.1104331205176565</v>
+        <v>0.1078954974696439</v>
       </c>
       <c r="C53">
-        <v>34177.34200601657</v>
+        <v>36737.07183820946</v>
       </c>
       <c r="D53">
-        <v>63689.34260026606</v>
+        <v>66249.07243245895</v>
       </c>
       <c r="E53">
         <v>21831.29746827009</v>
@@ -5639,45 +5639,45 @@
         <v>4533</v>
       </c>
       <c r="M53">
-        <v>2190.454040349541</v>
+        <v>1977.538036427494</v>
       </c>
       <c r="N53">
-        <v>2342.545959650459</v>
+        <v>2555.461963572506</v>
       </c>
       <c r="O53">
-        <v>604.3768575898185</v>
+        <v>659.3091866017065</v>
       </c>
       <c r="P53">
-        <v>1738.169102060641</v>
+        <v>1896.152776970799</v>
       </c>
       <c r="Q53">
-        <v>1909.169102060641</v>
+        <v>2067.152776970799</v>
       </c>
       <c r="R53">
         <v>1.040816326530612</v>
       </c>
       <c r="S53">
-        <v>0.1729355153421562</v>
+        <v>0.1728537785094774</v>
       </c>
       <c r="T53">
         <v>2.934267402066452</v>
       </c>
       <c r="U53">
-        <v>0.0679</v>
+        <v>0.0613</v>
       </c>
       <c r="V53">
         <v>0.258</v>
       </c>
       <c r="W53">
-        <v>0.0503818</v>
+        <v>0.0454846</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y53">
-        <v>2.069433969624238</v>
+        <v>2.2922441523244</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5688,13 +5688,13 @@
         <v>0.52</v>
       </c>
       <c r="B54">
-        <v>0.1102938613447499</v>
+        <v>0.1087877372849042</v>
       </c>
       <c r="C54">
-        <v>33682.31498054999</v>
+        <v>35166.08522058367</v>
       </c>
       <c r="D54">
-        <v>63826.86460605927</v>
+        <v>65310.63484609296</v>
       </c>
       <c r="E54">
         <v>22463.84649952989</v>
@@ -5721,37 +5721,37 @@
         <v>4533</v>
       </c>
       <c r="M54">
-        <v>2233.404119572081</v>
+        <v>2108.412430995145</v>
       </c>
       <c r="N54">
-        <v>2299.595880427919</v>
+        <v>2424.587569004855</v>
       </c>
       <c r="O54">
-        <v>593.2957371504032</v>
+        <v>625.5435928032525</v>
       </c>
       <c r="P54">
-        <v>1706.300143277516</v>
+        <v>1799.043976201602</v>
       </c>
       <c r="Q54">
-        <v>1877.300143277516</v>
+        <v>1970.043976201602</v>
       </c>
       <c r="R54">
         <v>1.083333333333333</v>
       </c>
       <c r="S54">
-        <v>0.175198594468229</v>
+        <v>0.1751154026768837</v>
       </c>
       <c r="T54">
         <v>2.986498907087384</v>
       </c>
       <c r="U54">
-        <v>0.0679</v>
+        <v>0.0641</v>
       </c>
       <c r="V54">
         <v>0.258</v>
       </c>
       <c r="W54">
-        <v>0.0503818</v>
+        <v>0.04756220000000001</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5759,7 +5759,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>2.029637162516079</v>
+        <v>2.149958866378187</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5770,13 +5770,13 @@
         <v>0.53</v>
       </c>
       <c r="B55">
-        <v>0.1138119201718433</v>
+        <v>0.1086204011001645</v>
       </c>
       <c r="C55">
-        <v>29748.18787495131</v>
+        <v>34707.50566845291</v>
       </c>
       <c r="D55">
-        <v>60525.2865317204</v>
+        <v>65484.604325222</v>
       </c>
       <c r="E55">
         <v>23096.39553078968</v>
@@ -5803,45 +5803,45 @@
         <v>4533</v>
       </c>
       <c r="M55">
-        <v>2588.137616302573</v>
+        <v>2148.958823898899</v>
       </c>
       <c r="N55">
-        <v>1944.862383697427</v>
+        <v>2384.041176101101</v>
       </c>
       <c r="O55">
-        <v>501.7744949939362</v>
+        <v>615.0826234340842</v>
       </c>
       <c r="P55">
-        <v>1443.087888703491</v>
+        <v>1768.958552667017</v>
       </c>
       <c r="Q55">
-        <v>1614.087888703491</v>
+        <v>1939.958552667017</v>
       </c>
       <c r="R55">
         <v>1.127659574468085</v>
       </c>
       <c r="S55">
-        <v>0.1775579748337092</v>
+        <v>0.1774732661705627</v>
       </c>
       <c r="T55">
         <v>3.040953029343248</v>
       </c>
       <c r="U55">
-        <v>0.07719999999999999</v>
+        <v>0.0641</v>
       </c>
       <c r="V55">
         <v>0.258</v>
       </c>
       <c r="W55">
-        <v>0.05728239999999999</v>
+        <v>0.04756220000000001</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y55">
-        <v>1.751452461973745</v>
+        <v>2.109393604748409</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5852,13 +5852,13 @@
         <v>0.54</v>
       </c>
       <c r="B56">
-        <v>0.1156248629989367</v>
+        <v>0.1084530649154247</v>
       </c>
       <c r="C56">
-        <v>27544.15156304874</v>
+        <v>34249.85540490332</v>
       </c>
       <c r="D56">
-        <v>58953.79925107762</v>
+        <v>65659.50309293219</v>
       </c>
       <c r="E56">
         <v>23728.94456204947</v>
@@ -5885,45 +5885,45 @@
         <v>4533</v>
       </c>
       <c r="M56">
-        <v>2797.511345649565</v>
+        <v>2189.505216802651</v>
       </c>
       <c r="N56">
-        <v>1735.488654350435</v>
+        <v>2343.494783197349</v>
       </c>
       <c r="O56">
-        <v>447.7560728224122</v>
+        <v>604.6216540649161</v>
       </c>
       <c r="P56">
-        <v>1287.732581528023</v>
+        <v>1738.873129132433</v>
       </c>
       <c r="Q56">
-        <v>1458.732581528023</v>
+        <v>1909.873129132433</v>
       </c>
       <c r="R56">
         <v>1.173913043478261</v>
       </c>
       <c r="S56">
-        <v>0.1800199369542103</v>
+        <v>0.1799336454683146</v>
       </c>
       <c r="T56">
         <v>3.097774722131976</v>
       </c>
       <c r="U56">
-        <v>0.0819</v>
+        <v>0.0641</v>
       </c>
       <c r="V56">
         <v>0.258</v>
       </c>
       <c r="W56">
-        <v>0.0607698</v>
+        <v>0.04756220000000001</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y56">
-        <v>1.620368763490203</v>
+        <v>2.070330760216032</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5934,13 +5934,13 @@
         <v>0.55</v>
       </c>
       <c r="B57">
-        <v>0.1155894838260301</v>
+        <v>0.108285728730685</v>
       </c>
       <c r="C57">
-        <v>26941.48864847673</v>
+        <v>33793.14189581265</v>
       </c>
       <c r="D57">
-        <v>58983.6853677654</v>
+        <v>65835.33861510133</v>
       </c>
       <c r="E57">
         <v>24361.49359330927</v>
@@ -5967,45 +5967,45 @@
         <v>4533</v>
       </c>
       <c r="M57">
-        <v>2849.317111309742</v>
+        <v>2230.051609706404</v>
       </c>
       <c r="N57">
-        <v>1683.682888690258</v>
+        <v>2302.948390293596</v>
       </c>
       <c r="O57">
-        <v>434.3901852820865</v>
+        <v>594.1606846957477</v>
       </c>
       <c r="P57">
-        <v>1249.292703408171</v>
+        <v>1708.787705597848</v>
       </c>
       <c r="Q57">
-        <v>1420.292703408171</v>
+        <v>1879.787705597848</v>
       </c>
       <c r="R57">
         <v>1.222222222222223</v>
       </c>
       <c r="S57">
-        <v>0.1825913196134002</v>
+        <v>0.1825033749570777</v>
       </c>
       <c r="T57">
         <v>3.157121823489093</v>
       </c>
       <c r="U57">
-        <v>0.0819</v>
+        <v>0.0641</v>
       </c>
       <c r="V57">
         <v>0.258</v>
       </c>
       <c r="W57">
-        <v>0.0607698</v>
+        <v>0.04756220000000001</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y57">
-        <v>1.590907513244927</v>
+        <v>2.032688382757558</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6016,13 +6016,13 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1155541046531235</v>
+        <v>0.1113594485459452</v>
       </c>
       <c r="C58">
-        <v>26338.8560502881</v>
+        <v>30073.93809039337</v>
       </c>
       <c r="D58">
-        <v>59013.60180083656</v>
+        <v>62748.68384094183</v>
       </c>
       <c r="E58">
         <v>24994.04262456906</v>
@@ -6049,45 +6049,45 @@
         <v>4533</v>
       </c>
       <c r="M58">
-        <v>2901.122876969919</v>
+        <v>2546.895419464435</v>
       </c>
       <c r="N58">
-        <v>1631.877123030081</v>
+        <v>1986.104580535565</v>
       </c>
       <c r="O58">
-        <v>421.0242977417608</v>
+        <v>512.4149817781758</v>
       </c>
       <c r="P58">
-        <v>1210.85282528832</v>
+        <v>1473.689598757389</v>
       </c>
       <c r="Q58">
-        <v>1381.85282528832</v>
+        <v>1644.689598757389</v>
       </c>
       <c r="R58">
         <v>1.272727272727273</v>
       </c>
       <c r="S58">
-        <v>0.1852795833025534</v>
+        <v>0.1851899103316937</v>
       </c>
       <c r="T58">
         <v>3.219166520362442</v>
       </c>
       <c r="U58">
-        <v>0.0819</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V58">
         <v>0.258</v>
       </c>
       <c r="W58">
-        <v>0.0607698</v>
+        <v>0.0533498</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y58">
-        <v>1.56249845050841</v>
+        <v>1.779813951274531</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6098,13 +6098,13 @@
         <v>0.5700000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1155187254802169</v>
+        <v>0.1128994543612055</v>
       </c>
       <c r="C59">
-        <v>25736.25381463554</v>
+        <v>28001.23818257371</v>
       </c>
       <c r="D59">
-        <v>59043.5485964438</v>
+        <v>61308.53296438197</v>
       </c>
       <c r="E59">
         <v>25626.59165582886</v>
@@ -6131,37 +6131,37 @@
         <v>4533</v>
       </c>
       <c r="M59">
-        <v>2952.928642630096</v>
+        <v>2732.991344461067</v>
       </c>
       <c r="N59">
-        <v>1580.071357369904</v>
+        <v>1800.008655538933</v>
       </c>
       <c r="O59">
-        <v>407.6584102014351</v>
+        <v>464.4022331290448</v>
       </c>
       <c r="P59">
-        <v>1172.412947168468</v>
+        <v>1335.606422409889</v>
       </c>
       <c r="Q59">
-        <v>1343.412947168468</v>
+        <v>1506.606422409889</v>
       </c>
       <c r="R59">
         <v>1.325581395348838</v>
       </c>
       <c r="S59">
-        <v>0.1880928825121324</v>
+        <v>0.1880014008400128</v>
       </c>
       <c r="T59">
         <v>3.284097017090365</v>
       </c>
       <c r="U59">
-        <v>0.0819</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V59">
         <v>0.258</v>
       </c>
       <c r="W59">
-        <v>0.0607698</v>
+        <v>0.0562436</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6169,7 +6169,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>1.535086196990719</v>
+        <v>1.658622157434563</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6180,13 +6180,13 @@
         <v>0.58</v>
       </c>
       <c r="B60">
-        <v>0.1154833463073103</v>
+        <v>0.1128189321764658</v>
       </c>
       <c r="C60">
-        <v>25133.68198776547</v>
+        <v>27442.35038191188</v>
       </c>
       <c r="D60">
-        <v>59073.52580083352</v>
+        <v>61382.19419497993</v>
       </c>
       <c r="E60">
         <v>26259.14068708865</v>
@@ -6213,37 +6213,37 @@
         <v>4533</v>
       </c>
       <c r="M60">
-        <v>3004.734408290273</v>
+        <v>2780.938561030559</v>
       </c>
       <c r="N60">
-        <v>1528.265591709727</v>
+        <v>1752.061438969441</v>
       </c>
       <c r="O60">
-        <v>394.2925226611095</v>
+        <v>452.0318512541159</v>
       </c>
       <c r="P60">
-        <v>1133.973069048617</v>
+        <v>1300.029587715326</v>
       </c>
       <c r="Q60">
-        <v>1304.973069048617</v>
+        <v>1471.029587715326</v>
       </c>
       <c r="R60">
         <v>1.380952380952381</v>
       </c>
       <c r="S60">
-        <v>0.1910401483507388</v>
+        <v>0.190946771848728</v>
       </c>
       <c r="T60">
         <v>3.352119442233903</v>
       </c>
       <c r="U60">
-        <v>0.0819</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V60">
         <v>0.258</v>
       </c>
       <c r="W60">
-        <v>0.0607698</v>
+        <v>0.0562436</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6251,7 +6251,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>1.508619193594327</v>
+        <v>1.630025223685691</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6262,13 +6262,13 @@
         <v>0.59</v>
       </c>
       <c r="B61">
-        <v>0.1391232087902592</v>
+        <v>0.112738409991726</v>
       </c>
       <c r="C61">
-        <v>9537.116562114395</v>
+        <v>26883.63979977735</v>
       </c>
       <c r="D61">
-        <v>44109.50940644224</v>
+        <v>61456.03264410519</v>
       </c>
       <c r="E61">
         <v>26891.68971834844</v>
@@ -6295,45 +6295,45 @@
         <v>4533</v>
       </c>
       <c r="M61">
-        <v>4885.239423322514</v>
+        <v>2828.88577760005</v>
       </c>
       <c r="N61">
-        <v>-352.2394233225141</v>
+        <v>1704.11422239995</v>
       </c>
       <c r="O61">
-        <v>-90.87777121720863</v>
+        <v>439.661469379187</v>
       </c>
       <c r="P61">
-        <v>-261.3616521053054</v>
+        <v>1264.452753020762</v>
       </c>
       <c r="Q61">
-        <v>-90.36165210530544</v>
+        <v>1435.452753020762</v>
       </c>
       <c r="R61">
         <v>1.439024390243902</v>
       </c>
       <c r="S61">
-        <v>0.1960515011103942</v>
+        <v>0.1940358194920147</v>
       </c>
       <c r="T61">
-        <v>3.467780664067458</v>
+        <v>3.423460034457614</v>
       </c>
       <c r="U61">
-        <v>0.1309</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V61">
-        <v>0.2393974785384415</v>
+        <v>0.258</v>
       </c>
       <c r="W61">
-        <v>0.09956287005931799</v>
+        <v>0.0562436</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y61">
-        <v>0.9278972036373703</v>
+        <v>1.602397677521527</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6344,13 +6344,13 @@
         <v>0.6</v>
       </c>
       <c r="B62">
-        <v>0.1399742087902592</v>
+        <v>0.1126578878069863</v>
       </c>
       <c r="C62">
-        <v>8505.974402363507</v>
+        <v>26325.10707648446</v>
       </c>
       <c r="D62">
-        <v>43710.91627795115</v>
+        <v>61530.04895207209</v>
       </c>
       <c r="E62">
         <v>27524.23874960824</v>
@@ -6377,45 +6377,45 @@
         <v>4533</v>
       </c>
       <c r="M62">
-        <v>4968.040091514422</v>
+        <v>2876.832994169543</v>
       </c>
       <c r="N62">
-        <v>-435.0400915144219</v>
+        <v>1656.167005830457</v>
       </c>
       <c r="O62">
-        <v>-112.2403436107208</v>
+        <v>427.2910875042579</v>
       </c>
       <c r="P62">
-        <v>-322.799747903701</v>
+        <v>1228.875918326199</v>
       </c>
       <c r="Q62">
-        <v>-151.799747903701</v>
+        <v>1399.875918326199</v>
       </c>
       <c r="R62">
         <v>1.5</v>
       </c>
       <c r="S62">
-        <v>0.199807788638154</v>
+        <v>0.1972793195174657</v>
       </c>
       <c r="T62">
-        <v>3.554475180669144</v>
+        <v>3.49836765629251</v>
       </c>
       <c r="U62">
-        <v>0.1309</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V62">
-        <v>0.2354075205628008</v>
+        <v>0.258</v>
       </c>
       <c r="W62">
-        <v>0.1000851555583294</v>
+        <v>0.0562436</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y62">
-        <v>0.9124322502434139</v>
+        <v>1.575691049562835</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6426,13 +6426,13 @@
         <v>0.61</v>
       </c>
       <c r="B63">
-        <v>0.1408252087902592</v>
+        <v>0.1125773656222465</v>
       </c>
       <c r="C63">
-        <v>7481.971458756721</v>
+        <v>25766.75285543613</v>
       </c>
       <c r="D63">
-        <v>43319.46236560415</v>
+        <v>61604.24376228356</v>
       </c>
       <c r="E63">
         <v>28156.78778086803</v>
@@ -6459,45 +6459,45 @@
         <v>4533</v>
       </c>
       <c r="M63">
-        <v>5050.840759706328</v>
+        <v>2924.780210739035</v>
       </c>
       <c r="N63">
-        <v>-517.8407597063278</v>
+        <v>1608.219789260965</v>
       </c>
       <c r="O63">
-        <v>-133.6029160042326</v>
+        <v>414.9207056293289</v>
       </c>
       <c r="P63">
-        <v>-384.2378437020952</v>
+        <v>1193.299083631636</v>
       </c>
       <c r="Q63">
-        <v>-213.2378437020952</v>
+        <v>1364.299083631636</v>
       </c>
       <c r="R63">
         <v>1.564102564102564</v>
       </c>
       <c r="S63">
-        <v>0.2037567062955426</v>
+        <v>0.2006891528775553</v>
       </c>
       <c r="T63">
-        <v>3.645615569917071</v>
+        <v>3.577116694631761</v>
       </c>
       <c r="U63">
-        <v>0.1309</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V63">
-        <v>0.2315483808814435</v>
+        <v>0.258</v>
       </c>
       <c r="W63">
-        <v>0.100590316942619</v>
+        <v>0.0562436</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y63">
-        <v>0.8974743445017188</v>
+        <v>1.549860048750329</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6508,13 +6508,13 @@
         <v>0.62</v>
       </c>
       <c r="B64">
-        <v>0.1416762087902592</v>
+        <v>0.1124968434375068</v>
       </c>
       <c r="C64">
-        <v>6464.91762762759</v>
+        <v>25208.57778314226</v>
       </c>
       <c r="D64">
-        <v>42934.95756573482</v>
+        <v>61678.61772124949</v>
       </c>
       <c r="E64">
         <v>28789.33681212783</v>
@@ -6541,45 +6541,45 @@
         <v>4533</v>
       </c>
       <c r="M64">
-        <v>5133.641427898236</v>
+        <v>2972.727427308528</v>
       </c>
       <c r="N64">
-        <v>-600.6414278982356</v>
+        <v>1560.272572691472</v>
       </c>
       <c r="O64">
-        <v>-154.9654883977448</v>
+        <v>402.5503237543998</v>
       </c>
       <c r="P64">
-        <v>-445.6759395004908</v>
+        <v>1157.722248937072</v>
       </c>
       <c r="Q64">
-        <v>-274.6759395004908</v>
+        <v>1328.722248937072</v>
       </c>
       <c r="R64">
         <v>1.631578947368421</v>
       </c>
       <c r="S64">
-        <v>0.2079134617243726</v>
+        <v>0.2042784511513337</v>
       </c>
       <c r="T64">
-        <v>3.741552821756994</v>
+        <v>3.660010419199393</v>
       </c>
       <c r="U64">
-        <v>0.1309</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V64">
-        <v>0.227813729576904</v>
+        <v>0.258</v>
       </c>
       <c r="W64">
-        <v>0.1010791827983833</v>
+        <v>0.0562436</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y64">
-        <v>0.8829989518484651</v>
+        <v>1.52486230602855</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6590,13 +6590,13 @@
         <v>0.63</v>
       </c>
       <c r="B65">
-        <v>0.1425272087902592</v>
+        <v>0.1124163212527671</v>
       </c>
       <c r="C65">
-        <v>5454.629495390873</v>
+        <v>24650.58250923869</v>
       </c>
       <c r="D65">
-        <v>42557.2184647579</v>
+        <v>61753.17147860571</v>
       </c>
       <c r="E65">
         <v>29421.88584338762</v>
@@ -6623,45 +6623,45 @@
         <v>4533</v>
       </c>
       <c r="M65">
-        <v>5216.442096090143</v>
+        <v>3020.674643878021</v>
       </c>
       <c r="N65">
-        <v>-683.4420960901434</v>
+        <v>1512.325356121979</v>
       </c>
       <c r="O65">
-        <v>-176.328060791257</v>
+        <v>390.1799418794707</v>
       </c>
       <c r="P65">
-        <v>-507.1140352988864</v>
+        <v>1122.145414242509</v>
       </c>
       <c r="Q65">
-        <v>-336.1140352988864</v>
+        <v>1293.145414242509</v>
       </c>
       <c r="R65">
         <v>1.702702702702703</v>
       </c>
       <c r="S65">
-        <v>0.2122949066358422</v>
+        <v>0.2080617655480191</v>
       </c>
       <c r="T65">
-        <v>3.84267587099367</v>
+        <v>3.747384885635546</v>
       </c>
       <c r="U65">
-        <v>0.1309</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V65">
-        <v>0.2241976386312388</v>
+        <v>0.258</v>
       </c>
       <c r="W65">
-        <v>0.1015525291031708</v>
+        <v>0.0562436</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y65">
-        <v>0.8689830954699179</v>
+        <v>1.500658142440795</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6672,13 +6672,13 @@
         <v>0.64</v>
       </c>
       <c r="B66">
-        <v>0.1433782087902592</v>
+        <v>0.1344164667207233</v>
       </c>
       <c r="C66">
-        <v>4450.930046814487</v>
+        <v>8687.036814361512</v>
       </c>
       <c r="D66">
-        <v>42186.0680474413</v>
+        <v>46422.17481498833</v>
       </c>
       <c r="E66">
         <v>30054.43487464741</v>
@@ -6705,37 +6705,37 @@
         <v>4533</v>
       </c>
       <c r="M66">
-        <v>5299.242764282049</v>
+        <v>4801.300166874341</v>
       </c>
       <c r="N66">
-        <v>-766.2427642820494</v>
+        <v>-268.3001668743409</v>
       </c>
       <c r="O66">
-        <v>-197.6906331847688</v>
+        <v>-69.22144305357996</v>
       </c>
       <c r="P66">
-        <v>-568.5521310972806</v>
+        <v>-199.078723820761</v>
       </c>
       <c r="Q66">
-        <v>-397.5521310972806</v>
+        <v>-28.07872382076096</v>
       </c>
       <c r="R66">
         <v>1.777777777777778</v>
       </c>
       <c r="S66">
-        <v>0.2169197651535045</v>
+        <v>0.2138927038492379</v>
       </c>
       <c r="T66">
-        <v>3.949416867410161</v>
+        <v>3.882048587742215</v>
       </c>
       <c r="U66">
-        <v>0.1309</v>
+        <v>0.1186</v>
       </c>
       <c r="V66">
-        <v>0.2206945505276258</v>
+        <v>0.2435827711978601</v>
       </c>
       <c r="W66">
-        <v>0.1020110833359338</v>
+        <v>0.08971108333593381</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6743,7 +6743,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.8554052346032006</v>
+        <v>0.94411926820876</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6754,13 +6754,13 @@
         <v>0.65</v>
       </c>
       <c r="B67">
-        <v>0.1442292087902592</v>
+        <v>0.1351444667207233</v>
       </c>
       <c r="C67">
-        <v>3453.648388424976</v>
+        <v>7676.228843228571</v>
       </c>
       <c r="D67">
-        <v>41821.33542031159</v>
+        <v>46043.91587511518</v>
       </c>
       <c r="E67">
         <v>30686.98390590721</v>
@@ -6787,37 +6787,37 @@
         <v>4533</v>
       </c>
       <c r="M67">
-        <v>5382.043432473957</v>
+        <v>4876.320481981753</v>
       </c>
       <c r="N67">
-        <v>-849.0434324739572</v>
+        <v>-343.3204819817529</v>
       </c>
       <c r="O67">
-        <v>-219.053205578281</v>
+        <v>-88.57668435129224</v>
       </c>
       <c r="P67">
-        <v>-629.9902268956762</v>
+        <v>-254.7437976304606</v>
       </c>
       <c r="Q67">
-        <v>-458.9902268956762</v>
+        <v>-83.74379763046065</v>
       </c>
       <c r="R67">
         <v>1.857142857142857</v>
       </c>
       <c r="S67">
-        <v>0.2218089013007474</v>
+        <v>0.2186953525306447</v>
       </c>
       <c r="T67">
-        <v>4.062257349336165</v>
+        <v>3.992964261677706</v>
       </c>
       <c r="U67">
-        <v>0.1309</v>
+        <v>0.1186</v>
       </c>
       <c r="V67">
-        <v>0.2172992497502776</v>
+        <v>0.2398353439486622</v>
       </c>
       <c r="W67">
-        <v>0.1024555282076886</v>
+        <v>0.09015552820768867</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6825,7 +6825,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.8422451540708435</v>
+        <v>0.9295943563901636</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6836,13 +6836,13 @@
         <v>0.66</v>
       </c>
       <c r="B68">
-        <v>0.1450802087902592</v>
+        <v>0.1358724667207233</v>
       </c>
       <c r="C68">
-        <v>2462.61948613797</v>
+        <v>6671.535337886424</v>
       </c>
       <c r="D68">
-        <v>41462.85554928437</v>
+        <v>45671.77140103283</v>
       </c>
       <c r="E68">
         <v>31319.532937167</v>
@@ -6869,37 +6869,37 @@
         <v>4533</v>
       </c>
       <c r="M68">
-        <v>5464.844100665864</v>
+        <v>4951.340797089164</v>
       </c>
       <c r="N68">
-        <v>-931.8441006658641</v>
+        <v>-418.340797089164</v>
       </c>
       <c r="O68">
-        <v>-240.4157779717929</v>
+        <v>-107.9319256490043</v>
       </c>
       <c r="P68">
-        <v>-691.4283226940711</v>
+        <v>-310.4088714401597</v>
       </c>
       <c r="Q68">
-        <v>-520.4283226940711</v>
+        <v>-139.4088714401597</v>
       </c>
       <c r="R68">
         <v>1.941176470588236</v>
       </c>
       <c r="S68">
-        <v>0.2269856336919459</v>
+        <v>0.2237805099580166</v>
       </c>
       <c r="T68">
-        <v>4.181735506669582</v>
+        <v>4.110404387021169</v>
       </c>
       <c r="U68">
-        <v>0.1309</v>
+        <v>0.1186</v>
       </c>
       <c r="V68">
-        <v>0.2140068368752735</v>
+        <v>0.2362014751009552</v>
       </c>
       <c r="W68">
-        <v>0.1028865050530267</v>
+        <v>0.09058650505302672</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.8294838638576491</v>
+        <v>0.9155095934145552</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6918,13 +6918,13 @@
         <v>0.67</v>
       </c>
       <c r="B69">
-        <v>0.1459312087902592</v>
+        <v>0.1366004667207233</v>
       </c>
       <c r="C69">
-        <v>1477.683916268121</v>
+        <v>5672.809228680351</v>
       </c>
       <c r="D69">
-        <v>41110.46901067432</v>
+        <v>45305.59432308655</v>
       </c>
       <c r="E69">
         <v>31952.0819684268</v>
@@ -6951,37 +6951,37 @@
         <v>4533</v>
       </c>
       <c r="M69">
-        <v>5547.644768857771</v>
+        <v>5026.361112196576</v>
       </c>
       <c r="N69">
-        <v>-1014.644768857771</v>
+        <v>-493.361112196576</v>
       </c>
       <c r="O69">
-        <v>-261.7783503653049</v>
+        <v>-127.2871669467166</v>
       </c>
       <c r="P69">
-        <v>-752.866418492466</v>
+        <v>-366.0739452498594</v>
       </c>
       <c r="Q69">
-        <v>-581.866418492466</v>
+        <v>-195.0739452498594</v>
       </c>
       <c r="R69">
         <v>2.030303030303031</v>
       </c>
       <c r="S69">
-        <v>0.2324761074401867</v>
+        <v>0.2291738587446232</v>
       </c>
       <c r="T69">
-        <v>4.308454764447449</v>
+        <v>4.23496209571878</v>
       </c>
       <c r="U69">
-        <v>0.1309</v>
+        <v>0.1186</v>
       </c>
       <c r="V69">
-        <v>0.2108127049816127</v>
+        <v>0.2326760799501947</v>
       </c>
       <c r="W69">
-        <v>0.1033046169179069</v>
+        <v>0.09100461691790691</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6989,7 +6989,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.8171035076806692</v>
+        <v>0.9018452711247856</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7000,13 +7000,13 @@
         <v>0.68</v>
       </c>
       <c r="B70">
-        <v>0.1467822087902592</v>
+        <v>0.1373284667207233</v>
       </c>
       <c r="C70">
-        <v>498.6876291283552</v>
+        <v>4679.908125011818</v>
       </c>
       <c r="D70">
-        <v>40764.02175479435</v>
+        <v>44945.24225067781</v>
       </c>
       <c r="E70">
         <v>32584.63099968659</v>
@@ -7033,37 +7033,37 @@
         <v>4533</v>
       </c>
       <c r="M70">
-        <v>5630.445437049678</v>
+        <v>5101.381427303987</v>
       </c>
       <c r="N70">
-        <v>-1097.445437049678</v>
+        <v>-568.381427303987</v>
       </c>
       <c r="O70">
-        <v>-283.1409227588169</v>
+        <v>-146.6424082444287</v>
       </c>
       <c r="P70">
-        <v>-814.3045142908609</v>
+        <v>-421.7390190595584</v>
       </c>
       <c r="Q70">
-        <v>-643.3045142908609</v>
+        <v>-250.7390190595584</v>
       </c>
       <c r="R70">
         <v>2.125</v>
       </c>
       <c r="S70">
-        <v>0.2383097357976925</v>
+        <v>0.2349042918303927</v>
       </c>
       <c r="T70">
-        <v>4.443093975836431</v>
+        <v>4.367304661209992</v>
       </c>
       <c r="U70">
-        <v>0.1309</v>
+        <v>0.1186</v>
       </c>
       <c r="V70">
-        <v>0.2077125181436478</v>
+        <v>0.2292543728921036</v>
       </c>
       <c r="W70">
-        <v>0.1037104313749965</v>
+        <v>0.09141043137499652</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.8050872796265418</v>
+        <v>0.8885828406670683</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7082,13 +7082,13 @@
         <v>0.6900000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2102004262256885</v>
+        <v>0.1380564667207232</v>
       </c>
       <c r="C71">
-        <v>-15858.76950935975</v>
+        <v>3692.694130725198</v>
       </c>
       <c r="D71">
-        <v>25039.11364756604</v>
+        <v>44590.57728765099</v>
       </c>
       <c r="E71">
         <v>33217.18003094639</v>
@@ -7115,45 +7115,45 @@
         <v>4533</v>
       </c>
       <c r="M71">
-        <v>9418.781585264585</v>
+        <v>5176.401742411399</v>
       </c>
       <c r="N71">
-        <v>-4885.781585264585</v>
+        <v>-643.401742411399</v>
       </c>
       <c r="O71">
-        <v>-1260.531648998263</v>
+        <v>-165.9976495421409</v>
       </c>
       <c r="P71">
-        <v>-3625.249936266322</v>
+        <v>-477.4040928692581</v>
       </c>
       <c r="Q71">
-        <v>-3454.249936266322</v>
+        <v>-306.4040928692581</v>
       </c>
       <c r="R71">
         <v>2.225806451612904</v>
       </c>
       <c r="S71">
-        <v>0.2573784931957771</v>
+        <v>0.2410044302765343</v>
       </c>
       <c r="T71">
-        <v>4.883197853030217</v>
+        <v>4.508185456732894</v>
       </c>
       <c r="U71">
-        <v>0.2158</v>
+        <v>0.1186</v>
       </c>
       <c r="V71">
-        <v>0.1241682896468978</v>
+        <v>0.2259318457487398</v>
       </c>
       <c r="W71">
-        <v>0.1890044830941995</v>
+        <v>0.09180448309419946</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y71">
-        <v>0.4812724404918518</v>
+        <v>0.8757048284834875</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7164,13 +7164,13 @@
         <v>0.7000000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2119004262256885</v>
+        <v>0.1387844667207233</v>
       </c>
       <c r="C72">
-        <v>-16747.58816116239</v>
+        <v>2711.033668166776</v>
       </c>
       <c r="D72">
-        <v>24782.84402702319</v>
+        <v>44241.46585635236</v>
       </c>
       <c r="E72">
         <v>33849.72906220618</v>
@@ -7197,45 +7197,45 @@
         <v>4533</v>
       </c>
       <c r="M72">
-        <v>9555.285666210451</v>
+        <v>5251.422057518811</v>
       </c>
       <c r="N72">
-        <v>-5022.285666210451</v>
+        <v>-718.422057518811</v>
       </c>
       <c r="O72">
-        <v>-1295.749701882296</v>
+        <v>-185.3528908398532</v>
       </c>
       <c r="P72">
-        <v>-3726.535964328155</v>
+        <v>-533.0691666789578</v>
       </c>
       <c r="Q72">
-        <v>-3555.535964328155</v>
+        <v>-362.0691666789578</v>
       </c>
       <c r="R72">
         <v>2.333333333333334</v>
       </c>
       <c r="S72">
-        <v>0.2644311096356363</v>
+        <v>0.2475112446190855</v>
       </c>
       <c r="T72">
-        <v>5.04597111479789</v>
+        <v>4.658458305290658</v>
       </c>
       <c r="U72">
-        <v>0.2158</v>
+        <v>0.1186</v>
       </c>
       <c r="V72">
-        <v>0.1223944569376563</v>
+        <v>0.2227042479523292</v>
       </c>
       <c r="W72">
-        <v>0.1893872761928538</v>
+        <v>0.09218727619285376</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y72">
-        <v>0.4743971199133967</v>
+        <v>0.8631947595051519</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7246,13 +7246,13 @@
         <v>0.71</v>
       </c>
       <c r="B73">
-        <v>0.2136004262256885</v>
+        <v>0.1395124667207233</v>
       </c>
       <c r="C73">
-        <v>-17631.21423551189</v>
+        <v>1734.797310444781</v>
       </c>
       <c r="D73">
-        <v>24531.76698393348</v>
+        <v>43897.77852989015</v>
       </c>
       <c r="E73">
         <v>34482.27809346597</v>
@@ -7279,45 +7279,45 @@
         <v>4533</v>
       </c>
       <c r="M73">
-        <v>9691.789747156312</v>
+        <v>5326.442372626221</v>
       </c>
       <c r="N73">
-        <v>-5158.789747156312</v>
+        <v>-793.4423726262212</v>
       </c>
       <c r="O73">
-        <v>-1330.967754766328</v>
+        <v>-204.7081321375651</v>
       </c>
       <c r="P73">
-        <v>-3827.821992389983</v>
+        <v>-588.7342404886562</v>
       </c>
       <c r="Q73">
-        <v>-3656.821992389983</v>
+        <v>-417.7342404886562</v>
       </c>
       <c r="R73">
         <v>2.448275862068965</v>
       </c>
       <c r="S73">
-        <v>0.2719701134161754</v>
+        <v>0.2544668047783643</v>
       </c>
       <c r="T73">
-        <v>5.219970118756438</v>
+        <v>4.819094798576542</v>
       </c>
       <c r="U73">
-        <v>0.2158</v>
+        <v>0.1186</v>
       </c>
       <c r="V73">
-        <v>0.1206705913469852</v>
+        <v>0.2195675684037049</v>
       </c>
       <c r="W73">
-        <v>0.1897592863873206</v>
+        <v>0.09255928638732061</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y73">
-        <v>0.4677154703371518</v>
+        <v>0.8510370868360655</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7328,13 +7328,13 @@
         <v>0.72</v>
       </c>
       <c r="B74">
-        <v>0.2153004262256885</v>
+        <v>0.1402404667207233</v>
       </c>
       <c r="C74">
-        <v>-18509.80396885911</v>
+        <v>763.8596214471472</v>
       </c>
       <c r="D74">
-        <v>24285.72628184605</v>
+        <v>43559.38987215231</v>
       </c>
       <c r="E74">
         <v>35114.82712472577</v>
@@ -7361,45 +7361,45 @@
         <v>4533</v>
       </c>
       <c r="M74">
-        <v>9828.293828102176</v>
+        <v>5401.462687733633</v>
       </c>
       <c r="N74">
-        <v>-5295.293828102176</v>
+        <v>-868.4626877336332</v>
       </c>
       <c r="O74">
-        <v>-1366.185807650362</v>
+        <v>-224.0633734352774</v>
       </c>
       <c r="P74">
-        <v>-3929.108020451815</v>
+        <v>-644.3993142983559</v>
       </c>
       <c r="Q74">
-        <v>-3758.108020451815</v>
+        <v>-473.3993142983559</v>
       </c>
       <c r="R74">
         <v>2.571428571428571</v>
       </c>
       <c r="S74">
-        <v>0.2800476174667531</v>
+        <v>0.2619191906633058</v>
       </c>
       <c r="T74">
-        <v>5.406397622997739</v>
+        <v>4.991205327097132</v>
       </c>
       <c r="U74">
-        <v>0.2158</v>
+        <v>0.1186</v>
       </c>
       <c r="V74">
-        <v>0.1189946109116104</v>
+        <v>0.2165180188425423</v>
       </c>
       <c r="W74">
-        <v>0.1901209629652745</v>
+        <v>0.0929209629652745</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y74">
-        <v>0.4612194221380247</v>
+        <v>0.8392171272966756</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7410,13 +7410,13 @@
         <v>0.73</v>
       </c>
       <c r="B75">
-        <v>0.2170004262256885</v>
+        <v>0.1409684667207233</v>
       </c>
       <c r="C75">
-        <v>-19383.50739201693</v>
+        <v>-201.9009967974926</v>
       </c>
       <c r="D75">
-        <v>24044.57188994803</v>
+        <v>43226.17828516747</v>
       </c>
       <c r="E75">
         <v>35747.37615598556</v>
@@ -7443,45 +7443,45 @@
         <v>4533</v>
       </c>
       <c r="M75">
-        <v>9964.797909048038</v>
+        <v>5476.483002841044</v>
       </c>
       <c r="N75">
-        <v>-5431.797909048038</v>
+        <v>-943.4830028410443</v>
       </c>
       <c r="O75">
-        <v>-1401.403860534394</v>
+        <v>-243.4186147329894</v>
       </c>
       <c r="P75">
-        <v>-4030.394048513645</v>
+        <v>-700.0643881080548</v>
       </c>
       <c r="Q75">
-        <v>-3859.394048513645</v>
+        <v>-529.0643881080548</v>
       </c>
       <c r="R75">
         <v>2.703703703703703</v>
       </c>
       <c r="S75">
-        <v>0.2887234551507069</v>
+        <v>0.2699236051323171</v>
       </c>
       <c r="T75">
-        <v>5.606634571997654</v>
+        <v>5.176064783656285</v>
       </c>
       <c r="U75">
-        <v>0.2158</v>
+        <v>0.1186</v>
       </c>
       <c r="V75">
-        <v>0.1173645477484376</v>
+        <v>0.2135520185844253</v>
       </c>
       <c r="W75">
-        <v>0.1904727305958872</v>
+        <v>0.09327273059588717</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y75">
-        <v>0.4549013478621614</v>
+        <v>0.8277210022652144</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7492,13 +7492,13 @@
         <v>0.74</v>
       </c>
       <c r="B76">
-        <v>0.2187004262256885</v>
+        <v>0.1416964667207232</v>
       </c>
       <c r="C76">
-        <v>-20252.46863523712</v>
+        <v>-1162.602449806524</v>
       </c>
       <c r="D76">
-        <v>23808.15967798763</v>
+        <v>42898.02586341823</v>
       </c>
       <c r="E76">
         <v>36379.92518724535</v>
@@ -7525,45 +7525,45 @@
         <v>4533</v>
       </c>
       <c r="M76">
-        <v>10101.3019899939</v>
+        <v>5551.503317948456</v>
       </c>
       <c r="N76">
-        <v>-5568.301989993903</v>
+        <v>-1018.503317948456</v>
       </c>
       <c r="O76">
-        <v>-1436.621913418427</v>
+        <v>-262.7738560307017</v>
       </c>
       <c r="P76">
-        <v>-4131.680076575476</v>
+        <v>-755.7294619177545</v>
       </c>
       <c r="Q76">
-        <v>-3960.680076575476</v>
+        <v>-584.7294619177545</v>
       </c>
       <c r="R76">
         <v>2.846153846153846</v>
       </c>
       <c r="S76">
-        <v>0.2980666649641956</v>
+        <v>0.2785437437912524</v>
       </c>
       <c r="T76">
-        <v>5.822274363228334</v>
+        <v>5.375144198412295</v>
       </c>
       <c r="U76">
-        <v>0.2158</v>
+        <v>0.1186</v>
       </c>
       <c r="V76">
-        <v>0.1157785403464317</v>
+        <v>0.2106661804954466</v>
       </c>
       <c r="W76">
-        <v>0.19081499099324</v>
+        <v>0.09361499099324004</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y76">
-        <v>0.4487540323505105</v>
+        <v>0.8165355833156844</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7574,13 +7574,13 @@
         <v>0.75</v>
       </c>
       <c r="B77">
-        <v>0.2204004262256885</v>
+        <v>0.1424244667207233</v>
       </c>
       <c r="C77">
-        <v>-21116.82621546496</v>
+        <v>-2118.359089744081</v>
       </c>
       <c r="D77">
-        <v>23576.35112901958</v>
+        <v>42574.81825474046</v>
       </c>
       <c r="E77">
         <v>37012.47421850514</v>
@@ -7607,45 +7607,45 @@
         <v>4533</v>
       </c>
       <c r="M77">
-        <v>10237.80607093977</v>
+        <v>5626.523633055867</v>
       </c>
       <c r="N77">
-        <v>-5704.806070939765</v>
+        <v>-1093.523633055867</v>
       </c>
       <c r="O77">
-        <v>-1471.83996630246</v>
+        <v>-282.1290973284138</v>
       </c>
       <c r="P77">
-        <v>-4232.966104637306</v>
+        <v>-811.3945357274536</v>
       </c>
       <c r="Q77">
-        <v>-4061.966104637306</v>
+        <v>-640.3945357274536</v>
       </c>
       <c r="R77">
         <v>3</v>
       </c>
       <c r="S77">
-        <v>0.3081573315627635</v>
+        <v>0.2878534935429025</v>
       </c>
       <c r="T77">
-        <v>6.055165337757468</v>
+        <v>5.590149966348788</v>
       </c>
       <c r="U77">
-        <v>0.2158</v>
+        <v>0.1186</v>
       </c>
       <c r="V77">
-        <v>0.114234826475146</v>
+        <v>0.2078572980888407</v>
       </c>
       <c r="W77">
-        <v>0.1911481244466635</v>
+        <v>0.09394812444666351</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y77">
-        <v>0.4427706452525038</v>
+        <v>0.8056484422048087</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7656,13 +7656,13 @@
         <v>0.76</v>
       </c>
       <c r="B78">
-        <v>0.2221004262256885</v>
+        <v>0.2101994393330938</v>
       </c>
       <c r="C78">
-        <v>-21976.71330697441</v>
+        <v>-20302.71458030263</v>
       </c>
       <c r="D78">
-        <v>23349.01306876993</v>
+        <v>25023.01179544171</v>
       </c>
       <c r="E78">
         <v>37645.02324976494</v>
@@ -7689,37 +7689,37 @@
         <v>4533</v>
       </c>
       <c r="M78">
-        <v>10374.31015188563</v>
+        <v>9653.204256249464</v>
       </c>
       <c r="N78">
-        <v>-5841.310151885631</v>
+        <v>-5120.204256249464</v>
       </c>
       <c r="O78">
-        <v>-1507.058019186493</v>
+        <v>-1321.012698112362</v>
       </c>
       <c r="P78">
-        <v>-4334.252132699138</v>
+        <v>-3799.191558137102</v>
       </c>
       <c r="Q78">
-        <v>-4163.252132699138</v>
+        <v>-3628.191558137102</v>
       </c>
       <c r="R78">
         <v>3.166666666666667</v>
       </c>
       <c r="S78">
-        <v>0.3190888870445454</v>
+        <v>0.3170014416587341</v>
       </c>
       <c r="T78">
-        <v>6.307463893497363</v>
+        <v>6.263312740386468</v>
       </c>
       <c r="U78">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V78">
-        <v>0.1127317366531046</v>
+        <v>0.121152932120219</v>
       </c>
       <c r="W78">
-        <v>0.1914724912302601</v>
+        <v>0.17647249123026</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7727,7 +7727,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.4369447157097075</v>
+        <v>0.4695850082179029</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7738,13 +7738,13 @@
         <v>0.77</v>
       </c>
       <c r="B79">
-        <v>0.2238004262256885</v>
+        <v>0.2117494393330938</v>
       </c>
       <c r="C79">
-        <v>-22832.25799649506</v>
+        <v>-21168.98340259519</v>
       </c>
       <c r="D79">
-        <v>23126.01741050908</v>
+        <v>24789.29200440895</v>
       </c>
       <c r="E79">
         <v>38277.57228102474</v>
@@ -7771,37 +7771,37 @@
         <v>4533</v>
       </c>
       <c r="M79">
-        <v>10510.8142328315</v>
+        <v>9780.220101726432</v>
       </c>
       <c r="N79">
-        <v>-5977.814232831495</v>
+        <v>-5247.220101726432</v>
       </c>
       <c r="O79">
-        <v>-1542.276072070526</v>
+        <v>-1353.78278624542</v>
       </c>
       <c r="P79">
-        <v>-4435.53816076097</v>
+        <v>-3893.437315481013</v>
       </c>
       <c r="Q79">
-        <v>-4264.53816076097</v>
+        <v>-3722.437315481013</v>
       </c>
       <c r="R79">
         <v>3.347826086956522</v>
       </c>
       <c r="S79">
-        <v>0.3309710125682213</v>
+        <v>0.3287928086873746</v>
       </c>
       <c r="T79">
-        <v>6.581701454084205</v>
+        <v>6.535630685620661</v>
       </c>
       <c r="U79">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V79">
-        <v>0.1112676881251421</v>
+        <v>0.1195795174173589</v>
       </c>
       <c r="W79">
-        <v>0.1917884329025943</v>
+        <v>0.1767884329025943</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7809,7 +7809,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.4312701090121789</v>
+        <v>0.4634865016176704</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7820,13 +7820,13 @@
         <v>0.78</v>
       </c>
       <c r="B80">
-        <v>0.2255004262256885</v>
+        <v>0.2132994393330938</v>
       </c>
       <c r="C80">
-        <v>-23683.5835238578</v>
+        <v>-22030.92665009724</v>
       </c>
       <c r="D80">
-        <v>22907.24091440613</v>
+        <v>24559.89778816669</v>
       </c>
       <c r="E80">
         <v>38910.12131228453</v>
@@ -7853,37 +7853,37 @@
         <v>4533</v>
       </c>
       <c r="M80">
-        <v>10647.31831377736</v>
+        <v>9907.235947203399</v>
       </c>
       <c r="N80">
-        <v>-6114.318313777358</v>
+        <v>-5374.235947203399</v>
       </c>
       <c r="O80">
-        <v>-1577.494124954558</v>
+        <v>-1386.552874378477</v>
       </c>
       <c r="P80">
-        <v>-4536.824188822799</v>
+        <v>-3987.683072824922</v>
       </c>
       <c r="Q80">
-        <v>-4365.824188822799</v>
+        <v>-3816.683072824922</v>
       </c>
       <c r="R80">
         <v>3.545454545454546</v>
       </c>
       <c r="S80">
-        <v>0.3439333313213222</v>
+        <v>0.3416561181731644</v>
       </c>
       <c r="T80">
-        <v>6.880869701997123</v>
+        <v>6.832704807694327</v>
       </c>
       <c r="U80">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V80">
-        <v>0.1098411793030249</v>
+        <v>0.118046446681239</v>
       </c>
       <c r="W80">
-        <v>0.1920962735064072</v>
+        <v>0.1770962735064072</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7891,7 +7891,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.4257410050504843</v>
+        <v>0.4575443669815463</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7902,13 +7902,13 @@
         <v>0.79</v>
       </c>
       <c r="B81">
-        <v>0.2272004262256885</v>
+        <v>0.2148494393330938</v>
       </c>
       <c r="C81">
-        <v>-24530.80850910925</v>
+        <v>-22888.66330529616</v>
       </c>
       <c r="D81">
-        <v>22692.56496041448</v>
+        <v>24334.71016422757</v>
       </c>
       <c r="E81">
         <v>39542.67034354433</v>
@@ -7935,37 +7935,37 @@
         <v>4533</v>
       </c>
       <c r="M81">
-        <v>10783.82239472322</v>
+        <v>10034.25179268036</v>
       </c>
       <c r="N81">
-        <v>-6250.822394723222</v>
+        <v>-5501.251792680365</v>
       </c>
       <c r="O81">
-        <v>-1612.712177838591</v>
+        <v>-1419.322962511534</v>
       </c>
       <c r="P81">
-        <v>-4638.11021688463</v>
+        <v>-4081.928830168831</v>
       </c>
       <c r="Q81">
-        <v>-4467.11021688463</v>
+        <v>-3910.928830168831</v>
       </c>
       <c r="R81">
         <v>3.761904761904763</v>
       </c>
       <c r="S81">
-        <v>0.3581301566223376</v>
+        <v>0.3557445047528389</v>
       </c>
       <c r="T81">
-        <v>7.208530163996987</v>
+        <v>7.158071703298821</v>
       </c>
       <c r="U81">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V81">
-        <v>0.1084507846283031</v>
+        <v>0.1165521878624891</v>
       </c>
       <c r="W81">
-        <v>0.1923963206772122</v>
+        <v>0.1773963206772122</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7973,7 +7973,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.4203518784042756</v>
+        <v>0.4517526661336787</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7984,13 +7984,13 @@
         <v>0.8</v>
       </c>
       <c r="B82">
-        <v>0.2289004262256885</v>
+        <v>0.2163994393330938</v>
       </c>
       <c r="C82">
-        <v>-25374.04716697403</v>
+        <v>-23742.30802656526</v>
       </c>
       <c r="D82">
-        <v>22481.87533380949</v>
+        <v>24113.61447421826</v>
       </c>
       <c r="E82">
         <v>40175.21937480412</v>
@@ -8017,37 +8017,37 @@
         <v>4533</v>
       </c>
       <c r="M82">
-        <v>10920.32647566908</v>
+        <v>10161.26763815733</v>
       </c>
       <c r="N82">
-        <v>-6387.326475669084</v>
+        <v>-5628.267638157331</v>
       </c>
       <c r="O82">
-        <v>-1647.930230722624</v>
+        <v>-1452.093050644591</v>
       </c>
       <c r="P82">
-        <v>-4739.396244946461</v>
+        <v>-4176.17458751274</v>
       </c>
       <c r="Q82">
-        <v>-4568.396244946461</v>
+        <v>-4005.17458751274</v>
       </c>
       <c r="R82">
         <v>4.000000000000001</v>
       </c>
       <c r="S82">
-        <v>0.3737466644534544</v>
+        <v>0.3712417299904809</v>
       </c>
       <c r="T82">
-        <v>7.568956672196836</v>
+        <v>7.515975288463761</v>
       </c>
       <c r="U82">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V82">
-        <v>0.1070951498204493</v>
+        <v>0.115095285514208</v>
       </c>
       <c r="W82">
-        <v>0.192688866668747</v>
+        <v>0.177688866668747</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.4150974799242222</v>
+        <v>0.4461057578070078</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8066,13 +8066,13 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2306004262256885</v>
+        <v>0.2179494393330938</v>
       </c>
       <c r="C83">
-        <v>-26213.4095094802</v>
+        <v>-24591.97134283135</v>
       </c>
       <c r="D83">
-        <v>22275.06202256311</v>
+        <v>23896.50018921197</v>
       </c>
       <c r="E83">
         <v>40807.76840606391</v>
@@ -8099,37 +8099,37 @@
         <v>4533</v>
       </c>
       <c r="M83">
-        <v>11056.83055661495</v>
+        <v>10288.2834836343</v>
       </c>
       <c r="N83">
-        <v>-6523.830556614948</v>
+        <v>-5755.283483634299</v>
       </c>
       <c r="O83">
-        <v>-1683.148283606657</v>
+        <v>-1484.863138777649</v>
       </c>
       <c r="P83">
-        <v>-4840.682273008291</v>
+        <v>-4270.42034485665</v>
       </c>
       <c r="Q83">
-        <v>-4669.682273008291</v>
+        <v>-4099.42034485665</v>
       </c>
       <c r="R83">
         <v>4.263157894736843</v>
       </c>
       <c r="S83">
-        <v>0.3910070152141626</v>
+        <v>0.388370242095243</v>
       </c>
       <c r="T83">
-        <v>7.967322812838774</v>
+        <v>7.911552935225012</v>
       </c>
       <c r="U83">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V83">
-        <v>0.105772987476987</v>
+        <v>0.1136743560634153</v>
       </c>
       <c r="W83">
-        <v>0.1929741893024662</v>
+        <v>0.1779741893024662</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.4099728196782442</v>
+        <v>0.4405982793155632</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8148,13 +8148,13 @@
         <v>0.8200000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2323004262256885</v>
+        <v>0.2194994393330938</v>
       </c>
       <c r="C84">
-        <v>-27049.00153750255</v>
+        <v>-25437.75983781935</v>
       </c>
       <c r="D84">
-        <v>22072.01902580057</v>
+        <v>23683.26072548377</v>
       </c>
       <c r="E84">
         <v>41440.31743732371</v>
@@ -8181,37 +8181,37 @@
         <v>4533</v>
       </c>
       <c r="M84">
-        <v>11193.33463756081</v>
+        <v>10415.29932911127</v>
       </c>
       <c r="N84">
-        <v>-6660.334637560813</v>
+        <v>-5882.299329111265</v>
       </c>
       <c r="O84">
-        <v>-1718.36633649069</v>
+        <v>-1517.633226910707</v>
       </c>
       <c r="P84">
-        <v>-4941.968301070123</v>
+        <v>-4364.666102200559</v>
       </c>
       <c r="Q84">
-        <v>-4770.968301070123</v>
+        <v>-4193.666102200559</v>
       </c>
       <c r="R84">
         <v>4.555555555555557</v>
       </c>
       <c r="S84">
-        <v>0.4101851827260605</v>
+        <v>0.4074019222116454</v>
       </c>
       <c r="T84">
-        <v>8.409951857996484</v>
+        <v>8.351083653848624</v>
       </c>
       <c r="U84">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V84">
-        <v>0.1044830729955603</v>
+        <v>0.1122880834284956</v>
       </c>
       <c r="W84">
-        <v>0.1932525528475581</v>
+        <v>0.1782525528475581</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.4049731511455826</v>
+        <v>0.4352251295678125</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8230,13 +8230,13 @@
         <v>0.8300000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2340004262256886</v>
+        <v>0.2210494393330938</v>
       </c>
       <c r="C85">
-        <v>-27880.92542192482</v>
+        <v>-26279.77632451977</v>
       </c>
       <c r="D85">
-        <v>21872.64417263809</v>
+        <v>23473.79327004314</v>
       </c>
       <c r="E85">
         <v>42072.8664685835</v>
@@ -8263,37 +8263,37 @@
         <v>4533</v>
       </c>
       <c r="M85">
-        <v>11329.83871850668</v>
+        <v>10542.31517458823</v>
       </c>
       <c r="N85">
-        <v>-6796.838718506677</v>
+        <v>-6009.315174588231</v>
       </c>
       <c r="O85">
-        <v>-1753.584389374723</v>
+        <v>-1550.403315043764</v>
       </c>
       <c r="P85">
-        <v>-5043.254329131954</v>
+        <v>-4458.911859544468</v>
       </c>
       <c r="Q85">
-        <v>-4872.254329131954</v>
+        <v>-4287.911859544468</v>
       </c>
       <c r="R85">
         <v>4.882352941176473</v>
       </c>
       <c r="S85">
-        <v>0.4316196052393583</v>
+        <v>0.4286726235182129</v>
       </c>
       <c r="T85">
-        <v>8.904654908466869</v>
+        <v>8.842323868780898</v>
       </c>
       <c r="U85">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V85">
-        <v>0.1032242407907945</v>
+        <v>0.1109352149534535</v>
       </c>
       <c r="W85">
-        <v>0.1935242088373466</v>
+        <v>0.1785242088373465</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8301,7 +8301,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.4000939565534671</v>
+        <v>0.4299814533079592</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8312,13 +8312,13 @@
         <v>0.84</v>
       </c>
       <c r="B86">
-        <v>0.2357004262256885</v>
+        <v>0.2225994393330938</v>
       </c>
       <c r="C86">
-        <v>-28709.27967507123</v>
+        <v>-27118.12001047876</v>
       </c>
       <c r="D86">
-        <v>21676.83895075147</v>
+        <v>23267.99861534394</v>
       </c>
       <c r="E86">
         <v>42705.41549984329</v>
@@ -8345,37 +8345,37 @@
         <v>4533</v>
       </c>
       <c r="M86">
-        <v>11466.34279945254</v>
+        <v>10669.3310200652</v>
       </c>
       <c r="N86">
-        <v>-6933.342799452539</v>
+        <v>-6136.331020065198</v>
       </c>
       <c r="O86">
-        <v>-1788.802442258755</v>
+        <v>-1583.173403176821</v>
       </c>
       <c r="P86">
-        <v>-5144.540357193784</v>
+        <v>-4553.157616888377</v>
       </c>
       <c r="Q86">
-        <v>-4973.540357193784</v>
+        <v>-4382.157616888377</v>
       </c>
       <c r="R86">
         <v>5.249999999999999</v>
       </c>
       <c r="S86">
-        <v>0.455733330566818</v>
+        <v>0.4526021624881009</v>
       </c>
       <c r="T86">
-        <v>9.461195840246043</v>
+        <v>9.394969110579698</v>
       </c>
       <c r="U86">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V86">
-        <v>0.1019953807813803</v>
+        <v>0.1096145576325791</v>
       </c>
       <c r="W86">
-        <v>0.1937893968273782</v>
+        <v>0.1787893968273781</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.395330933261164</v>
+        <v>0.4248626264828645</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8394,13 +8394,13 @@
         <v>0.85</v>
       </c>
       <c r="B87">
-        <v>0.2374004262256885</v>
+        <v>0.2241494393330938</v>
       </c>
       <c r="C87">
-        <v>-29534.15931301177</v>
+        <v>-27952.88665446917</v>
       </c>
       <c r="D87">
-        <v>21484.50834407072</v>
+        <v>23065.78100261331</v>
       </c>
       <c r="E87">
         <v>43337.96453110308</v>
@@ -8427,37 +8427,37 @@
         <v>4533</v>
       </c>
       <c r="M87">
-        <v>11602.8468803984</v>
+        <v>10796.34686554216</v>
       </c>
       <c r="N87">
-        <v>-7069.846880398401</v>
+        <v>-6263.346865542164</v>
       </c>
       <c r="O87">
-        <v>-1824.020495142788</v>
+        <v>-1615.943491309878</v>
       </c>
       <c r="P87">
-        <v>-5245.826385255614</v>
+        <v>-4647.403374232285</v>
       </c>
       <c r="Q87">
-        <v>-5074.826385255614</v>
+        <v>-4476.403374232285</v>
       </c>
       <c r="R87">
         <v>5.666666666666666</v>
       </c>
       <c r="S87">
-        <v>0.4830622192712725</v>
+        <v>0.4797223066539744</v>
       </c>
       <c r="T87">
-        <v>10.09194222959578</v>
+        <v>10.02130038461835</v>
       </c>
       <c r="U87">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V87">
-        <v>0.1007954351251288</v>
+        <v>0.1083249746016075</v>
       </c>
       <c r="W87">
-        <v>0.1940483450999972</v>
+        <v>0.1790483450999972</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8465,7 +8465,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3906799811051503</v>
+        <v>0.4198642426418897</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8476,13 +8476,13 @@
         <v>0.86</v>
       </c>
       <c r="B88">
-        <v>0.2391004262256885</v>
+        <v>0.2256994393330938</v>
       </c>
       <c r="C88">
-        <v>-30355.65600930298</v>
+        <v>-28784.16871506239</v>
       </c>
       <c r="D88">
-        <v>21295.56067903931</v>
+        <v>22867.04797327989</v>
       </c>
       <c r="E88">
         <v>43970.51356236288</v>
@@ -8509,37 +8509,37 @@
         <v>4533</v>
       </c>
       <c r="M88">
-        <v>11739.35096134427</v>
+        <v>10923.36271101913</v>
       </c>
       <c r="N88">
-        <v>-7206.350961344266</v>
+        <v>-6390.36271101913</v>
       </c>
       <c r="O88">
-        <v>-1859.238548026821</v>
+        <v>-1648.713579442935</v>
       </c>
       <c r="P88">
-        <v>-5347.112413317445</v>
+        <v>-4741.649131576194</v>
       </c>
       <c r="Q88">
-        <v>-5176.112413317445</v>
+        <v>-4570.649131576194</v>
       </c>
       <c r="R88">
         <v>6.142857142857142</v>
       </c>
       <c r="S88">
-        <v>0.5142952349335063</v>
+        <v>0.5107167571292582</v>
       </c>
       <c r="T88">
-        <v>10.81279524599548</v>
+        <v>10.73710755494823</v>
       </c>
       <c r="U88">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V88">
-        <v>0.09962339518181333</v>
+        <v>0.1070653818736819</v>
       </c>
       <c r="W88">
-        <v>0.1943012713197647</v>
+        <v>0.1793012713197647</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.3861371906271834</v>
+        <v>0.4149821002855887</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8558,13 +8558,13 @@
         <v>0.87</v>
       </c>
       <c r="B89">
-        <v>0.2408004262256885</v>
+        <v>0.2272494393330938</v>
       </c>
       <c r="C89">
-        <v>-31173.85824068688</v>
+        <v>-29612.0554915853</v>
       </c>
       <c r="D89">
-        <v>21109.90747891519</v>
+        <v>22671.71022801677</v>
       </c>
       <c r="E89">
         <v>44603.06259362267</v>
@@ -8591,37 +8591,37 @@
         <v>4533</v>
       </c>
       <c r="M89">
-        <v>11875.85504229013</v>
+        <v>11050.3785564961</v>
       </c>
       <c r="N89">
-        <v>-7342.855042290128</v>
+        <v>-6517.378556496096</v>
       </c>
       <c r="O89">
-        <v>-1894.456600910853</v>
+        <v>-1681.483667575993</v>
       </c>
       <c r="P89">
-        <v>-5448.398441379275</v>
+        <v>-4835.894888920104</v>
       </c>
       <c r="Q89">
-        <v>-5277.398441379275</v>
+        <v>-4664.894888920104</v>
       </c>
       <c r="R89">
         <v>6.692307692307692</v>
       </c>
       <c r="S89">
-        <v>0.5503333299283912</v>
+        <v>0.5464795846007396</v>
       </c>
       <c r="T89">
-        <v>11.64454872645667</v>
+        <v>11.56303890532886</v>
       </c>
       <c r="U89">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V89">
-        <v>0.09847829868547066</v>
+        <v>0.1058347453004212</v>
       </c>
       <c r="W89">
-        <v>0.1945483831436755</v>
+        <v>0.1795483831436754</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8629,7 +8629,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.3816988321142274</v>
+        <v>0.4102121910869038</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8640,13 +8640,13 @@
         <v>0.88</v>
       </c>
       <c r="B90">
-        <v>0.2425004262256885</v>
+        <v>0.2287994393330938</v>
       </c>
       <c r="C90">
-        <v>-31988.85142523479</v>
+        <v>-30436.63325791387</v>
       </c>
       <c r="D90">
-        <v>20927.46332562708</v>
+        <v>22479.68149294801</v>
       </c>
       <c r="E90">
         <v>45235.61162488247</v>
@@ -8673,37 +8673,37 @@
         <v>4533</v>
       </c>
       <c r="M90">
-        <v>12012.35912323599</v>
+        <v>11177.39440197306</v>
       </c>
       <c r="N90">
-        <v>-7479.359123235992</v>
+        <v>-6644.394401973064</v>
       </c>
       <c r="O90">
-        <v>-1929.674653794886</v>
+        <v>-1714.253755709051</v>
       </c>
       <c r="P90">
-        <v>-5549.684469441107</v>
+        <v>-4930.140646264013</v>
       </c>
       <c r="Q90">
-        <v>-5378.684469441107</v>
+        <v>-4759.140646264013</v>
       </c>
       <c r="R90">
         <v>7.333333333333334</v>
       </c>
       <c r="S90">
-        <v>0.5923777740890906</v>
+        <v>0.588202883317468</v>
       </c>
       <c r="T90">
-        <v>12.61492778699473</v>
+        <v>12.52662548077293</v>
       </c>
       <c r="U90">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V90">
-        <v>0.0973592271094994</v>
+        <v>0.1046320777401891</v>
       </c>
       <c r="W90">
-        <v>0.1947898787897701</v>
+        <v>0.17978987878977</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.3773613453856566</v>
+        <v>0.4055506889154615</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8722,13 +8722,13 @@
         <v>0.89</v>
       </c>
       <c r="B91">
-        <v>0.2442004262256885</v>
+        <v>0.2303494393330938</v>
       </c>
       <c r="C91">
-        <v>-32800.71805338874</v>
+        <v>-31257.98538952435</v>
       </c>
       <c r="D91">
-        <v>20748.14572873292</v>
+        <v>22290.87839259732</v>
       </c>
       <c r="E91">
         <v>45868.16065614227</v>
@@ -8755,37 +8755,37 @@
         <v>4533</v>
       </c>
       <c r="M91">
-        <v>12148.86320418186</v>
+        <v>11304.41024745003</v>
       </c>
       <c r="N91">
-        <v>-7615.863204181856</v>
+        <v>-6771.410247450032</v>
       </c>
       <c r="O91">
-        <v>-1964.892706678919</v>
+        <v>-1747.023843842108</v>
       </c>
       <c r="P91">
-        <v>-5650.970497502937</v>
+        <v>-5024.386403607924</v>
       </c>
       <c r="Q91">
-        <v>-5479.970497502937</v>
+        <v>-4853.386403607924</v>
       </c>
       <c r="R91">
         <v>8.090909090909092</v>
       </c>
       <c r="S91">
-        <v>0.6420666626426443</v>
+        <v>0.6375122363463287</v>
       </c>
       <c r="T91">
-        <v>13.76173940399425</v>
+        <v>13.66540961538865</v>
       </c>
       <c r="U91">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V91">
-        <v>0.09626530320939265</v>
+        <v>0.1034564364172656</v>
       </c>
       <c r="W91">
-        <v>0.1950259475674131</v>
+        <v>0.1800259475674131</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.3731213302689638</v>
+        <v>0.4009939396018046</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8804,13 +8804,13 @@
         <v>0.9</v>
       </c>
       <c r="B92">
-        <v>0.2459004262256885</v>
+        <v>0.2318994393330938</v>
       </c>
       <c r="C92">
-        <v>-33609.53781232337</v>
+        <v>-32076.19248419552</v>
       </c>
       <c r="D92">
-        <v>20571.8750010581</v>
+        <v>22105.22032918594</v>
       </c>
       <c r="E92">
         <v>46500.70968740206</v>
@@ -8837,37 +8837,37 @@
         <v>4533</v>
       </c>
       <c r="M92">
-        <v>12285.36728512772</v>
+        <v>11431.426092927</v>
       </c>
       <c r="N92">
-        <v>-7752.367285127721</v>
+        <v>-6898.426092926997</v>
       </c>
       <c r="O92">
-        <v>-2000.110759562952</v>
+        <v>-1779.793931975165</v>
       </c>
       <c r="P92">
-        <v>-5752.256525564769</v>
+        <v>-5118.632160951832</v>
       </c>
       <c r="Q92">
-        <v>-5581.256525564769</v>
+        <v>-4947.632160951832</v>
       </c>
       <c r="R92">
         <v>9.000000000000002</v>
       </c>
       <c r="S92">
-        <v>0.7016933289069088</v>
+        <v>0.6966834599809617</v>
       </c>
       <c r="T92">
-        <v>15.13791334439367</v>
+        <v>15.03195057692752</v>
       </c>
       <c r="U92">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V92">
-        <v>0.0951956887292883</v>
+        <v>0.1023069204570738</v>
       </c>
       <c r="W92">
-        <v>0.1952567703722196</v>
+        <v>0.1802567703722196</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3689755377104197</v>
+        <v>0.3965384513840069</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8886,13 +8886,13 @@
         <v>0.91</v>
       </c>
       <c r="B93">
-        <v>0.2476004262256885</v>
+        <v>0.2334494393330938</v>
       </c>
       <c r="C93">
-        <v>-34415.38770402181</v>
+        <v>-32891.33247672868</v>
       </c>
       <c r="D93">
-        <v>20398.57414061945</v>
+        <v>21922.62936791258</v>
       </c>
       <c r="E93">
         <v>47133.25871866185</v>
@@ -8919,37 +8919,37 @@
         <v>4533</v>
       </c>
       <c r="M93">
-        <v>12421.87136607358</v>
+        <v>11558.44193840396</v>
       </c>
       <c r="N93">
-        <v>-7888.871366073585</v>
+        <v>-7025.441938403965</v>
       </c>
       <c r="O93">
-        <v>-2035.328812446985</v>
+        <v>-1812.564020108223</v>
       </c>
       <c r="P93">
-        <v>-5853.542553626599</v>
+        <v>-5212.877918295742</v>
       </c>
       <c r="Q93">
-        <v>-5682.542553626599</v>
+        <v>-5041.877918295742</v>
       </c>
       <c r="R93">
         <v>10.11111111111111</v>
       </c>
       <c r="S93">
-        <v>0.7745703654521209</v>
+        <v>0.7690038444232907</v>
       </c>
       <c r="T93">
-        <v>16.81990371599297</v>
+        <v>16.70216730769725</v>
       </c>
       <c r="U93">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V93">
-        <v>0.09414958225973567</v>
+        <v>0.1011826685839191</v>
       </c>
       <c r="W93">
-        <v>0.195482520148349</v>
+        <v>0.180482520148349</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8957,7 +8957,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3649208614718437</v>
+        <v>0.3921808859841827</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8968,13 +8968,13 @@
         <v>0.92</v>
       </c>
       <c r="B94">
-        <v>0.2493004262256885</v>
+        <v>0.2349994393330938</v>
       </c>
       <c r="C94">
-        <v>-35218.34215743338</v>
+        <v>-33703.48074802872</v>
       </c>
       <c r="D94">
-        <v>20228.16871846767</v>
+        <v>21743.03012787233</v>
       </c>
       <c r="E94">
         <v>47765.80774992165</v>
@@ -9001,37 +9001,37 @@
         <v>4533</v>
       </c>
       <c r="M94">
-        <v>12558.37544701945</v>
+        <v>11685.45778388093</v>
       </c>
       <c r="N94">
-        <v>-8025.375447019447</v>
+        <v>-7152.457783880931</v>
       </c>
       <c r="O94">
-        <v>-2070.546865331017</v>
+        <v>-1845.33410824128</v>
       </c>
       <c r="P94">
-        <v>-5954.82858168843</v>
+        <v>-5307.12367563965</v>
       </c>
       <c r="Q94">
-        <v>-5783.82858168843</v>
+        <v>-5136.12367563965</v>
       </c>
       <c r="R94">
         <v>11.50000000000001</v>
       </c>
       <c r="S94">
-        <v>0.8656666611336364</v>
+        <v>0.8594043249762026</v>
       </c>
       <c r="T94">
-        <v>18.9223916804921</v>
+        <v>18.78993822115941</v>
       </c>
       <c r="U94">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V94">
-        <v>0.09312621723517332</v>
+        <v>0.1000828569688765</v>
       </c>
       <c r="W94">
-        <v>0.1957033623206496</v>
+        <v>0.1807033623206496</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3609543303688889</v>
+        <v>0.3879180502669632</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9050,13 +9050,13 @@
         <v>0.93</v>
       </c>
       <c r="B95">
-        <v>0.2510004262256885</v>
+        <v>0.2365494393330938</v>
       </c>
       <c r="C95">
-        <v>-36018.47313505606</v>
+        <v>-34512.71022886694</v>
       </c>
       <c r="D95">
-        <v>20060.58677210478</v>
+        <v>21566.3496782939</v>
       </c>
       <c r="E95">
         <v>48398.35678118144</v>
@@ -9083,37 +9083,37 @@
         <v>4533</v>
       </c>
       <c r="M95">
-        <v>12694.87952796531</v>
+        <v>11812.4736293579</v>
       </c>
       <c r="N95">
-        <v>-8161.879527965311</v>
+        <v>-7279.473629357897</v>
       </c>
       <c r="O95">
-        <v>-2105.76491821505</v>
+        <v>-1878.104196374338</v>
       </c>
       <c r="P95">
-        <v>-6056.114609750261</v>
+        <v>-5401.36943298356</v>
       </c>
       <c r="Q95">
-        <v>-5885.114609750261</v>
+        <v>-5230.36943298356</v>
       </c>
       <c r="R95">
         <v>13.2857142857143</v>
       </c>
       <c r="S95">
-        <v>0.9827904698670131</v>
+        <v>0.9756335142585171</v>
       </c>
       <c r="T95">
-        <v>21.62559049199097</v>
+        <v>21.47421510989647</v>
       </c>
       <c r="U95">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V95">
-        <v>0.09212486006060157</v>
+        <v>0.09900669721652301</v>
       </c>
       <c r="W95">
-        <v>0.1959194551989222</v>
+        <v>0.1809194551989222</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9121,7 +9121,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3570731010100836</v>
+        <v>0.3837468884361357</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9132,13 +9132,13 @@
         <v>0.9400000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2527004262256886</v>
+        <v>0.2380994393330938</v>
       </c>
       <c r="C96">
-        <v>-36815.85023426473</v>
+        <v>-35319.09149862564</v>
       </c>
       <c r="D96">
-        <v>19895.75870415592</v>
+        <v>21392.517439795</v>
       </c>
       <c r="E96">
         <v>49030.90581244124</v>
@@ -9165,37 +9165,37 @@
         <v>4533</v>
       </c>
       <c r="M96">
-        <v>12831.38360891118</v>
+        <v>11939.48947483487</v>
       </c>
       <c r="N96">
-        <v>-8298.383608911176</v>
+        <v>-7406.489474834865</v>
       </c>
       <c r="O96">
-        <v>-2140.982971099083</v>
+        <v>-1910.874284507395</v>
       </c>
       <c r="P96">
-        <v>-6157.400637812092</v>
+        <v>-5495.615190327469</v>
       </c>
       <c r="Q96">
-        <v>-5986.400637812092</v>
+        <v>-5324.615190327469</v>
       </c>
       <c r="R96">
         <v>15.66666666666668</v>
       </c>
       <c r="S96">
-        <v>1.138955548178182</v>
+        <v>1.130605766634937</v>
       </c>
       <c r="T96">
-        <v>25.22985557398947</v>
+        <v>25.05325096154589</v>
       </c>
       <c r="U96">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V96">
-        <v>0.0911448083578292</v>
+        <v>0.09795343448017702</v>
       </c>
       <c r="W96">
-        <v>0.1961309503563805</v>
+        <v>0.1811309503563805</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.353274450999338</v>
+        <v>0.3796644747293683</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9214,13 +9214,13 @@
         <v>0.9500000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2544004262256885</v>
+        <v>0.2396494393330938</v>
       </c>
       <c r="C97">
-        <v>-37610.54078368456</v>
+        <v>-36122.69287930547</v>
       </c>
       <c r="D97">
-        <v>19733.61718599587</v>
+        <v>21221.46509037496</v>
       </c>
       <c r="E97">
         <v>49663.45484370103</v>
@@ -9247,37 +9247,37 @@
         <v>4533</v>
       </c>
       <c r="M97">
-        <v>12967.88768985704</v>
+        <v>12066.50532031183</v>
       </c>
       <c r="N97">
-        <v>-8434.887689857038</v>
+        <v>-7533.505320311831</v>
       </c>
       <c r="O97">
-        <v>-2176.201023983116</v>
+        <v>-1943.644372640453</v>
       </c>
       <c r="P97">
-        <v>-6258.686665873922</v>
+        <v>-5589.860947671379</v>
       </c>
       <c r="Q97">
-        <v>-6087.686665873922</v>
+        <v>-5418.860947671379</v>
       </c>
       <c r="R97">
         <v>19.00000000000003</v>
       </c>
       <c r="S97">
-        <v>1.357586657813819</v>
+        <v>1.347566919961925</v>
       </c>
       <c r="T97">
-        <v>30.27582668878738</v>
+        <v>30.06390115385508</v>
       </c>
       <c r="U97">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V97">
-        <v>0.09018538932248364</v>
+        <v>0.09692234569617515</v>
       </c>
       <c r="W97">
-        <v>0.196337992984208</v>
+        <v>0.181337992984208</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.349555772567766</v>
+        <v>0.3756680065743223</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9296,13 +9296,13 @@
         <v>0.96</v>
       </c>
       <c r="B98">
-        <v>0.2561004262256885</v>
+        <v>0.2411994393330938</v>
       </c>
       <c r="C98">
-        <v>-38402.60993489024</v>
+        <v>-36923.58052505846</v>
       </c>
       <c r="D98">
-        <v>19574.09706604998</v>
+        <v>21053.12647588176</v>
       </c>
       <c r="E98">
         <v>50296.00387496082</v>
@@ -9329,37 +9329,37 @@
         <v>4533</v>
       </c>
       <c r="M98">
-        <v>13104.3917708029</v>
+        <v>12193.5211657888</v>
       </c>
       <c r="N98">
-        <v>-8571.391770802902</v>
+        <v>-7660.521165788798</v>
       </c>
       <c r="O98">
-        <v>-2211.419076867149</v>
+        <v>-1976.41446077351</v>
       </c>
       <c r="P98">
-        <v>-6359.972693935753</v>
+        <v>-5684.106705015288</v>
       </c>
       <c r="Q98">
-        <v>-6188.972693935753</v>
+        <v>-5513.106705015288</v>
       </c>
       <c r="R98">
         <v>23.99999999999998</v>
       </c>
       <c r="S98">
-        <v>1.685533322267271</v>
+        <v>1.673008649952403</v>
       </c>
       <c r="T98">
-        <v>37.84478336098415</v>
+        <v>37.57987644231877</v>
       </c>
       <c r="U98">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V98">
-        <v>0.08924595818370777</v>
+        <v>0.09591273792850667</v>
       </c>
       <c r="W98">
-        <v>0.1965407222239559</v>
+        <v>0.1815407222239559</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.3459145666035185</v>
+        <v>0.3717547981725065</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9378,13 +9378,13 @@
         <v>0.97</v>
       </c>
       <c r="B99">
-        <v>0.2578004262256885</v>
+        <v>0.2427494393330938</v>
       </c>
       <c r="C99">
-        <v>-39192.12074969315</v>
+        <v>-37721.81850749331</v>
       </c>
       <c r="D99">
-        <v>19417.13528250687</v>
+        <v>20887.43752470671</v>
       </c>
       <c r="E99">
         <v>50928.55290622061</v>
@@ -9411,37 +9411,37 @@
         <v>4533</v>
       </c>
       <c r="M99">
-        <v>13240.89585174876</v>
+        <v>12320.53701126576</v>
       </c>
       <c r="N99">
-        <v>-8707.895851748764</v>
+        <v>-7787.537011265764</v>
       </c>
       <c r="O99">
-        <v>-2246.637129751181</v>
+        <v>-2009.184548906567</v>
       </c>
       <c r="P99">
-        <v>-6461.258721997583</v>
+        <v>-5778.352462359197</v>
       </c>
       <c r="Q99">
-        <v>-6290.258721997583</v>
+        <v>-5607.352462359197</v>
       </c>
       <c r="R99">
         <v>32.33333333333331</v>
       </c>
       <c r="S99">
-        <v>2.232111096356361</v>
+        <v>2.215411533269871</v>
       </c>
       <c r="T99">
-        <v>50.45971114797886</v>
+        <v>50.1065019230917</v>
       </c>
       <c r="U99">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V99">
-        <v>0.08832589675913347</v>
+        <v>0.09492394681584165</v>
       </c>
       <c r="W99">
-        <v>0.196739271479379</v>
+        <v>0.181739271479379</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.3423484370509049</v>
+        <v>0.3679222744800064</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9460,13 +9460,13 @@
         <v>0.98</v>
       </c>
       <c r="B100">
-        <v>0.2595004262256885</v>
+        <v>0.2442994393330938</v>
       </c>
       <c r="C100">
-        <v>-39979.13428326236</v>
+        <v>-38517.46889698398</v>
       </c>
       <c r="D100">
-        <v>19262.67078019745</v>
+        <v>20724.33616647583</v>
       </c>
       <c r="E100">
         <v>51561.10193748041</v>
@@ -9493,37 +9493,37 @@
         <v>4533</v>
       </c>
       <c r="M100">
-        <v>13377.39993269463</v>
+        <v>12447.55285674273</v>
       </c>
       <c r="N100">
-        <v>-8844.399932694629</v>
+        <v>-7914.55285674273</v>
       </c>
       <c r="O100">
-        <v>-2281.855182635214</v>
+        <v>-2041.954637039624</v>
       </c>
       <c r="P100">
-        <v>-6562.544750059415</v>
+        <v>-5872.598219703105</v>
       </c>
       <c r="Q100">
-        <v>-6391.544750059415</v>
+        <v>-5701.598219703105</v>
       </c>
       <c r="R100">
         <v>48.99999999999996</v>
       </c>
       <c r="S100">
-        <v>3.325266644534541</v>
+        <v>3.300217299904805</v>
       </c>
       <c r="T100">
-        <v>75.68956672196829</v>
+        <v>75.15975288463754</v>
       </c>
       <c r="U100">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V100">
-        <v>0.08742461209832599</v>
+        <v>0.09395533511363918</v>
       </c>
       <c r="W100">
-        <v>0.1969337687091813</v>
+        <v>0.1819337687091813</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9531,7 +9531,7 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.3388550856524263</v>
+        <v>0.364167965556741</v>
       </c>
       <c r="Z100">
         <v>0</v>
@@ -9542,13 +9542,13 @@
         <v>0.99</v>
       </c>
       <c r="B101">
-        <v>0.2612004262256885</v>
+        <v>0.2458494393330938</v>
       </c>
       <c r="C101">
-        <v>-40763.70966330952</v>
+        <v>-39310.59184019837</v>
       </c>
       <c r="D101">
-        <v>19110.64443141008</v>
+        <v>20563.76225452123</v>
       </c>
       <c r="E101">
         <v>52193.6509687402</v>
@@ -9575,37 +9575,37 @@
         <v>4533</v>
       </c>
       <c r="M101">
-        <v>13513.90401364049</v>
+        <v>12574.5687022197</v>
       </c>
       <c r="N101">
-        <v>-8980.904013640491</v>
+        <v>-8041.568702219696</v>
       </c>
       <c r="O101">
-        <v>-2317.073235519247</v>
+        <v>-2074.724725172682</v>
       </c>
       <c r="P101">
-        <v>-6663.830778121244</v>
+        <v>-5966.843977047014</v>
       </c>
       <c r="Q101">
-        <v>-6492.830778121244</v>
+        <v>-5795.843977047014</v>
       </c>
       <c r="R101">
         <v>98.99999999999991</v>
       </c>
       <c r="S101">
-        <v>6.604733289069083</v>
+        <v>6.554634599809609</v>
       </c>
       <c r="T101">
-        <v>151.3791334439366</v>
+        <v>150.3195057692751</v>
       </c>
       <c r="U101">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V101">
-        <v>0.08654153520844392</v>
+        <v>0.09300629132461254</v>
       </c>
       <c r="W101">
-        <v>0.1971243367020178</v>
+        <v>0.1821243367020178</v>
       </c>
       <c r="X101" t="inlineStr">
         <is>
@@ -9613,7 +9613,7 @@
         </is>
       </c>
       <c r="Y101">
-        <v>0.3354323070094725</v>
+        <v>0.3604895012581881</v>
       </c>
       <c r="Z101">
         <v>0</v>

--- a/research/traditional_assets/database/data/netherlands/netherlands_semiconductor.xlsx
+++ b/research/traditional_assets/database/data/netherlands/netherlands_semiconductor.xlsx
@@ -1284,7 +1284,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1421,22 +1421,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1174892188913704</v>
+        <v>0.1172194867066307</v>
       </c>
       <c r="C2">
-        <v>60131.37191021068</v>
+        <v>59715.54443474495</v>
       </c>
       <c r="D2">
-        <v>57383.37191021068</v>
+        <v>57600.09346600475</v>
       </c>
       <c r="E2">
-        <v>-10428.7031259794</v>
+        <v>-9796.154094719608</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>632.549031259794</v>
       </c>
       <c r="G2">
         <v>2748</v>
@@ -1457,28 +1457,28 @@
         <v>4533</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>31.81721627236764</v>
       </c>
       <c r="N2">
-        <v>4533</v>
+        <v>4501.182783727632</v>
       </c>
       <c r="O2">
-        <v>1169.514</v>
+        <v>1161.305158201729</v>
       </c>
       <c r="P2">
-        <v>3363.486</v>
+        <v>3339.877625525903</v>
       </c>
       <c r="Q2">
-        <v>3534.486</v>
+        <v>3510.877625525903</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1174892188913704</v>
+        <v>0.1180265259662936</v>
       </c>
       <c r="T2">
-        <v>1.655640159154051</v>
+        <v>1.668049098528721</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1495,7 +1495,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>142.4700376423812</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1503,22 +1503,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1172194867066307</v>
+        <v>0.116949754521891</v>
       </c>
       <c r="C3">
-        <v>59715.54443474495</v>
+        <v>59301.36016322607</v>
       </c>
       <c r="D3">
-        <v>57600.09346600475</v>
+        <v>57818.45822574566</v>
       </c>
       <c r="E3">
-        <v>-9796.154094719608</v>
+        <v>-9163.605063459814</v>
       </c>
       <c r="F3">
-        <v>632.549031259794</v>
+        <v>1265.098062519588</v>
       </c>
       <c r="G3">
         <v>2748</v>
@@ -1539,28 +1539,28 @@
         <v>4533</v>
       </c>
       <c r="M3">
-        <v>31.81721627236764</v>
+        <v>63.63443254473528</v>
       </c>
       <c r="N3">
-        <v>4501.182783727632</v>
+        <v>4469.365567455265</v>
       </c>
       <c r="O3">
-        <v>1161.305158201729</v>
+        <v>1153.096316403458</v>
       </c>
       <c r="P3">
-        <v>3339.877625525903</v>
+        <v>3316.269251051806</v>
       </c>
       <c r="Q3">
-        <v>3510.877625525903</v>
+        <v>3487.269251051806</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1180265259662936</v>
+        <v>0.1185747984917255</v>
       </c>
       <c r="T3">
-        <v>1.668049098528721</v>
+        <v>1.680711281564099</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>142.4700376423812</v>
+        <v>71.23501882119058</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1585,22 +1585,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.116949754521891</v>
+        <v>0.1166800223371512</v>
       </c>
       <c r="C4">
-        <v>59301.36016322607</v>
+        <v>58888.8378551709</v>
       </c>
       <c r="D4">
-        <v>57818.45822574566</v>
+        <v>58038.48494895028</v>
       </c>
       <c r="E4">
-        <v>-9163.605063459814</v>
+        <v>-8531.05603220002</v>
       </c>
       <c r="F4">
-        <v>1265.098062519588</v>
+        <v>1897.647093779382</v>
       </c>
       <c r="G4">
         <v>2748</v>
@@ -1621,28 +1621,28 @@
         <v>4533</v>
       </c>
       <c r="M4">
-        <v>63.63443254473528</v>
+        <v>95.45164881710291</v>
       </c>
       <c r="N4">
-        <v>4469.365567455265</v>
+        <v>4437.548351182897</v>
       </c>
       <c r="O4">
-        <v>1153.096316403458</v>
+        <v>1144.887474605187</v>
       </c>
       <c r="P4">
-        <v>3316.269251051806</v>
+        <v>3292.66087657771</v>
       </c>
       <c r="Q4">
-        <v>3487.269251051806</v>
+        <v>3463.66087657771</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1185747984917255</v>
+        <v>0.1191343756053105</v>
       </c>
       <c r="T4">
-        <v>1.680711281564099</v>
+        <v>1.693634540538349</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>71.23501882119058</v>
+        <v>47.4900125474604</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1667,22 +1667,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1166800223371512</v>
+        <v>0.1164102901524115</v>
       </c>
       <c r="C5">
-        <v>58888.8378551709</v>
+        <v>58477.99655674259</v>
       </c>
       <c r="D5">
-        <v>58038.48494895028</v>
+        <v>58260.19268178177</v>
       </c>
       <c r="E5">
-        <v>-8531.05603220002</v>
+        <v>-7898.507000940226</v>
       </c>
       <c r="F5">
-        <v>1897.647093779382</v>
+        <v>2530.196125039176</v>
       </c>
       <c r="G5">
         <v>2748</v>
@@ -1703,28 +1703,28 @@
         <v>4533</v>
       </c>
       <c r="M5">
-        <v>95.45164881710291</v>
+        <v>127.2688650894706</v>
       </c>
       <c r="N5">
-        <v>4437.548351182897</v>
+        <v>4405.731134910529</v>
       </c>
       <c r="O5">
-        <v>1144.887474605187</v>
+        <v>1136.678632806917</v>
       </c>
       <c r="P5">
-        <v>3292.66087657771</v>
+        <v>3269.052502103613</v>
       </c>
       <c r="Q5">
-        <v>3463.66087657771</v>
+        <v>3440.052502103613</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1191343756053105</v>
+        <v>0.1197056105754286</v>
       </c>
       <c r="T5">
-        <v>1.693634540538349</v>
+        <v>1.706827034074564</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>47.4900125474604</v>
+        <v>35.61750941059529</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1749,22 +1749,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1164102901524115</v>
+        <v>0.1161405579676717</v>
       </c>
       <c r="C6">
-        <v>58477.99655674259</v>
+        <v>58068.85560624664</v>
       </c>
       <c r="D6">
-        <v>58260.19268178177</v>
+        <v>58483.60076254561</v>
       </c>
       <c r="E6">
-        <v>-7898.507000940226</v>
+        <v>-7265.957969680432</v>
       </c>
       <c r="F6">
-        <v>2530.196125039176</v>
+        <v>3162.74515629897</v>
       </c>
       <c r="G6">
         <v>2748</v>
@@ -1785,28 +1785,28 @@
         <v>4533</v>
       </c>
       <c r="M6">
-        <v>127.2688650894706</v>
+        <v>159.0860813618382</v>
       </c>
       <c r="N6">
-        <v>4405.731134910529</v>
+        <v>4373.913918638162</v>
       </c>
       <c r="O6">
-        <v>1136.678632806917</v>
+        <v>1128.469791008646</v>
       </c>
       <c r="P6">
-        <v>3269.052502103613</v>
+        <v>3245.444127629516</v>
       </c>
       <c r="Q6">
-        <v>3440.052502103613</v>
+        <v>3416.444127629516</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1197056105754286</v>
+        <v>0.1202888715449176</v>
       </c>
       <c r="T6">
-        <v>1.706827034074564</v>
+        <v>1.720297264316805</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>35.61750941059529</v>
+        <v>28.49400752847624</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1831,22 +1831,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1161405579676717</v>
+        <v>0.115870825782932</v>
       </c>
       <c r="C7">
-        <v>58068.85560624664</v>
+        <v>57661.43463975373</v>
       </c>
       <c r="D7">
-        <v>58483.60076254561</v>
+        <v>58708.72882731249</v>
       </c>
       <c r="E7">
-        <v>-7265.957969680432</v>
+        <v>-6633.408938420638</v>
       </c>
       <c r="F7">
-        <v>3162.74515629897</v>
+        <v>3795.294187558764</v>
       </c>
       <c r="G7">
         <v>2748</v>
@@ -1867,28 +1867,28 @@
         <v>4533</v>
       </c>
       <c r="M7">
-        <v>159.0860813618382</v>
+        <v>190.9032976342058</v>
       </c>
       <c r="N7">
-        <v>4373.913918638162</v>
+        <v>4342.096702365794</v>
       </c>
       <c r="O7">
-        <v>1128.469791008646</v>
+        <v>1120.260949210375</v>
       </c>
       <c r="P7">
-        <v>3245.444127629516</v>
+        <v>3221.835753155419</v>
       </c>
       <c r="Q7">
-        <v>3416.444127629516</v>
+        <v>3392.835753155419</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1202888715449176</v>
+        <v>0.1208845423222681</v>
       </c>
       <c r="T7">
-        <v>1.720297264316805</v>
+        <v>1.734054095202497</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>28.49400752847624</v>
+        <v>23.74500627373019</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1913,22 +1913,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.115870825782932</v>
+        <v>0.1156010935981923</v>
       </c>
       <c r="C8">
-        <v>57661.43463975373</v>
+        <v>57255.75359685297</v>
       </c>
       <c r="D8">
-        <v>58708.72882731249</v>
+        <v>58935.59681567152</v>
       </c>
       <c r="E8">
-        <v>-6633.408938420638</v>
+        <v>-6000.859907160845</v>
       </c>
       <c r="F8">
-        <v>3795.294187558764</v>
+        <v>4427.843218818557</v>
       </c>
       <c r="G8">
         <v>2748</v>
@@ -1949,28 +1949,28 @@
         <v>4533</v>
       </c>
       <c r="M8">
-        <v>190.9032976342058</v>
+        <v>222.7205139065734</v>
       </c>
       <c r="N8">
-        <v>4342.096702365794</v>
+        <v>4310.279486093426</v>
       </c>
       <c r="O8">
-        <v>1120.260949210375</v>
+        <v>1112.052107412104</v>
       </c>
       <c r="P8">
-        <v>3221.835753155419</v>
+        <v>3198.227378681322</v>
       </c>
       <c r="Q8">
-        <v>3392.835753155419</v>
+        <v>3369.227378681322</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1208845423222681</v>
+        <v>0.1214930232238627</v>
       </c>
       <c r="T8">
-        <v>1.734054095202497</v>
+        <v>1.748106771913687</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>23.74500627373019</v>
+        <v>20.35286252034017</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1995,22 +1995,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1156010935981923</v>
+        <v>0.1153313614134525</v>
       </c>
       <c r="C9">
-        <v>57255.75359685298</v>
+        <v>56851.8327265392</v>
       </c>
       <c r="D9">
-        <v>58935.59681567154</v>
+        <v>59164.22497661755</v>
       </c>
       <c r="E9">
-        <v>-6000.859907160844</v>
+        <v>-5368.31087590105</v>
       </c>
       <c r="F9">
-        <v>4427.843218818558</v>
+        <v>5060.392250078352</v>
       </c>
       <c r="G9">
         <v>2748</v>
@@ -2031,28 +2031,28 @@
         <v>4533</v>
       </c>
       <c r="M9">
-        <v>222.7205139065734</v>
+        <v>254.5377301789411</v>
       </c>
       <c r="N9">
-        <v>4310.279486093426</v>
+        <v>4278.462269821059</v>
       </c>
       <c r="O9">
-        <v>1112.052107412104</v>
+        <v>1103.843265613833</v>
       </c>
       <c r="P9">
-        <v>3198.227378681322</v>
+        <v>3174.619004207226</v>
       </c>
       <c r="Q9">
-        <v>3369.227378681322</v>
+        <v>3345.619004207226</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1214930232238627</v>
+        <v>0.1221147319711441</v>
       </c>
       <c r="T9">
-        <v>1.748106771913687</v>
+        <v>1.762464941596861</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>20.35286252034017</v>
+        <v>17.80875470529764</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2077,22 +2077,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1153313614134525</v>
+        <v>0.1150616292287128</v>
       </c>
       <c r="C10">
-        <v>56851.8327265392</v>
+        <v>56449.6925932376</v>
       </c>
       <c r="D10">
-        <v>59164.22497661755</v>
+        <v>59394.63387457575</v>
       </c>
       <c r="E10">
-        <v>-5368.31087590105</v>
+        <v>-4735.761844641256</v>
       </c>
       <c r="F10">
-        <v>5060.392250078352</v>
+        <v>5692.941281338146</v>
       </c>
       <c r="G10">
         <v>2748</v>
@@ -2113,28 +2113,28 @@
         <v>4533</v>
       </c>
       <c r="M10">
-        <v>254.5377301789411</v>
+        <v>286.3549464513087</v>
       </c>
       <c r="N10">
-        <v>4278.462269821059</v>
+        <v>4246.645053548691</v>
       </c>
       <c r="O10">
-        <v>1103.843265613833</v>
+        <v>1095.634423815562</v>
       </c>
       <c r="P10">
-        <v>3174.619004207226</v>
+        <v>3151.010629733129</v>
       </c>
       <c r="Q10">
-        <v>3345.619004207226</v>
+        <v>3322.010629733129</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1221147319711441</v>
+        <v>0.1227501046469371</v>
       </c>
       <c r="T10">
-        <v>1.762464941596861</v>
+        <v>1.777138675448895</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>17.80875470529764</v>
+        <v>15.8300041824868</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1150616292287128</v>
+        <v>0.1147918970439731</v>
       </c>
       <c r="C11">
-        <v>56449.6925932376</v>
+        <v>56049.35408296977</v>
       </c>
       <c r="D11">
-        <v>59394.63387457575</v>
+        <v>59626.84439556771</v>
       </c>
       <c r="E11">
-        <v>-4735.761844641256</v>
+        <v>-4103.212813381463</v>
       </c>
       <c r="F11">
-        <v>5692.941281338146</v>
+        <v>6325.490312597939</v>
       </c>
       <c r="G11">
         <v>2748</v>
@@ -2195,28 +2195,28 @@
         <v>4533</v>
       </c>
       <c r="M11">
-        <v>286.3549464513087</v>
+        <v>318.1721627236763</v>
       </c>
       <c r="N11">
-        <v>4246.645053548691</v>
+        <v>4214.827837276323</v>
       </c>
       <c r="O11">
-        <v>1095.634423815562</v>
+        <v>1087.425582017291</v>
       </c>
       <c r="P11">
-        <v>3151.010629733129</v>
+        <v>3127.402255259032</v>
       </c>
       <c r="Q11">
-        <v>3322.010629733129</v>
+        <v>3298.402255259032</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1227501046469371</v>
+        <v>0.1233995967155256</v>
       </c>
       <c r="T11">
-        <v>1.777138675448895</v>
+        <v>1.792138492275419</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>15.8300041824868</v>
+        <v>14.24700376423812</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2241,22 +2241,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1147918970439731</v>
+        <v>0.1145221648592333</v>
       </c>
       <c r="C12">
-        <v>56049.35408296977</v>
+        <v>55650.83840966513</v>
       </c>
       <c r="D12">
-        <v>59626.84439556771</v>
+        <v>59860.87775352286</v>
       </c>
       <c r="E12">
-        <v>-4103.212813381462</v>
+        <v>-3470.663782121668</v>
       </c>
       <c r="F12">
-        <v>6325.49031259794</v>
+        <v>6958.039343857734</v>
       </c>
       <c r="G12">
         <v>2748</v>
@@ -2277,28 +2277,28 @@
         <v>4533</v>
       </c>
       <c r="M12">
-        <v>318.1721627236764</v>
+        <v>349.989378996044</v>
       </c>
       <c r="N12">
-        <v>4214.827837276323</v>
+        <v>4183.010621003956</v>
       </c>
       <c r="O12">
-        <v>1087.425582017291</v>
+        <v>1079.216740219021</v>
       </c>
       <c r="P12">
-        <v>3127.402255259032</v>
+        <v>3103.793880784935</v>
       </c>
       <c r="Q12">
-        <v>3298.402255259032</v>
+        <v>3274.793880784935</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1233995967155256</v>
+        <v>0.1240636841114981</v>
       </c>
       <c r="T12">
-        <v>1.792138492275419</v>
+        <v>1.80747538363737</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>14.24700376423812</v>
+        <v>12.95182160385283</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2323,22 +2323,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1145221648592333</v>
+        <v>0.1142524326744936</v>
       </c>
       <c r="C13">
-        <v>55650.83840966513</v>
+        <v>55254.1671216212</v>
       </c>
       <c r="D13">
-        <v>59860.87775352286</v>
+        <v>60096.75549673873</v>
       </c>
       <c r="E13">
-        <v>-3470.663782121668</v>
+        <v>-2838.114750861874</v>
       </c>
       <c r="F13">
-        <v>6958.039343857734</v>
+        <v>7590.588375117528</v>
       </c>
       <c r="G13">
         <v>2748</v>
@@ -2359,28 +2359,28 @@
         <v>4533</v>
       </c>
       <c r="M13">
-        <v>349.989378996044</v>
+        <v>381.8065952684116</v>
       </c>
       <c r="N13">
-        <v>4183.010621003956</v>
+        <v>4151.193404731588</v>
       </c>
       <c r="O13">
-        <v>1079.216740219021</v>
+        <v>1071.00789842075</v>
       </c>
       <c r="P13">
-        <v>3103.793880784935</v>
+        <v>3080.185506310838</v>
       </c>
       <c r="Q13">
-        <v>3274.793880784935</v>
+        <v>3251.185506310838</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1240636841114981</v>
+        <v>0.1247428644028336</v>
       </c>
       <c r="T13">
-        <v>1.80747538363737</v>
+        <v>1.823160840712093</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>12.95182160385283</v>
+        <v>11.8725031368651</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2405,22 +2405,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1142524326744936</v>
+        <v>0.1139827004897539</v>
       </c>
       <c r="C14">
-        <v>55254.1671216212</v>
+        <v>54859.36210811765</v>
       </c>
       <c r="D14">
-        <v>60096.75549673873</v>
+        <v>60334.49951449497</v>
       </c>
       <c r="E14">
-        <v>-2838.114750861874</v>
+        <v>-2205.56571960208</v>
       </c>
       <c r="F14">
-        <v>7590.588375117528</v>
+        <v>8223.137406377322</v>
       </c>
       <c r="G14">
         <v>2748</v>
@@ -2441,28 +2441,28 @@
         <v>4533</v>
       </c>
       <c r="M14">
-        <v>381.8065952684116</v>
+        <v>413.6238115407793</v>
       </c>
       <c r="N14">
-        <v>4151.193404731588</v>
+        <v>4119.37618845922</v>
       </c>
       <c r="O14">
-        <v>1071.00789842075</v>
+        <v>1062.799056622479</v>
       </c>
       <c r="P14">
-        <v>3080.185506310838</v>
+        <v>3056.577131836742</v>
       </c>
       <c r="Q14">
-        <v>3251.185506310838</v>
+        <v>3227.577131836742</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1247428644028336</v>
+        <v>0.1254376580341998</v>
       </c>
       <c r="T14">
-        <v>1.823160840712093</v>
+        <v>1.839206883006925</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2479,7 +2479,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>11.8725031368651</v>
+        <v>10.95923366479855</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2487,22 +2487,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1139827004897539</v>
+        <v>0.1137129683050141</v>
       </c>
       <c r="C15">
-        <v>54859.36210811765</v>
+        <v>54466.44560618763</v>
       </c>
       <c r="D15">
-        <v>60334.49951449497</v>
+        <v>60574.13204382474</v>
       </c>
       <c r="E15">
-        <v>-2205.56571960208</v>
+        <v>-1573.016688342286</v>
       </c>
       <c r="F15">
-        <v>8223.137406377322</v>
+        <v>8855.686437637116</v>
       </c>
       <c r="G15">
         <v>2748</v>
@@ -2523,28 +2523,28 @@
         <v>4533</v>
       </c>
       <c r="M15">
-        <v>413.6238115407793</v>
+        <v>445.4410278131469</v>
       </c>
       <c r="N15">
-        <v>4119.37618845922</v>
+        <v>4087.558972186853</v>
       </c>
       <c r="O15">
-        <v>1062.799056622479</v>
+        <v>1054.590214824208</v>
       </c>
       <c r="P15">
-        <v>3056.577131836742</v>
+        <v>3032.968757362645</v>
       </c>
       <c r="Q15">
-        <v>3227.577131836742</v>
+        <v>3203.968757362645</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1254376580341998</v>
+        <v>0.1261486096569932</v>
       </c>
       <c r="T15">
-        <v>1.839206883006925</v>
+        <v>1.855626089076055</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2561,7 +2561,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>10.95923366479855</v>
+        <v>10.17643126017009</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2569,22 +2569,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1137129683050141</v>
+        <v>0.1134432361202744</v>
       </c>
       <c r="C16">
-        <v>54466.44560618763</v>
+        <v>54075.44020755125</v>
       </c>
       <c r="D16">
-        <v>60574.13204382474</v>
+        <v>60815.67567644816</v>
       </c>
       <c r="E16">
-        <v>-1573.016688342286</v>
+        <v>-940.4676570824904</v>
       </c>
       <c r="F16">
-        <v>8855.686437637116</v>
+        <v>9488.235468896912</v>
       </c>
       <c r="G16">
         <v>2748</v>
@@ -2605,28 +2605,28 @@
         <v>4533</v>
       </c>
       <c r="M16">
-        <v>445.4410278131469</v>
+        <v>477.2582440855147</v>
       </c>
       <c r="N16">
-        <v>4087.558972186853</v>
+        <v>4055.741755914485</v>
       </c>
       <c r="O16">
-        <v>1054.590214824208</v>
+        <v>1046.381373025937</v>
       </c>
       <c r="P16">
-        <v>3032.968757362645</v>
+        <v>3009.360382888548</v>
       </c>
       <c r="Q16">
-        <v>3203.968757362645</v>
+        <v>3180.360382888548</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1261486096569932</v>
+        <v>0.126876289553264</v>
       </c>
       <c r="T16">
-        <v>1.855626089076055</v>
+        <v>1.872431629405635</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>10.17643126017009</v>
+        <v>9.498002509492075</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2651,22 +2651,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1134432361202744</v>
+        <v>0.1131735039355347</v>
       </c>
       <c r="C17">
-        <v>54075.44020755125</v>
+        <v>53686.36886571559</v>
       </c>
       <c r="D17">
-        <v>60815.67567644816</v>
+        <v>61059.15336587229</v>
       </c>
       <c r="E17">
-        <v>-940.4676570824922</v>
+        <v>-307.9186258226982</v>
       </c>
       <c r="F17">
-        <v>9488.23546889691</v>
+        <v>10120.7845001567</v>
       </c>
       <c r="G17">
         <v>2748</v>
@@ -2687,28 +2687,28 @@
         <v>4533</v>
       </c>
       <c r="M17">
-        <v>477.2582440855145</v>
+        <v>509.0754603578822</v>
       </c>
       <c r="N17">
-        <v>4055.741755914486</v>
+        <v>4023.924539642118</v>
       </c>
       <c r="O17">
-        <v>1046.381373025937</v>
+        <v>1038.172531227666</v>
       </c>
       <c r="P17">
-        <v>3009.360382888548</v>
+        <v>2985.752008414452</v>
       </c>
       <c r="Q17">
-        <v>3180.360382888548</v>
+        <v>3156.752008414452</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.126876289553264</v>
+        <v>0.1276212951613508</v>
       </c>
       <c r="T17">
-        <v>1.872431629405635</v>
+        <v>1.889637301647824</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>9.498002509492078</v>
+        <v>8.904377352648822</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2733,22 +2733,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1131735039355347</v>
+        <v>0.1130929817507949</v>
       </c>
       <c r="C18">
-        <v>53686.36886571559</v>
+        <v>53126.88267547516</v>
       </c>
       <c r="D18">
-        <v>61059.15336587229</v>
+        <v>61132.21620689167</v>
       </c>
       <c r="E18">
-        <v>-307.9186258226982</v>
+        <v>324.6304054370958</v>
       </c>
       <c r="F18">
-        <v>10120.7845001567</v>
+        <v>10753.3335314165</v>
       </c>
       <c r="G18">
         <v>2748</v>
@@ -2769,45 +2769,45 @@
         <v>4533</v>
       </c>
       <c r="M18">
-        <v>509.0754603578822</v>
+        <v>557.0226769273746</v>
       </c>
       <c r="N18">
-        <v>4023.924539642118</v>
+        <v>3975.977323072625</v>
       </c>
       <c r="O18">
-        <v>1038.172531227666</v>
+        <v>1025.802149352737</v>
       </c>
       <c r="P18">
-        <v>2985.752008414452</v>
+        <v>2950.175173719888</v>
       </c>
       <c r="Q18">
-        <v>3156.752008414452</v>
+        <v>3121.175173719888</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1276212951613508</v>
+        <v>0.1283842527118011</v>
       </c>
       <c r="T18">
-        <v>1.889637301647824</v>
+        <v>1.907257568401873</v>
       </c>
       <c r="U18">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V18">
         <v>0.258</v>
       </c>
       <c r="W18">
-        <v>0.0373226</v>
+        <v>0.0384356</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y18">
-        <v>8.904377352648822</v>
+        <v>8.137909258927746</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2815,22 +2815,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1130929817507949</v>
+        <v>0.1128343795660552</v>
       </c>
       <c r="C19">
-        <v>53126.88267547516</v>
+        <v>52730.1667312287</v>
       </c>
       <c r="D19">
-        <v>61132.21620689167</v>
+        <v>61368.04929390499</v>
       </c>
       <c r="E19">
-        <v>324.6304054370958</v>
+        <v>957.1794366968916</v>
       </c>
       <c r="F19">
-        <v>10753.3335314165</v>
+        <v>11385.88256267629</v>
       </c>
       <c r="G19">
         <v>2748</v>
@@ -2851,28 +2851,28 @@
         <v>4533</v>
       </c>
       <c r="M19">
-        <v>557.0226769273746</v>
+        <v>589.788716746632</v>
       </c>
       <c r="N19">
-        <v>3975.977323072625</v>
+        <v>3943.211283253368</v>
       </c>
       <c r="O19">
-        <v>1025.802149352737</v>
+        <v>1017.348511079369</v>
       </c>
       <c r="P19">
-        <v>2950.175173719888</v>
+        <v>2925.862772173999</v>
       </c>
       <c r="Q19">
-        <v>3121.175173719888</v>
+        <v>3096.862772173999</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1283842527118011</v>
+        <v>0.1291658189829941</v>
       </c>
       <c r="T19">
-        <v>1.907257568401873</v>
+        <v>1.92530759775968</v>
       </c>
       <c r="U19">
         <v>0.0518</v>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>8.137909258927746</v>
+        <v>7.685803188987315</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2897,22 +2897,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1128343795660552</v>
+        <v>0.1125757773813155</v>
       </c>
       <c r="C20">
-        <v>52730.16673122868</v>
+        <v>52335.27740597269</v>
       </c>
       <c r="D20">
-        <v>61368.04929390497</v>
+        <v>61605.70899990878</v>
       </c>
       <c r="E20">
-        <v>957.1794366968898</v>
+        <v>1589.728467956684</v>
       </c>
       <c r="F20">
-        <v>11385.88256267629</v>
+        <v>12018.43159393609</v>
       </c>
       <c r="G20">
         <v>2748</v>
@@ -2933,28 +2933,28 @@
         <v>4533</v>
       </c>
       <c r="M20">
-        <v>589.7887167466318</v>
+        <v>622.5547565658892</v>
       </c>
       <c r="N20">
-        <v>3943.211283253368</v>
+        <v>3910.445243434111</v>
       </c>
       <c r="O20">
-        <v>1017.348511079369</v>
+        <v>1008.894872806001</v>
       </c>
       <c r="P20">
-        <v>2925.862772173999</v>
+        <v>2901.550370628111</v>
       </c>
       <c r="Q20">
-        <v>3096.862772173999</v>
+        <v>3072.550370628111</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1291658189829941</v>
+        <v>0.1299666831868092</v>
       </c>
       <c r="T20">
-        <v>1.92530759775968</v>
+        <v>1.943803306854716</v>
       </c>
       <c r="U20">
         <v>0.0518</v>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>7.685803188987316</v>
+        <v>7.281287231672194</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2979,22 +2979,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1125757773813155</v>
+        <v>0.1123171751965757</v>
       </c>
       <c r="C21">
-        <v>52335.27740597269</v>
+        <v>51942.23600402421</v>
       </c>
       <c r="D21">
-        <v>61605.70899990878</v>
+        <v>61845.21662922009</v>
       </c>
       <c r="E21">
-        <v>1589.728467956684</v>
+        <v>2222.277499216478</v>
       </c>
       <c r="F21">
-        <v>12018.43159393609</v>
+        <v>12650.98062519588</v>
       </c>
       <c r="G21">
         <v>2748</v>
@@ -3015,28 +3015,28 @@
         <v>4533</v>
       </c>
       <c r="M21">
-        <v>622.5547565658892</v>
+        <v>655.3207963851465</v>
       </c>
       <c r="N21">
-        <v>3910.445243434111</v>
+        <v>3877.679203614854</v>
       </c>
       <c r="O21">
-        <v>1008.894872806001</v>
+        <v>1000.441234532632</v>
       </c>
       <c r="P21">
-        <v>2901.550370628111</v>
+        <v>2877.237969082221</v>
       </c>
       <c r="Q21">
-        <v>3072.550370628111</v>
+        <v>3048.237969082221</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1299666831868092</v>
+        <v>0.1307875689957196</v>
       </c>
       <c r="T21">
-        <v>1.943803306854716</v>
+        <v>1.962761408677128</v>
       </c>
       <c r="U21">
         <v>0.0518</v>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>7.281287231672194</v>
+        <v>6.917222870088584</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3061,22 +3061,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1123171751965757</v>
+        <v>0.112323467011836</v>
       </c>
       <c r="C22">
-        <v>51942.23600402421</v>
+        <v>51303.83762823622</v>
       </c>
       <c r="D22">
-        <v>61845.21662922009</v>
+        <v>61839.36728469189</v>
       </c>
       <c r="E22">
-        <v>2222.277499216478</v>
+        <v>2854.826530476274</v>
       </c>
       <c r="F22">
-        <v>12650.98062519588</v>
+        <v>13283.52965645568</v>
       </c>
       <c r="G22">
         <v>2748</v>
@@ -3097,45 +3097,45 @@
         <v>4533</v>
       </c>
       <c r="M22">
-        <v>655.3207963851465</v>
+        <v>710.6688366203787</v>
       </c>
       <c r="N22">
-        <v>3877.679203614854</v>
+        <v>3822.331163379621</v>
       </c>
       <c r="O22">
-        <v>1000.441234532632</v>
+        <v>986.1614401519423</v>
       </c>
       <c r="P22">
-        <v>2877.237969082221</v>
+        <v>2836.169723227679</v>
       </c>
       <c r="Q22">
-        <v>3048.237969082221</v>
+        <v>3007.169723227679</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1307875689957196</v>
+        <v>0.131629236723843</v>
       </c>
       <c r="T22">
-        <v>1.962761408677128</v>
+        <v>1.982199462444411</v>
       </c>
       <c r="U22">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V22">
         <v>0.258</v>
       </c>
       <c r="W22">
-        <v>0.0384356</v>
+        <v>0.039697</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y22">
-        <v>6.917222870088584</v>
+        <v>6.378498347496014</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3143,22 +3143,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.112323467011836</v>
+        <v>0.1120774788270962</v>
       </c>
       <c r="C23">
-        <v>51303.83762823623</v>
+        <v>50900.80477612229</v>
       </c>
       <c r="D23">
-        <v>61839.36728469191</v>
+        <v>62068.88346383776</v>
       </c>
       <c r="E23">
-        <v>2854.826530476272</v>
+        <v>3487.375561736066</v>
       </c>
       <c r="F23">
-        <v>13283.52965645567</v>
+        <v>13916.07868771547</v>
       </c>
       <c r="G23">
         <v>2748</v>
@@ -3179,28 +3179,28 @@
         <v>4533</v>
       </c>
       <c r="M23">
-        <v>710.6688366203786</v>
+        <v>744.5102097927775</v>
       </c>
       <c r="N23">
-        <v>3822.331163379622</v>
+        <v>3788.489790207223</v>
       </c>
       <c r="O23">
-        <v>986.1614401519424</v>
+        <v>977.4303658734634</v>
       </c>
       <c r="P23">
-        <v>2836.169723227679</v>
+        <v>2811.059424333759</v>
       </c>
       <c r="Q23">
-        <v>3007.169723227679</v>
+        <v>2982.059424333759</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.131629236723843</v>
+        <v>0.1324924856757644</v>
       </c>
       <c r="T23">
-        <v>1.982199462444411</v>
+        <v>2.002135927846753</v>
       </c>
       <c r="U23">
         <v>0.0535</v>
@@ -3217,7 +3217,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>6.378498347496015</v>
+        <v>6.088566604428014</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1120774788270962</v>
+        <v>0.1118314906423565</v>
       </c>
       <c r="C24">
-        <v>50900.80477612229</v>
+        <v>50499.48196470946</v>
       </c>
       <c r="D24">
-        <v>62068.88346383776</v>
+        <v>62300.10968368471</v>
       </c>
       <c r="E24">
-        <v>3487.375561736066</v>
+        <v>4119.92459299586</v>
       </c>
       <c r="F24">
-        <v>13916.07868771547</v>
+        <v>14548.62771897526</v>
       </c>
       <c r="G24">
         <v>2748</v>
@@ -3261,28 +3261,28 @@
         <v>4533</v>
       </c>
       <c r="M24">
-        <v>744.5102097927775</v>
+        <v>778.3515829651765</v>
       </c>
       <c r="N24">
-        <v>3788.489790207223</v>
+        <v>3754.648417034824</v>
       </c>
       <c r="O24">
-        <v>977.4303658734634</v>
+        <v>968.6992915949845</v>
       </c>
       <c r="P24">
-        <v>2811.059424333759</v>
+        <v>2785.949125439839</v>
       </c>
       <c r="Q24">
-        <v>2982.059424333759</v>
+        <v>2956.949125439839</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1324924856757644</v>
+        <v>0.1333781566783851</v>
       </c>
       <c r="T24">
-        <v>2.002135927846753</v>
+        <v>2.022590223519286</v>
       </c>
       <c r="U24">
         <v>0.0535</v>
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>6.088566604428014</v>
+        <v>5.823846317278971</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3307,22 +3307,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1118314906423565</v>
+        <v>0.1117279664576168</v>
       </c>
       <c r="C25">
-        <v>50499.48196470946</v>
+        <v>49964.76043232066</v>
       </c>
       <c r="D25">
-        <v>62300.10968368471</v>
+        <v>62397.93718255572</v>
       </c>
       <c r="E25">
-        <v>4119.92459299586</v>
+        <v>4752.473624255656</v>
       </c>
       <c r="F25">
-        <v>14548.62771897526</v>
+        <v>15181.17675023506</v>
       </c>
       <c r="G25">
         <v>2748</v>
@@ -3343,45 +3343,45 @@
         <v>4533</v>
       </c>
       <c r="M25">
-        <v>778.3515829651765</v>
+        <v>824.3378975377636</v>
       </c>
       <c r="N25">
-        <v>3754.648417034824</v>
+        <v>3708.662102462236</v>
       </c>
       <c r="O25">
-        <v>968.6992915949845</v>
+        <v>956.834822435257</v>
       </c>
       <c r="P25">
-        <v>2785.949125439839</v>
+        <v>2751.827280026979</v>
       </c>
       <c r="Q25">
-        <v>2956.949125439839</v>
+        <v>2922.827280026979</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1333781566783851</v>
+        <v>0.1342871348126536</v>
       </c>
       <c r="T25">
-        <v>2.022590223519286</v>
+        <v>2.043582790130569</v>
       </c>
       <c r="U25">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V25">
         <v>0.258</v>
       </c>
       <c r="W25">
-        <v>0.039697</v>
+        <v>0.0402906</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y25">
-        <v>5.823846317278971</v>
+        <v>5.498958635214681</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3389,22 +3389,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1117279664576168</v>
+        <v>0.111487914272877</v>
       </c>
       <c r="C26">
-        <v>49964.76043232066</v>
+        <v>49560.24057978771</v>
       </c>
       <c r="D26">
-        <v>62397.93718255572</v>
+        <v>62625.96636128257</v>
       </c>
       <c r="E26">
-        <v>4752.473624255654</v>
+        <v>5385.022655515448</v>
       </c>
       <c r="F26">
-        <v>15181.17675023506</v>
+        <v>15813.72578149485</v>
       </c>
       <c r="G26">
         <v>2748</v>
@@ -3425,28 +3425,28 @@
         <v>4533</v>
       </c>
       <c r="M26">
-        <v>824.3378975377635</v>
+        <v>858.6853099351704</v>
       </c>
       <c r="N26">
-        <v>3708.662102462236</v>
+        <v>3674.31469006483</v>
       </c>
       <c r="O26">
-        <v>956.834822435257</v>
+        <v>947.9731900367261</v>
       </c>
       <c r="P26">
-        <v>2751.827280026979</v>
+        <v>2726.341500028104</v>
       </c>
       <c r="Q26">
-        <v>2922.827280026979</v>
+        <v>2897.341500028104</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1342871348126536</v>
+        <v>0.1352203523638361</v>
       </c>
       <c r="T26">
-        <v>2.043582790130569</v>
+        <v>2.065135158518154</v>
       </c>
       <c r="U26">
         <v>0.0543</v>
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>5.498958635214681</v>
+        <v>5.279000289806095</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3471,22 +3471,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.111487914272877</v>
+        <v>0.1112478620881373</v>
       </c>
       <c r="C27">
-        <v>49560.24057978771</v>
+        <v>49157.39347563167</v>
       </c>
       <c r="D27">
-        <v>62625.96636128257</v>
+        <v>62855.6682883863</v>
       </c>
       <c r="E27">
-        <v>5385.022655515448</v>
+        <v>6017.571686775242</v>
       </c>
       <c r="F27">
-        <v>15813.72578149485</v>
+        <v>16446.27481275464</v>
       </c>
       <c r="G27">
         <v>2748</v>
@@ -3507,28 +3507,28 @@
         <v>4533</v>
       </c>
       <c r="M27">
-        <v>858.6853099351704</v>
+        <v>893.0327223325771</v>
       </c>
       <c r="N27">
-        <v>3674.31469006483</v>
+        <v>3639.967277667423</v>
       </c>
       <c r="O27">
-        <v>947.9731900367261</v>
+        <v>939.1115576381951</v>
       </c>
       <c r="P27">
-        <v>2726.341500028104</v>
+        <v>2700.855720029228</v>
       </c>
       <c r="Q27">
-        <v>2897.341500028104</v>
+        <v>2871.855720029228</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1352203523638361</v>
+        <v>0.1361787920109963</v>
       </c>
       <c r="T27">
-        <v>2.065135158518154</v>
+        <v>2.087270023348645</v>
       </c>
       <c r="U27">
         <v>0.0543</v>
@@ -3545,7 +3545,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>5.279000289806095</v>
+        <v>5.075961817121245</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3553,22 +3553,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1112478620881373</v>
+        <v>0.1110078099033976</v>
       </c>
       <c r="C28">
-        <v>49157.39347563167</v>
+        <v>48756.23759372398</v>
       </c>
       <c r="D28">
-        <v>62855.6682883863</v>
+        <v>63087.06143773843</v>
       </c>
       <c r="E28">
-        <v>6017.571686775242</v>
+        <v>6650.120718035036</v>
       </c>
       <c r="F28">
-        <v>16446.27481275464</v>
+        <v>17078.82384401444</v>
       </c>
       <c r="G28">
         <v>2748</v>
@@ -3589,28 +3589,28 @@
         <v>4533</v>
       </c>
       <c r="M28">
-        <v>893.0327223325771</v>
+        <v>927.380134729984</v>
       </c>
       <c r="N28">
-        <v>3639.967277667423</v>
+        <v>3605.619865270016</v>
       </c>
       <c r="O28">
-        <v>939.1115576381951</v>
+        <v>930.2499252396641</v>
       </c>
       <c r="P28">
-        <v>2700.855720029228</v>
+        <v>2675.369940030352</v>
       </c>
       <c r="Q28">
-        <v>2871.855720029228</v>
+        <v>2846.369940030352</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1361787920109963</v>
+        <v>0.1371634902786268</v>
       </c>
       <c r="T28">
-        <v>2.087270023348645</v>
+        <v>2.110011322832028</v>
       </c>
       <c r="U28">
         <v>0.0543</v>
@@ -3627,7 +3627,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>5.075961817121245</v>
+        <v>4.887963231301939</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3635,22 +3635,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1110078099033976</v>
+        <v>0.1107677577186578</v>
       </c>
       <c r="C29">
-        <v>48756.23759372398</v>
+        <v>48356.79168097601</v>
       </c>
       <c r="D29">
-        <v>63087.06143773843</v>
+        <v>63320.16455625024</v>
       </c>
       <c r="E29">
-        <v>6650.120718035036</v>
+        <v>7282.66974929483</v>
       </c>
       <c r="F29">
-        <v>17078.82384401444</v>
+        <v>17711.37287527423</v>
       </c>
       <c r="G29">
         <v>2748</v>
@@ -3671,28 +3671,28 @@
         <v>4533</v>
       </c>
       <c r="M29">
-        <v>927.380134729984</v>
+        <v>961.7275471273908</v>
       </c>
       <c r="N29">
-        <v>3605.619865270016</v>
+        <v>3571.272452872609</v>
       </c>
       <c r="O29">
-        <v>930.2499252396641</v>
+        <v>921.3882928411332</v>
       </c>
       <c r="P29">
-        <v>2675.369940030352</v>
+        <v>2649.884160031476</v>
       </c>
       <c r="Q29">
-        <v>2846.369940030352</v>
+        <v>2820.884160031476</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1371634902786268</v>
+        <v>0.1381755412759137</v>
       </c>
       <c r="T29">
-        <v>2.110011322832028</v>
+        <v>2.133384325078838</v>
       </c>
       <c r="U29">
         <v>0.0543</v>
@@ -3709,7 +3709,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>4.887963231301939</v>
+        <v>4.713393115898299</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3717,22 +3717,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1107677577186578</v>
+        <v>0.1105277055339181</v>
       </c>
       <c r="C30">
-        <v>48356.79168097601</v>
+        <v>47959.07476240161</v>
       </c>
       <c r="D30">
-        <v>63320.16455625024</v>
+        <v>63554.99666893564</v>
       </c>
       <c r="E30">
-        <v>7282.66974929483</v>
+        <v>7915.218780554627</v>
       </c>
       <c r="F30">
-        <v>17711.37287527423</v>
+        <v>18343.92190653403</v>
       </c>
       <c r="G30">
         <v>2748</v>
@@ -3753,28 +3753,28 @@
         <v>4533</v>
       </c>
       <c r="M30">
-        <v>961.7275471273908</v>
+        <v>996.0749595247978</v>
       </c>
       <c r="N30">
-        <v>3571.272452872609</v>
+        <v>3536.925040475202</v>
       </c>
       <c r="O30">
-        <v>921.3882928411332</v>
+        <v>912.5266604426022</v>
       </c>
       <c r="P30">
-        <v>2649.884160031476</v>
+        <v>2624.3983800326</v>
       </c>
       <c r="Q30">
-        <v>2820.884160031476</v>
+        <v>2795.3983800326</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1381755412759137</v>
+        <v>0.1392161007519973</v>
       </c>
       <c r="T30">
-        <v>2.133384325078838</v>
+        <v>2.157415721755134</v>
       </c>
       <c r="U30">
         <v>0.0543</v>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>4.713393115898299</v>
+        <v>4.550862318798355</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3799,22 +3799,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1105277055339181</v>
+        <v>0.1102876533491784</v>
       </c>
       <c r="C31">
-        <v>47959.07476240161</v>
+        <v>47563.10614629348</v>
       </c>
       <c r="D31">
-        <v>63554.99666893564</v>
+        <v>63791.57708408729</v>
       </c>
       <c r="E31">
-        <v>7915.218780554624</v>
+        <v>8547.767811814418</v>
       </c>
       <c r="F31">
-        <v>18343.92190653403</v>
+        <v>18976.47093779382</v>
       </c>
       <c r="G31">
         <v>2748</v>
@@ -3835,28 +3835,28 @@
         <v>4533</v>
       </c>
       <c r="M31">
-        <v>996.0749595247976</v>
+        <v>1030.422371922204</v>
       </c>
       <c r="N31">
-        <v>3536.925040475202</v>
+        <v>3502.577628077795</v>
       </c>
       <c r="O31">
-        <v>912.5266604426023</v>
+        <v>903.6650280440713</v>
       </c>
       <c r="P31">
-        <v>2624.3983800326</v>
+        <v>2598.912600033724</v>
       </c>
       <c r="Q31">
-        <v>2795.3983800326</v>
+        <v>2769.912600033724</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1392161007519973</v>
+        <v>0.1402863904988262</v>
       </c>
       <c r="T31">
-        <v>2.157415721755134</v>
+        <v>2.18213372976504</v>
       </c>
       <c r="U31">
         <v>0.0543</v>
@@ -3873,7 +3873,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>4.550862318798357</v>
+        <v>4.399166908171745</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3881,22 +3881,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1102876533491784</v>
+        <v>0.1100476011644386</v>
       </c>
       <c r="C32">
-        <v>47563.10614629348</v>
+        <v>47168.90542951525</v>
       </c>
       <c r="D32">
-        <v>63791.57708408729</v>
+        <v>64029.92539856886</v>
       </c>
       <c r="E32">
-        <v>8547.767811814418</v>
+        <v>9180.316843074212</v>
       </c>
       <c r="F32">
-        <v>18976.47093779382</v>
+        <v>19609.01996905361</v>
       </c>
       <c r="G32">
         <v>2748</v>
@@ -3917,28 +3917,28 @@
         <v>4533</v>
       </c>
       <c r="M32">
-        <v>1030.422371922204</v>
+        <v>1064.769784319611</v>
       </c>
       <c r="N32">
-        <v>3502.577628077795</v>
+        <v>3468.230215680389</v>
       </c>
       <c r="O32">
-        <v>903.6650280440713</v>
+        <v>894.8033956455404</v>
       </c>
       <c r="P32">
-        <v>2598.912600033724</v>
+        <v>2573.426820034849</v>
       </c>
       <c r="Q32">
-        <v>2769.912600033724</v>
+        <v>2744.426820034849</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1402863904988262</v>
+        <v>0.1413877031368676</v>
       </c>
       <c r="T32">
-        <v>2.18213372976504</v>
+        <v>2.207568201775233</v>
       </c>
       <c r="U32">
         <v>0.0543</v>
@@ -3955,7 +3955,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>4.399166908171745</v>
+        <v>4.257258298230721</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3963,22 +3963,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1100476011644386</v>
+        <v>0.1100449889796989</v>
       </c>
       <c r="C33">
-        <v>47168.90542951525</v>
+        <v>46538.95983856526</v>
       </c>
       <c r="D33">
-        <v>64029.92539856886</v>
+        <v>64032.52883887868</v>
       </c>
       <c r="E33">
-        <v>9180.316843074212</v>
+        <v>9812.865874334006</v>
       </c>
       <c r="F33">
-        <v>19609.01996905361</v>
+        <v>20241.56900031341</v>
       </c>
       <c r="G33">
         <v>2748</v>
@@ -3999,45 +3999,45 @@
         <v>4533</v>
       </c>
       <c r="M33">
-        <v>1064.769784319611</v>
+        <v>1119.358765717331</v>
       </c>
       <c r="N33">
-        <v>3468.230215680389</v>
+        <v>3413.641234282669</v>
       </c>
       <c r="O33">
-        <v>894.8033956455404</v>
+        <v>880.7194384449286</v>
       </c>
       <c r="P33">
-        <v>2573.426820034849</v>
+        <v>2532.92179583774</v>
       </c>
       <c r="Q33">
-        <v>2744.426820034849</v>
+        <v>2703.92179583774</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1413877031368676</v>
+        <v>0.1425214073230866</v>
       </c>
       <c r="T33">
-        <v>2.207568201775233</v>
+        <v>2.233750746491608</v>
       </c>
       <c r="U33">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V33">
         <v>0.258</v>
       </c>
       <c r="W33">
-        <v>0.0402906</v>
+        <v>0.0410326</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y33">
-        <v>4.257258298230721</v>
+        <v>4.049639971412621</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4045,22 +4045,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1100449889796989</v>
+        <v>0.1098123567949592</v>
       </c>
       <c r="C34">
-        <v>46538.95983856526</v>
+        <v>46139.11630080749</v>
       </c>
       <c r="D34">
-        <v>64032.52883887868</v>
+        <v>64265.23433238069</v>
       </c>
       <c r="E34">
-        <v>9812.865874334006</v>
+        <v>10445.4149055938</v>
       </c>
       <c r="F34">
-        <v>20241.56900031341</v>
+        <v>20874.1180315732</v>
       </c>
       <c r="G34">
         <v>2748</v>
@@ -4081,28 +4081,28 @@
         <v>4533</v>
       </c>
       <c r="M34">
-        <v>1119.358765717331</v>
+        <v>1154.338727145998</v>
       </c>
       <c r="N34">
-        <v>3413.641234282669</v>
+        <v>3378.661272854002</v>
       </c>
       <c r="O34">
-        <v>880.7194384449286</v>
+        <v>871.6946083963326</v>
       </c>
       <c r="P34">
-        <v>2532.92179583774</v>
+        <v>2506.96666445767</v>
       </c>
       <c r="Q34">
-        <v>2703.92179583774</v>
+        <v>2677.96666445767</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1425214073230866</v>
+        <v>0.1436889534253122</v>
       </c>
       <c r="T34">
-        <v>2.233750746491608</v>
+        <v>2.260714859706979</v>
       </c>
       <c r="U34">
         <v>0.0553</v>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>4.049639971412621</v>
+        <v>3.926923608642541</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4127,22 +4127,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1098123567949592</v>
+        <v>0.1095797246102194</v>
       </c>
       <c r="C35">
-        <v>46139.11630080749</v>
+        <v>45740.97031780353</v>
       </c>
       <c r="D35">
-        <v>64265.23433238069</v>
+        <v>64499.63738063653</v>
       </c>
       <c r="E35">
-        <v>10445.4149055938</v>
+        <v>11077.96393685359</v>
       </c>
       <c r="F35">
-        <v>20874.1180315732</v>
+        <v>21506.667062833</v>
       </c>
       <c r="G35">
         <v>2748</v>
@@ -4163,28 +4163,28 @@
         <v>4533</v>
       </c>
       <c r="M35">
-        <v>1154.338727145998</v>
+        <v>1189.318688574665</v>
       </c>
       <c r="N35">
-        <v>3378.661272854002</v>
+        <v>3343.681311425335</v>
       </c>
       <c r="O35">
-        <v>871.6946083963326</v>
+        <v>862.6697783477366</v>
       </c>
       <c r="P35">
-        <v>2506.96666445767</v>
+        <v>2481.011533077599</v>
       </c>
       <c r="Q35">
-        <v>2677.96666445767</v>
+        <v>2652.011533077599</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1436889534253122</v>
+        <v>0.1448918797124537</v>
       </c>
       <c r="T35">
-        <v>2.260714859706979</v>
+        <v>2.288496067262209</v>
       </c>
       <c r="U35">
         <v>0.0553</v>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>3.926923608642541</v>
+        <v>3.811425855447172</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4209,22 +4209,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1095797246102194</v>
+        <v>0.1093470924254797</v>
       </c>
       <c r="C36">
-        <v>45740.97031780353</v>
+        <v>45344.54053269765</v>
       </c>
       <c r="D36">
-        <v>64499.63738063653</v>
+        <v>64735.75662679045</v>
       </c>
       <c r="E36">
-        <v>11077.96393685359</v>
+        <v>11710.51296811339</v>
       </c>
       <c r="F36">
-        <v>21506.667062833</v>
+        <v>22139.21609409279</v>
       </c>
       <c r="G36">
         <v>2748</v>
@@ -4245,28 +4245,28 @@
         <v>4533</v>
       </c>
       <c r="M36">
-        <v>1189.318688574665</v>
+        <v>1224.298650003331</v>
       </c>
       <c r="N36">
-        <v>3343.681311425335</v>
+        <v>3308.701349996669</v>
       </c>
       <c r="O36">
-        <v>862.6697783477366</v>
+        <v>853.6449482991405</v>
       </c>
       <c r="P36">
-        <v>2481.011533077599</v>
+        <v>2455.056401697528</v>
       </c>
       <c r="Q36">
-        <v>2652.011533077599</v>
+        <v>2626.056401697528</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1448918797124537</v>
+        <v>0.1461318191161226</v>
       </c>
       <c r="T36">
-        <v>2.288496067262209</v>
+        <v>2.317132081203755</v>
       </c>
       <c r="U36">
         <v>0.0553</v>
@@ -4283,7 +4283,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>3.811425855447172</v>
+        <v>3.702527973862967</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1093470924254797</v>
+        <v>0.1091144602407399</v>
       </c>
       <c r="C37">
-        <v>45344.54053269765</v>
+        <v>44949.84586263134</v>
       </c>
       <c r="D37">
-        <v>64735.75662679045</v>
+        <v>64973.61098798392</v>
       </c>
       <c r="E37">
-        <v>11710.51296811339</v>
+        <v>12343.06199937319</v>
       </c>
       <c r="F37">
-        <v>22139.21609409279</v>
+        <v>22771.76512535259</v>
       </c>
       <c r="G37">
         <v>2748</v>
@@ -4327,28 +4327,28 @@
         <v>4533</v>
       </c>
       <c r="M37">
-        <v>1224.298650003331</v>
+        <v>1259.278611431998</v>
       </c>
       <c r="N37">
-        <v>3308.701349996669</v>
+        <v>3273.721388568002</v>
       </c>
       <c r="O37">
-        <v>853.6449482991405</v>
+        <v>844.6201182505446</v>
       </c>
       <c r="P37">
-        <v>2455.056401697528</v>
+        <v>2429.101270317457</v>
       </c>
       <c r="Q37">
-        <v>2626.056401697528</v>
+        <v>2600.101270317457</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1461318191161226</v>
+        <v>0.1474105066261562</v>
       </c>
       <c r="T37">
-        <v>2.317132081203755</v>
+        <v>2.346662970580974</v>
       </c>
       <c r="U37">
         <v>0.0553</v>
@@ -4365,7 +4365,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>3.702527973862967</v>
+        <v>3.599679974588995</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4373,22 +4373,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.10911446024074</v>
+        <v>0.1088818280560002</v>
       </c>
       <c r="C38">
-        <v>44949.84586263132</v>
+        <v>44556.90550379531</v>
       </c>
       <c r="D38">
-        <v>64973.6109879839</v>
+        <v>65213.21966040769</v>
       </c>
       <c r="E38">
-        <v>12343.06199937318</v>
+        <v>12975.61103063298</v>
       </c>
       <c r="F38">
-        <v>22771.76512535258</v>
+        <v>23404.31415661238</v>
       </c>
       <c r="G38">
         <v>2748</v>
@@ -4409,28 +4409,28 @@
         <v>4533</v>
       </c>
       <c r="M38">
-        <v>1259.278611431998</v>
+        <v>1294.258572860665</v>
       </c>
       <c r="N38">
-        <v>3273.721388568002</v>
+        <v>3238.741427139335</v>
       </c>
       <c r="O38">
-        <v>844.6201182505446</v>
+        <v>835.5952882019486</v>
       </c>
       <c r="P38">
-        <v>2429.101270317457</v>
+        <v>2403.146138937387</v>
       </c>
       <c r="Q38">
-        <v>2600.101270317457</v>
+        <v>2574.146138937387</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1474105066261562</v>
+        <v>0.1487297873904765</v>
       </c>
       <c r="T38">
-        <v>2.346662970580974</v>
+        <v>2.377131348509851</v>
       </c>
       <c r="U38">
         <v>0.0553</v>
@@ -4447,7 +4447,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>3.599679974588996</v>
+        <v>3.502391326627131</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4455,22 +4455,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1088818280560002</v>
+        <v>0.1086491958712605</v>
       </c>
       <c r="C39">
-        <v>44556.90550379531</v>
+        <v>44165.73893659421</v>
       </c>
       <c r="D39">
-        <v>65213.21966040769</v>
+        <v>65454.60212446639</v>
       </c>
       <c r="E39">
-        <v>12975.61103063298</v>
+        <v>13608.16006189277</v>
       </c>
       <c r="F39">
-        <v>23404.31415661238</v>
+        <v>24036.86318787217</v>
       </c>
       <c r="G39">
         <v>2748</v>
@@ -4491,28 +4491,28 @@
         <v>4533</v>
       </c>
       <c r="M39">
-        <v>1294.258572860665</v>
+        <v>1329.238534289331</v>
       </c>
       <c r="N39">
-        <v>3238.741427139335</v>
+        <v>3203.761465710669</v>
       </c>
       <c r="O39">
-        <v>835.5952882019486</v>
+        <v>826.5704581533525</v>
       </c>
       <c r="P39">
-        <v>2403.146138937387</v>
+        <v>2377.191007557316</v>
       </c>
       <c r="Q39">
-        <v>2574.146138937387</v>
+        <v>2548.191007557316</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1487297873904765</v>
+        <v>0.1500916255988072</v>
       </c>
       <c r="T39">
-        <v>2.377131348509851</v>
+        <v>2.408582577339659</v>
       </c>
       <c r="U39">
         <v>0.0553</v>
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>3.502391326627131</v>
+        <v>3.410223133821154</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4537,22 +4537,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1086491958712605</v>
+        <v>0.1084165636865207</v>
       </c>
       <c r="C40">
-        <v>44165.73893659421</v>
+        <v>43776.36593092595</v>
       </c>
       <c r="D40">
-        <v>65454.60212446639</v>
+        <v>65697.77815005791</v>
       </c>
       <c r="E40">
-        <v>13608.16006189277</v>
+        <v>14240.70909315256</v>
       </c>
       <c r="F40">
-        <v>24036.86318787217</v>
+        <v>24669.41221913197</v>
       </c>
       <c r="G40">
         <v>2748</v>
@@ -4573,28 +4573,28 @@
         <v>4533</v>
       </c>
       <c r="M40">
-        <v>1329.238534289331</v>
+        <v>1364.218495717998</v>
       </c>
       <c r="N40">
-        <v>3203.761465710669</v>
+        <v>3168.781504282002</v>
       </c>
       <c r="O40">
-        <v>826.5704581533525</v>
+        <v>817.5456281047566</v>
       </c>
       <c r="P40">
-        <v>2377.191007557316</v>
+        <v>2351.235876177246</v>
       </c>
       <c r="Q40">
-        <v>2548.191007557316</v>
+        <v>2522.235876177246</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1500916255988072</v>
+        <v>0.1514981142401979</v>
       </c>
       <c r="T40">
-        <v>2.408582577339659</v>
+        <v>2.441064993999952</v>
       </c>
       <c r="U40">
         <v>0.0553</v>
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>3.410223133821154</v>
+        <v>3.322781515005227</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4619,22 +4619,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1084165636865207</v>
+        <v>0.108183931501781</v>
       </c>
       <c r="C41">
-        <v>43776.36593092595</v>
+        <v>43388.80655157926</v>
       </c>
       <c r="D41">
-        <v>65697.77815005791</v>
+        <v>65942.76780197101</v>
       </c>
       <c r="E41">
-        <v>14240.70909315256</v>
+        <v>14873.25812441236</v>
       </c>
       <c r="F41">
-        <v>24669.41221913197</v>
+        <v>25301.96125039176</v>
       </c>
       <c r="G41">
         <v>2748</v>
@@ -4655,28 +4655,28 @@
         <v>4533</v>
       </c>
       <c r="M41">
-        <v>1364.218495717998</v>
+        <v>1399.198457146664</v>
       </c>
       <c r="N41">
-        <v>3168.781504282002</v>
+        <v>3133.801542853335</v>
       </c>
       <c r="O41">
-        <v>817.5456281047566</v>
+        <v>808.5207980561605</v>
       </c>
       <c r="P41">
-        <v>2351.235876177246</v>
+        <v>2325.280744797175</v>
       </c>
       <c r="Q41">
-        <v>2522.235876177246</v>
+        <v>2496.280744797175</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1514981142401979</v>
+        <v>0.1529514858363017</v>
       </c>
       <c r="T41">
-        <v>2.441064993999952</v>
+        <v>2.474630157882256</v>
       </c>
       <c r="U41">
         <v>0.0553</v>
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>3.322781515005227</v>
+        <v>3.239711977130096</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4701,22 +4701,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.108183931501781</v>
+        <v>0.1079512993170413</v>
       </c>
       <c r="C42">
-        <v>43388.80655157926</v>
+        <v>43003.08116375298</v>
       </c>
       <c r="D42">
-        <v>65942.76780197101</v>
+        <v>66189.59144540454</v>
       </c>
       <c r="E42">
-        <v>14873.25812441236</v>
+        <v>15505.80715567216</v>
       </c>
       <c r="F42">
-        <v>25301.96125039176</v>
+        <v>25934.51028165156</v>
       </c>
       <c r="G42">
         <v>2748</v>
@@ -4737,28 +4737,28 @@
         <v>4533</v>
       </c>
       <c r="M42">
-        <v>1399.198457146664</v>
+        <v>1434.178418575331</v>
       </c>
       <c r="N42">
-        <v>3133.801542853335</v>
+        <v>3098.821581424669</v>
       </c>
       <c r="O42">
-        <v>808.5207980561605</v>
+        <v>799.4959680075646</v>
       </c>
       <c r="P42">
-        <v>2325.280744797175</v>
+        <v>2299.325613417104</v>
       </c>
       <c r="Q42">
-        <v>2496.280744797175</v>
+        <v>2470.325613417104</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1529514858363017</v>
+        <v>0.1544541242661716</v>
       </c>
       <c r="T42">
-        <v>2.474630157882256</v>
+        <v>2.509333123930061</v>
       </c>
       <c r="U42">
         <v>0.0553</v>
@@ -4775,7 +4775,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>3.239711977130096</v>
+        <v>3.16069461183424</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4783,22 +4783,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1079512993170413</v>
+        <v>0.1077186671323015</v>
       </c>
       <c r="C43">
-        <v>43003.08116375298</v>
+        <v>42619.21043869888</v>
       </c>
       <c r="D43">
-        <v>66189.59144540454</v>
+        <v>66438.26975161023</v>
       </c>
       <c r="E43">
-        <v>15505.80715567216</v>
+        <v>16138.35618693195</v>
       </c>
       <c r="F43">
-        <v>25934.51028165156</v>
+        <v>26567.05931291135</v>
       </c>
       <c r="G43">
         <v>2748</v>
@@ -4819,28 +4819,28 @@
         <v>4533</v>
       </c>
       <c r="M43">
-        <v>1434.178418575331</v>
+        <v>1469.158380003998</v>
       </c>
       <c r="N43">
-        <v>3098.821581424669</v>
+        <v>3063.841619996002</v>
       </c>
       <c r="O43">
-        <v>799.4959680075646</v>
+        <v>790.4711379589685</v>
       </c>
       <c r="P43">
-        <v>2299.325613417104</v>
+        <v>2273.370482037034</v>
       </c>
       <c r="Q43">
-        <v>2470.325613417104</v>
+        <v>2444.370482037034</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1544541242661716</v>
+        <v>0.156008577814313</v>
       </c>
       <c r="T43">
-        <v>2.509333123930061</v>
+        <v>2.545232743979515</v>
       </c>
       <c r="U43">
         <v>0.0553</v>
@@ -4857,7 +4857,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>3.16069461183424</v>
+        <v>3.085439978219139</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4865,22 +4865,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1077186671323015</v>
+        <v>0.1074860349475618</v>
       </c>
       <c r="C44">
-        <v>42619.21043869886</v>
+        <v>42237.21535949296</v>
       </c>
       <c r="D44">
-        <v>66438.26975161021</v>
+        <v>66688.82370366409</v>
       </c>
       <c r="E44">
-        <v>16138.35618693195</v>
+        <v>16770.90521819174</v>
       </c>
       <c r="F44">
-        <v>26567.05931291135</v>
+        <v>27199.60834417114</v>
       </c>
       <c r="G44">
         <v>2748</v>
@@ -4901,28 +4901,28 @@
         <v>4533</v>
       </c>
       <c r="M44">
-        <v>1469.158380003998</v>
+        <v>1504.138341432664</v>
       </c>
       <c r="N44">
-        <v>3063.841619996002</v>
+        <v>3028.861658567336</v>
       </c>
       <c r="O44">
-        <v>790.4711379589687</v>
+        <v>781.4463079103726</v>
       </c>
       <c r="P44">
-        <v>2273.370482037034</v>
+        <v>2247.415350656963</v>
       </c>
       <c r="Q44">
-        <v>2444.370482037034</v>
+        <v>2418.415350656963</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.156008577814313</v>
+        <v>0.1576175735922137</v>
       </c>
       <c r="T44">
-        <v>2.545232743979515</v>
+        <v>2.582391999820177</v>
       </c>
       <c r="U44">
         <v>0.0553</v>
@@ -4939,7 +4939,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>3.085439978219139</v>
+        <v>3.01368556012102</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4947,22 +4947,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1074860349475618</v>
+        <v>0.1080696027628221</v>
       </c>
       <c r="C45">
-        <v>42237.21535949296</v>
+        <v>40979.683199639</v>
       </c>
       <c r="D45">
-        <v>66688.82370366409</v>
+        <v>66063.84057506993</v>
       </c>
       <c r="E45">
-        <v>16770.90521819174</v>
+        <v>17403.45424945153</v>
       </c>
       <c r="F45">
-        <v>27199.60834417114</v>
+        <v>27832.15737543094</v>
       </c>
       <c r="G45">
         <v>2748</v>
@@ -4983,45 +4983,45 @@
         <v>4533</v>
       </c>
       <c r="M45">
-        <v>1504.138341432664</v>
+        <v>1608.698696299908</v>
       </c>
       <c r="N45">
-        <v>3028.861658567336</v>
+        <v>2924.301303700092</v>
       </c>
       <c r="O45">
-        <v>781.4463079103726</v>
+        <v>754.4697363546237</v>
       </c>
       <c r="P45">
-        <v>2247.415350656963</v>
+        <v>2169.831567345468</v>
       </c>
       <c r="Q45">
-        <v>2418.415350656963</v>
+        <v>2340.831567345468</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1576175735922137</v>
+        <v>0.1592840335050394</v>
       </c>
       <c r="T45">
-        <v>2.582391999820177</v>
+        <v>2.620878371940863</v>
       </c>
       <c r="U45">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V45">
         <v>0.258</v>
       </c>
       <c r="W45">
-        <v>0.0410326</v>
+        <v>0.0428876</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y45">
-        <v>3.01368556012102</v>
+        <v>2.817805478692896</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5029,22 +5029,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1080696027628221</v>
+        <v>0.1078555205780823</v>
       </c>
       <c r="C46">
-        <v>40979.683199639</v>
+        <v>40575.04445244189</v>
       </c>
       <c r="D46">
-        <v>66063.84057506993</v>
+        <v>66291.75085913262</v>
       </c>
       <c r="E46">
-        <v>17403.45424945153</v>
+        <v>18036.00328071133</v>
       </c>
       <c r="F46">
-        <v>27832.15737543094</v>
+        <v>28464.70640669073</v>
       </c>
       <c r="G46">
         <v>2748</v>
@@ -5065,28 +5065,28 @@
         <v>4533</v>
       </c>
       <c r="M46">
-        <v>1608.698696299908</v>
+        <v>1645.260030306724</v>
       </c>
       <c r="N46">
-        <v>2924.301303700092</v>
+        <v>2887.739969693276</v>
       </c>
       <c r="O46">
-        <v>754.4697363546237</v>
+        <v>745.0369121808651</v>
       </c>
       <c r="P46">
-        <v>2169.831567345468</v>
+        <v>2142.703057512411</v>
       </c>
       <c r="Q46">
-        <v>2340.831567345468</v>
+        <v>2313.703057512411</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1592840335050394</v>
+        <v>0.1610110919601497</v>
       </c>
       <c r="T46">
-        <v>2.620878371940863</v>
+        <v>2.660764248502302</v>
       </c>
       <c r="U46">
         <v>0.0578</v>
@@ -5103,7 +5103,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>2.817805478692896</v>
+        <v>2.755187579166387</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5111,22 +5111,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1078555205780823</v>
+        <v>0.1076414383933426</v>
       </c>
       <c r="C47">
-        <v>40575.04445244189</v>
+        <v>40171.98366115279</v>
       </c>
       <c r="D47">
-        <v>66291.75085913262</v>
+        <v>66521.23909910332</v>
       </c>
       <c r="E47">
-        <v>18036.00328071133</v>
+        <v>18668.55231197112</v>
       </c>
       <c r="F47">
-        <v>28464.70640669073</v>
+        <v>29097.25543795052</v>
       </c>
       <c r="G47">
         <v>2748</v>
@@ -5147,28 +5147,28 @@
         <v>4533</v>
       </c>
       <c r="M47">
-        <v>1645.260030306724</v>
+        <v>1681.82136431354</v>
       </c>
       <c r="N47">
-        <v>2887.739969693276</v>
+        <v>2851.17863568646</v>
       </c>
       <c r="O47">
-        <v>745.0369121808651</v>
+        <v>735.6040880071066</v>
       </c>
       <c r="P47">
-        <v>2142.703057512411</v>
+        <v>2115.574547679353</v>
       </c>
       <c r="Q47">
-        <v>2313.703057512411</v>
+        <v>2286.574547679353</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1610110919601497</v>
+        <v>0.162802115543227</v>
       </c>
       <c r="T47">
-        <v>2.660764248502302</v>
+        <v>2.702127379751202</v>
       </c>
       <c r="U47">
         <v>0.0578</v>
@@ -5185,7 +5185,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>2.755187579166387</v>
+        <v>2.695292197010596</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5193,22 +5193,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1076414383933426</v>
+        <v>0.1074273562086028</v>
       </c>
       <c r="C48">
-        <v>40171.98366115279</v>
+        <v>39770.51727036401</v>
       </c>
       <c r="D48">
-        <v>66521.23909910332</v>
+        <v>66752.32173957433</v>
       </c>
       <c r="E48">
-        <v>18668.55231197112</v>
+        <v>19301.10134323092</v>
       </c>
       <c r="F48">
-        <v>29097.25543795052</v>
+        <v>29729.80446921032</v>
       </c>
       <c r="G48">
         <v>2748</v>
@@ -5229,28 +5229,28 @@
         <v>4533</v>
       </c>
       <c r="M48">
-        <v>1681.82136431354</v>
+        <v>1718.382698320357</v>
       </c>
       <c r="N48">
-        <v>2851.17863568646</v>
+        <v>2814.617301679643</v>
       </c>
       <c r="O48">
-        <v>735.6040880071066</v>
+        <v>726.171263833348</v>
       </c>
       <c r="P48">
-        <v>2115.574547679353</v>
+        <v>2088.446037846295</v>
       </c>
       <c r="Q48">
-        <v>2286.574547679353</v>
+        <v>2259.446037846295</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.162802115543227</v>
+        <v>0.1646607249218922</v>
       </c>
       <c r="T48">
-        <v>2.702127379751202</v>
+        <v>2.745051383877417</v>
       </c>
       <c r="U48">
         <v>0.0578</v>
@@ -5267,7 +5267,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>2.695292197010596</v>
+        <v>2.637945554521008</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5275,22 +5275,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1074273562086028</v>
+        <v>0.1072132740238631</v>
       </c>
       <c r="C49">
-        <v>39770.51727036401</v>
+        <v>39370.66195396631</v>
       </c>
       <c r="D49">
-        <v>66752.32173957433</v>
+        <v>66985.01545443642</v>
       </c>
       <c r="E49">
-        <v>19301.10134323092</v>
+        <v>19933.65037449071</v>
       </c>
       <c r="F49">
-        <v>29729.80446921032</v>
+        <v>30362.35350047012</v>
       </c>
       <c r="G49">
         <v>2748</v>
@@ -5311,28 +5311,28 @@
         <v>4533</v>
       </c>
       <c r="M49">
-        <v>1718.382698320357</v>
+        <v>1754.944032327173</v>
       </c>
       <c r="N49">
-        <v>2814.617301679643</v>
+        <v>2778.055967672827</v>
       </c>
       <c r="O49">
-        <v>726.171263833348</v>
+        <v>716.7384396595894</v>
       </c>
       <c r="P49">
-        <v>2088.446037846295</v>
+        <v>2061.317528013238</v>
       </c>
       <c r="Q49">
-        <v>2259.446037846295</v>
+        <v>2232.317528013238</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1646607249218922</v>
+        <v>0.1665908192766598</v>
       </c>
       <c r="T49">
-        <v>2.745051383877417</v>
+        <v>2.789626311239257</v>
       </c>
       <c r="U49">
         <v>0.0578</v>
@@ -5349,7 +5349,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>2.637945554521008</v>
+        <v>2.582988355468487</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1072132740238631</v>
+        <v>0.1069991918391234</v>
       </c>
       <c r="C50">
-        <v>39370.66195396634</v>
+        <v>38972.43461915976</v>
       </c>
       <c r="D50">
-        <v>66985.01545443645</v>
+        <v>67219.33715088967</v>
       </c>
       <c r="E50">
-        <v>19933.65037449071</v>
+        <v>20566.1994057505</v>
       </c>
       <c r="F50">
-        <v>30362.35350047011</v>
+        <v>30994.90253172991</v>
       </c>
       <c r="G50">
         <v>2748</v>
@@ -5393,28 +5393,28 @@
         <v>4533</v>
       </c>
       <c r="M50">
-        <v>1754.944032327173</v>
+        <v>1791.505366333989</v>
       </c>
       <c r="N50">
-        <v>2778.055967672827</v>
+        <v>2741.494633666011</v>
       </c>
       <c r="O50">
-        <v>716.7384396595894</v>
+        <v>707.3056154858309</v>
       </c>
       <c r="P50">
-        <v>2061.317528013238</v>
+        <v>2034.18901818018</v>
       </c>
       <c r="Q50">
-        <v>2232.317528013238</v>
+        <v>2205.18901818018</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1665908192766598</v>
+        <v>0.1685966036061243</v>
       </c>
       <c r="T50">
-        <v>2.789626311239257</v>
+        <v>2.835949274968228</v>
       </c>
       <c r="U50">
         <v>0.0578</v>
@@ -5431,7 +5431,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>2.582988355468487</v>
+        <v>2.530274307397702</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5439,22 +5439,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1069991918391234</v>
+        <v>0.1080836096543837</v>
       </c>
       <c r="C51">
-        <v>38972.43461915976</v>
+        <v>37169.53198859987</v>
       </c>
       <c r="D51">
-        <v>67219.33715088967</v>
+        <v>66048.98355158957</v>
       </c>
       <c r="E51">
-        <v>20566.1994057505</v>
+        <v>21198.7484370103</v>
       </c>
       <c r="F51">
-        <v>30994.90253172991</v>
+        <v>31627.4515629897</v>
       </c>
       <c r="G51">
         <v>2748</v>
@@ -5475,45 +5475,45 @@
         <v>4533</v>
       </c>
       <c r="M51">
-        <v>1791.505366333989</v>
+        <v>1938.762780811269</v>
       </c>
       <c r="N51">
-        <v>2741.494633666011</v>
+        <v>2594.237219188732</v>
       </c>
       <c r="O51">
-        <v>707.3056154858309</v>
+        <v>669.3132025506927</v>
       </c>
       <c r="P51">
-        <v>2034.18901818018</v>
+        <v>1924.924016638039</v>
       </c>
       <c r="Q51">
-        <v>2205.18901818018</v>
+        <v>2095.924016638039</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1685966036061243</v>
+        <v>0.1706826193087673</v>
       </c>
       <c r="T51">
-        <v>2.835949274968228</v>
+        <v>2.884125157246358</v>
       </c>
       <c r="U51">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V51">
         <v>0.258</v>
       </c>
       <c r="W51">
-        <v>0.0428876</v>
+        <v>0.0454846</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y51">
-        <v>2.530274307397702</v>
+        <v>2.338089035370889</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5521,22 +5521,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1080836096543837</v>
+        <v>0.1078954974696439</v>
       </c>
       <c r="C52">
-        <v>37169.53198859987</v>
+        <v>36737.07183820946</v>
       </c>
       <c r="D52">
-        <v>66048.98355158957</v>
+        <v>66249.07243245895</v>
       </c>
       <c r="E52">
-        <v>21198.7484370103</v>
+        <v>21831.29746827009</v>
       </c>
       <c r="F52">
-        <v>31627.4515629897</v>
+        <v>32260.00059424949</v>
       </c>
       <c r="G52">
         <v>2748</v>
@@ -5557,28 +5557,28 @@
         <v>4533</v>
       </c>
       <c r="M52">
-        <v>1938.762780811269</v>
+        <v>1977.538036427494</v>
       </c>
       <c r="N52">
-        <v>2594.237219188732</v>
+        <v>2555.461963572506</v>
       </c>
       <c r="O52">
-        <v>669.3132025506927</v>
+        <v>659.3091866017065</v>
       </c>
       <c r="P52">
-        <v>1924.924016638039</v>
+        <v>1896.152776970799</v>
       </c>
       <c r="Q52">
-        <v>2095.924016638039</v>
+        <v>2067.152776970799</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1706826193087673</v>
+        <v>0.1728537785094774</v>
       </c>
       <c r="T52">
-        <v>2.884125157246358</v>
+        <v>2.934267402066452</v>
       </c>
       <c r="U52">
         <v>0.0613</v>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>2.338089035370889</v>
+        <v>2.2922441523244</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5603,22 +5603,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1078954974696439</v>
+        <v>0.1087877372849042</v>
       </c>
       <c r="C53">
-        <v>36737.07183820946</v>
+        <v>35166.08522058367</v>
       </c>
       <c r="D53">
-        <v>66249.07243245895</v>
+        <v>65310.63484609296</v>
       </c>
       <c r="E53">
-        <v>21831.29746827009</v>
+        <v>22463.84649952989</v>
       </c>
       <c r="F53">
-        <v>32260.00059424949</v>
+        <v>32892.54962550929</v>
       </c>
       <c r="G53">
         <v>2748</v>
@@ -5639,45 +5639,45 @@
         <v>4533</v>
       </c>
       <c r="M53">
-        <v>1977.538036427494</v>
+        <v>2108.412430995145</v>
       </c>
       <c r="N53">
-        <v>2555.461963572506</v>
+        <v>2424.587569004855</v>
       </c>
       <c r="O53">
-        <v>659.3091866017065</v>
+        <v>625.5435928032525</v>
       </c>
       <c r="P53">
-        <v>1896.152776970799</v>
+        <v>1799.043976201602</v>
       </c>
       <c r="Q53">
-        <v>2067.152776970799</v>
+        <v>1970.043976201602</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1728537785094774</v>
+        <v>0.1751154026768837</v>
       </c>
       <c r="T53">
-        <v>2.934267402066452</v>
+        <v>2.986498907087384</v>
       </c>
       <c r="U53">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V53">
         <v>0.258</v>
       </c>
       <c r="W53">
-        <v>0.0454846</v>
+        <v>0.04756220000000001</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y53">
-        <v>2.2922441523244</v>
+        <v>2.149958866378187</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5685,22 +5685,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1087877372849042</v>
+        <v>0.1086204011001645</v>
       </c>
       <c r="C54">
-        <v>35166.08522058367</v>
+        <v>34707.50566845291</v>
       </c>
       <c r="D54">
-        <v>65310.63484609296</v>
+        <v>65484.604325222</v>
       </c>
       <c r="E54">
-        <v>22463.84649952989</v>
+        <v>23096.39553078968</v>
       </c>
       <c r="F54">
-        <v>32892.54962550929</v>
+        <v>33525.09865676909</v>
       </c>
       <c r="G54">
         <v>2748</v>
@@ -5721,28 +5721,28 @@
         <v>4533</v>
       </c>
       <c r="M54">
-        <v>2108.412430995145</v>
+        <v>2148.958823898899</v>
       </c>
       <c r="N54">
-        <v>2424.587569004855</v>
+        <v>2384.041176101101</v>
       </c>
       <c r="O54">
-        <v>625.5435928032525</v>
+        <v>615.0826234340842</v>
       </c>
       <c r="P54">
-        <v>1799.043976201602</v>
+        <v>1768.958552667017</v>
       </c>
       <c r="Q54">
-        <v>1970.043976201602</v>
+        <v>1939.958552667017</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1751154026768837</v>
+        <v>0.1774732661705627</v>
       </c>
       <c r="T54">
-        <v>2.986498907087384</v>
+        <v>3.040953029343248</v>
       </c>
       <c r="U54">
         <v>0.0641</v>
@@ -5759,7 +5759,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>2.149958866378187</v>
+        <v>2.109393604748409</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5767,22 +5767,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1086204011001645</v>
+        <v>0.1084530649154247</v>
       </c>
       <c r="C55">
-        <v>34707.50566845291</v>
+        <v>34249.85540490332</v>
       </c>
       <c r="D55">
-        <v>65484.604325222</v>
+        <v>65659.50309293219</v>
       </c>
       <c r="E55">
-        <v>23096.39553078968</v>
+        <v>23728.94456204947</v>
       </c>
       <c r="F55">
-        <v>33525.09865676909</v>
+        <v>34157.64768802888</v>
       </c>
       <c r="G55">
         <v>2748</v>
@@ -5803,28 +5803,28 @@
         <v>4533</v>
       </c>
       <c r="M55">
-        <v>2148.958823898899</v>
+        <v>2189.505216802651</v>
       </c>
       <c r="N55">
-        <v>2384.041176101101</v>
+        <v>2343.494783197349</v>
       </c>
       <c r="O55">
-        <v>615.0826234340842</v>
+        <v>604.6216540649161</v>
       </c>
       <c r="P55">
-        <v>1768.958552667017</v>
+        <v>1738.873129132433</v>
       </c>
       <c r="Q55">
-        <v>1939.958552667017</v>
+        <v>1909.873129132433</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1774732661705627</v>
+        <v>0.1799336454683146</v>
       </c>
       <c r="T55">
-        <v>3.040953029343248</v>
+        <v>3.097774722131976</v>
       </c>
       <c r="U55">
         <v>0.0641</v>
@@ -5841,7 +5841,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>2.109393604748409</v>
+        <v>2.070330760216032</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5849,22 +5849,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1084530649154247</v>
+        <v>0.108285728730685</v>
       </c>
       <c r="C56">
-        <v>34249.85540490332</v>
+        <v>33793.14189581265</v>
       </c>
       <c r="D56">
-        <v>65659.50309293219</v>
+        <v>65835.33861510133</v>
       </c>
       <c r="E56">
-        <v>23728.94456204947</v>
+        <v>24361.49359330927</v>
       </c>
       <c r="F56">
-        <v>34157.64768802888</v>
+        <v>34790.19671928867</v>
       </c>
       <c r="G56">
         <v>2748</v>
@@ -5885,28 +5885,28 @@
         <v>4533</v>
       </c>
       <c r="M56">
-        <v>2189.505216802651</v>
+        <v>2230.051609706404</v>
       </c>
       <c r="N56">
-        <v>2343.494783197349</v>
+        <v>2302.948390293596</v>
       </c>
       <c r="O56">
-        <v>604.6216540649161</v>
+        <v>594.1606846957477</v>
       </c>
       <c r="P56">
-        <v>1738.873129132433</v>
+        <v>1708.787705597848</v>
       </c>
       <c r="Q56">
-        <v>1909.873129132433</v>
+        <v>1879.787705597848</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1799336454683146</v>
+        <v>0.1825033749570777</v>
       </c>
       <c r="T56">
-        <v>3.097774722131976</v>
+        <v>3.157121823489093</v>
       </c>
       <c r="U56">
         <v>0.0641</v>
@@ -5923,7 +5923,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>2.070330760216032</v>
+        <v>2.032688382757558</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5931,22 +5931,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.108285728730685</v>
+        <v>0.1113594485459452</v>
       </c>
       <c r="C57">
-        <v>33793.14189581265</v>
+        <v>30073.93809039337</v>
       </c>
       <c r="D57">
-        <v>65835.33861510133</v>
+        <v>62748.68384094183</v>
       </c>
       <c r="E57">
-        <v>24361.49359330927</v>
+        <v>24994.04262456906</v>
       </c>
       <c r="F57">
-        <v>34790.19671928867</v>
+        <v>35422.74575054846</v>
       </c>
       <c r="G57">
         <v>2748</v>
@@ -5967,45 +5967,45 @@
         <v>4533</v>
       </c>
       <c r="M57">
-        <v>2230.051609706404</v>
+        <v>2546.895419464435</v>
       </c>
       <c r="N57">
-        <v>2302.948390293596</v>
+        <v>1986.104580535565</v>
       </c>
       <c r="O57">
-        <v>594.1606846957477</v>
+        <v>512.4149817781758</v>
       </c>
       <c r="P57">
-        <v>1708.787705597848</v>
+        <v>1473.689598757389</v>
       </c>
       <c r="Q57">
-        <v>1879.787705597848</v>
+        <v>1644.689598757389</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1825033749570777</v>
+        <v>0.1851899103316937</v>
       </c>
       <c r="T57">
-        <v>3.157121823489093</v>
+        <v>3.219166520362442</v>
       </c>
       <c r="U57">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V57">
         <v>0.258</v>
       </c>
       <c r="W57">
-        <v>0.04756220000000001</v>
+        <v>0.0533498</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y57">
-        <v>2.032688382757558</v>
+        <v>1.779813951274531</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6013,22 +6013,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1113594485459452</v>
+        <v>0.1128994543612055</v>
       </c>
       <c r="C58">
-        <v>30073.93809039337</v>
+        <v>28001.23818257371</v>
       </c>
       <c r="D58">
-        <v>62748.68384094183</v>
+        <v>61308.53296438197</v>
       </c>
       <c r="E58">
-        <v>24994.04262456906</v>
+        <v>25626.59165582886</v>
       </c>
       <c r="F58">
-        <v>35422.74575054846</v>
+        <v>36055.29478180826</v>
       </c>
       <c r="G58">
         <v>2748</v>
@@ -6049,45 +6049,45 @@
         <v>4533</v>
       </c>
       <c r="M58">
-        <v>2546.895419464435</v>
+        <v>2732.991344461067</v>
       </c>
       <c r="N58">
-        <v>1986.104580535565</v>
+        <v>1800.008655538933</v>
       </c>
       <c r="O58">
-        <v>512.4149817781758</v>
+        <v>464.4022331290448</v>
       </c>
       <c r="P58">
-        <v>1473.689598757389</v>
+        <v>1335.606422409889</v>
       </c>
       <c r="Q58">
-        <v>1644.689598757389</v>
+        <v>1506.606422409889</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1851899103316937</v>
+        <v>0.1880014008400128</v>
       </c>
       <c r="T58">
-        <v>3.219166520362442</v>
+        <v>3.284097017090365</v>
       </c>
       <c r="U58">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V58">
         <v>0.258</v>
       </c>
       <c r="W58">
-        <v>0.0533498</v>
+        <v>0.0562436</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y58">
-        <v>1.779813951274531</v>
+        <v>1.658622157434563</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6095,22 +6095,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1128994543612055</v>
+        <v>0.1128189321764658</v>
       </c>
       <c r="C59">
-        <v>28001.23818257371</v>
+        <v>27442.35038191187</v>
       </c>
       <c r="D59">
-        <v>61308.53296438197</v>
+        <v>61382.19419497993</v>
       </c>
       <c r="E59">
-        <v>25626.59165582886</v>
+        <v>26259.14068708866</v>
       </c>
       <c r="F59">
-        <v>36055.29478180826</v>
+        <v>36687.84381306806</v>
       </c>
       <c r="G59">
         <v>2748</v>
@@ -6131,28 +6131,28 @@
         <v>4533</v>
       </c>
       <c r="M59">
-        <v>2732.991344461067</v>
+        <v>2780.938561030559</v>
       </c>
       <c r="N59">
-        <v>1800.008655538933</v>
+        <v>1752.061438969441</v>
       </c>
       <c r="O59">
-        <v>464.4022331290448</v>
+        <v>452.0318512541158</v>
       </c>
       <c r="P59">
-        <v>1335.606422409889</v>
+        <v>1300.029587715325</v>
       </c>
       <c r="Q59">
-        <v>1506.606422409889</v>
+        <v>1471.029587715325</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1880014008400128</v>
+        <v>0.190946771848728</v>
       </c>
       <c r="T59">
-        <v>3.284097017090365</v>
+        <v>3.352119442233904</v>
       </c>
       <c r="U59">
         <v>0.07580000000000001</v>
@@ -6169,7 +6169,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>1.658622157434563</v>
+        <v>1.630025223685691</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6177,22 +6177,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1128189321764658</v>
+        <v>0.112738409991726</v>
       </c>
       <c r="C60">
-        <v>27442.35038191188</v>
+        <v>26883.63979977735</v>
       </c>
       <c r="D60">
-        <v>61382.19419497993</v>
+        <v>61456.03264410519</v>
       </c>
       <c r="E60">
-        <v>26259.14068708865</v>
+        <v>26891.68971834844</v>
       </c>
       <c r="F60">
-        <v>36687.84381306805</v>
+        <v>37320.39284432784</v>
       </c>
       <c r="G60">
         <v>2748</v>
@@ -6213,28 +6213,28 @@
         <v>4533</v>
       </c>
       <c r="M60">
-        <v>2780.938561030559</v>
+        <v>2828.88577760005</v>
       </c>
       <c r="N60">
-        <v>1752.061438969441</v>
+        <v>1704.11422239995</v>
       </c>
       <c r="O60">
-        <v>452.0318512541159</v>
+        <v>439.661469379187</v>
       </c>
       <c r="P60">
-        <v>1300.029587715326</v>
+        <v>1264.452753020762</v>
       </c>
       <c r="Q60">
-        <v>1471.029587715326</v>
+        <v>1435.452753020762</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.190946771848728</v>
+        <v>0.1940358194920147</v>
       </c>
       <c r="T60">
-        <v>3.352119442233903</v>
+        <v>3.423460034457614</v>
       </c>
       <c r="U60">
         <v>0.07580000000000001</v>
@@ -6251,7 +6251,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>1.630025223685691</v>
+        <v>1.602397677521527</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6259,22 +6259,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.112738409991726</v>
+        <v>0.1126578878069863</v>
       </c>
       <c r="C61">
-        <v>26883.63979977735</v>
+        <v>26325.10707648446</v>
       </c>
       <c r="D61">
-        <v>61456.03264410519</v>
+        <v>61530.04895207209</v>
       </c>
       <c r="E61">
-        <v>26891.68971834844</v>
+        <v>27524.23874960824</v>
       </c>
       <c r="F61">
-        <v>37320.39284432784</v>
+        <v>37952.94187558764</v>
       </c>
       <c r="G61">
         <v>2748</v>
@@ -6295,28 +6295,28 @@
         <v>4533</v>
       </c>
       <c r="M61">
-        <v>2828.88577760005</v>
+        <v>2876.832994169543</v>
       </c>
       <c r="N61">
-        <v>1704.11422239995</v>
+        <v>1656.167005830457</v>
       </c>
       <c r="O61">
-        <v>439.661469379187</v>
+        <v>427.2910875042579</v>
       </c>
       <c r="P61">
-        <v>1264.452753020762</v>
+        <v>1228.875918326199</v>
       </c>
       <c r="Q61">
-        <v>1435.452753020762</v>
+        <v>1399.875918326199</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1940358194920147</v>
+        <v>0.1972793195174657</v>
       </c>
       <c r="T61">
-        <v>3.423460034457614</v>
+        <v>3.49836765629251</v>
       </c>
       <c r="U61">
         <v>0.07580000000000001</v>
@@ -6333,7 +6333,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>1.602397677521527</v>
+        <v>1.575691049562835</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6341,22 +6341,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1126578878069863</v>
+        <v>0.1125773656222465</v>
       </c>
       <c r="C62">
-        <v>26325.10707648446</v>
+        <v>25766.75285543613</v>
       </c>
       <c r="D62">
-        <v>61530.04895207209</v>
+        <v>61604.24376228356</v>
       </c>
       <c r="E62">
-        <v>27524.23874960824</v>
+        <v>28156.78778086803</v>
       </c>
       <c r="F62">
-        <v>37952.94187558764</v>
+        <v>38585.49090684743</v>
       </c>
       <c r="G62">
         <v>2748</v>
@@ -6377,28 +6377,28 @@
         <v>4533</v>
       </c>
       <c r="M62">
-        <v>2876.832994169543</v>
+        <v>2924.780210739035</v>
       </c>
       <c r="N62">
-        <v>1656.167005830457</v>
+        <v>1608.219789260965</v>
       </c>
       <c r="O62">
-        <v>427.2910875042579</v>
+        <v>414.9207056293289</v>
       </c>
       <c r="P62">
-        <v>1228.875918326199</v>
+        <v>1193.299083631636</v>
       </c>
       <c r="Q62">
-        <v>1399.875918326199</v>
+        <v>1364.299083631636</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1972793195174657</v>
+        <v>0.2006891528775553</v>
       </c>
       <c r="T62">
-        <v>3.49836765629251</v>
+        <v>3.577116694631761</v>
       </c>
       <c r="U62">
         <v>0.07580000000000001</v>
@@ -6415,7 +6415,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>1.575691049562835</v>
+        <v>1.549860048750329</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1125773656222465</v>
+        <v>0.1124968434375068</v>
       </c>
       <c r="C63">
-        <v>25766.75285543613</v>
+        <v>25208.57778314226</v>
       </c>
       <c r="D63">
-        <v>61604.24376228356</v>
+        <v>61678.61772124949</v>
       </c>
       <c r="E63">
-        <v>28156.78778086803</v>
+        <v>28789.33681212783</v>
       </c>
       <c r="F63">
-        <v>38585.49090684743</v>
+        <v>39218.03993810723</v>
       </c>
       <c r="G63">
         <v>2748</v>
@@ -6459,28 +6459,28 @@
         <v>4533</v>
       </c>
       <c r="M63">
-        <v>2924.780210739035</v>
+        <v>2972.727427308528</v>
       </c>
       <c r="N63">
-        <v>1608.219789260965</v>
+        <v>1560.272572691472</v>
       </c>
       <c r="O63">
-        <v>414.9207056293289</v>
+        <v>402.5503237543998</v>
       </c>
       <c r="P63">
-        <v>1193.299083631636</v>
+        <v>1157.722248937072</v>
       </c>
       <c r="Q63">
-        <v>1364.299083631636</v>
+        <v>1328.722248937072</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.2006891528775553</v>
+        <v>0.2042784511513337</v>
       </c>
       <c r="T63">
-        <v>3.577116694631761</v>
+        <v>3.660010419199393</v>
       </c>
       <c r="U63">
         <v>0.07580000000000001</v>
@@ -6497,7 +6497,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>1.549860048750329</v>
+        <v>1.52486230602855</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6505,22 +6505,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1124968434375068</v>
+        <v>0.1124163212527671</v>
       </c>
       <c r="C64">
-        <v>25208.57778314226</v>
+        <v>24650.58250923869</v>
       </c>
       <c r="D64">
-        <v>61678.61772124949</v>
+        <v>61753.17147860571</v>
       </c>
       <c r="E64">
-        <v>28789.33681212783</v>
+        <v>29421.88584338762</v>
       </c>
       <c r="F64">
-        <v>39218.03993810723</v>
+        <v>39850.58896936703</v>
       </c>
       <c r="G64">
         <v>2748</v>
@@ -6541,28 +6541,28 @@
         <v>4533</v>
       </c>
       <c r="M64">
-        <v>2972.727427308528</v>
+        <v>3020.674643878021</v>
       </c>
       <c r="N64">
-        <v>1560.272572691472</v>
+        <v>1512.325356121979</v>
       </c>
       <c r="O64">
-        <v>402.5503237543998</v>
+        <v>390.1799418794707</v>
       </c>
       <c r="P64">
-        <v>1157.722248937072</v>
+        <v>1122.145414242509</v>
       </c>
       <c r="Q64">
-        <v>1328.722248937072</v>
+        <v>1293.145414242509</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.2042784511513337</v>
+        <v>0.2080617655480191</v>
       </c>
       <c r="T64">
-        <v>3.660010419199393</v>
+        <v>3.747384885635546</v>
       </c>
       <c r="U64">
         <v>0.07580000000000001</v>
@@ -6579,7 +6579,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>1.52486230602855</v>
+        <v>1.500658142440795</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6587,22 +6587,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1124163212527671</v>
+        <v>0.1344164667207233</v>
       </c>
       <c r="C65">
-        <v>24650.58250923869</v>
+        <v>8687.036814361512</v>
       </c>
       <c r="D65">
-        <v>61753.17147860571</v>
+        <v>46422.17481498833</v>
       </c>
       <c r="E65">
-        <v>29421.88584338762</v>
+        <v>30054.43487464741</v>
       </c>
       <c r="F65">
-        <v>39850.58896936703</v>
+        <v>40483.13800062682</v>
       </c>
       <c r="G65">
         <v>2748</v>
@@ -6623,45 +6623,45 @@
         <v>4533</v>
       </c>
       <c r="M65">
-        <v>3020.674643878021</v>
+        <v>4801.300166874341</v>
       </c>
       <c r="N65">
-        <v>1512.325356121979</v>
+        <v>-268.3001668743409</v>
       </c>
       <c r="O65">
-        <v>390.1799418794707</v>
+        <v>-69.22144305357996</v>
       </c>
       <c r="P65">
-        <v>1122.145414242509</v>
+        <v>-199.078723820761</v>
       </c>
       <c r="Q65">
-        <v>1293.145414242509</v>
+        <v>-28.07872382076096</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.2080617655480191</v>
+        <v>0.2138927038492379</v>
       </c>
       <c r="T65">
-        <v>3.747384885635546</v>
+        <v>3.882048587742215</v>
       </c>
       <c r="U65">
-        <v>0.07580000000000001</v>
+        <v>0.1186</v>
       </c>
       <c r="V65">
-        <v>0.258</v>
+        <v>0.2435827711978601</v>
       </c>
       <c r="W65">
-        <v>0.0562436</v>
+        <v>0.08971108333593381</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y65">
-        <v>1.500658142440795</v>
+        <v>0.94411926820876</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6669,22 +6669,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1344164667207233</v>
+        <v>0.1351444667207233</v>
       </c>
       <c r="C66">
-        <v>8687.036814361512</v>
+        <v>7676.228843228571</v>
       </c>
       <c r="D66">
-        <v>46422.17481498833</v>
+        <v>46043.91587511518</v>
       </c>
       <c r="E66">
-        <v>30054.43487464741</v>
+        <v>30686.98390590721</v>
       </c>
       <c r="F66">
-        <v>40483.13800062682</v>
+        <v>41115.68703188661</v>
       </c>
       <c r="G66">
         <v>2748</v>
@@ -6705,37 +6705,37 @@
         <v>4533</v>
       </c>
       <c r="M66">
-        <v>4801.300166874341</v>
+        <v>4876.320481981753</v>
       </c>
       <c r="N66">
-        <v>-268.3001668743409</v>
+        <v>-343.3204819817529</v>
       </c>
       <c r="O66">
-        <v>-69.22144305357996</v>
+        <v>-88.57668435129224</v>
       </c>
       <c r="P66">
-        <v>-199.078723820761</v>
+        <v>-254.7437976304606</v>
       </c>
       <c r="Q66">
-        <v>-28.07872382076096</v>
+        <v>-83.74379763046065</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2138927038492379</v>
+        <v>0.2186953525306447</v>
       </c>
       <c r="T66">
-        <v>3.882048587742215</v>
+        <v>3.992964261677706</v>
       </c>
       <c r="U66">
         <v>0.1186</v>
       </c>
       <c r="V66">
-        <v>0.2435827711978601</v>
+        <v>0.2398353439486622</v>
       </c>
       <c r="W66">
-        <v>0.08971108333593381</v>
+        <v>0.09015552820768867</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6743,7 +6743,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.94411926820876</v>
+        <v>0.9295943563901636</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6751,22 +6751,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1351444667207233</v>
+        <v>0.1358724667207233</v>
       </c>
       <c r="C67">
-        <v>7676.228843228571</v>
+        <v>6671.535337886424</v>
       </c>
       <c r="D67">
-        <v>46043.91587511518</v>
+        <v>45671.77140103283</v>
       </c>
       <c r="E67">
-        <v>30686.98390590721</v>
+        <v>31319.532937167</v>
       </c>
       <c r="F67">
-        <v>41115.68703188661</v>
+        <v>41748.2360631464</v>
       </c>
       <c r="G67">
         <v>2748</v>
@@ -6787,37 +6787,37 @@
         <v>4533</v>
       </c>
       <c r="M67">
-        <v>4876.320481981753</v>
+        <v>4951.340797089164</v>
       </c>
       <c r="N67">
-        <v>-343.3204819817529</v>
+        <v>-418.340797089164</v>
       </c>
       <c r="O67">
-        <v>-88.57668435129224</v>
+        <v>-107.9319256490043</v>
       </c>
       <c r="P67">
-        <v>-254.7437976304606</v>
+        <v>-310.4088714401597</v>
       </c>
       <c r="Q67">
-        <v>-83.74379763046065</v>
+        <v>-139.4088714401597</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2186953525306447</v>
+        <v>0.2237805099580166</v>
       </c>
       <c r="T67">
-        <v>3.992964261677706</v>
+        <v>4.110404387021169</v>
       </c>
       <c r="U67">
         <v>0.1186</v>
       </c>
       <c r="V67">
-        <v>0.2398353439486622</v>
+        <v>0.2362014751009552</v>
       </c>
       <c r="W67">
-        <v>0.09015552820768867</v>
+        <v>0.09058650505302672</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6825,7 +6825,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.9295943563901636</v>
+        <v>0.9155095934145552</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6833,22 +6833,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1358724667207233</v>
+        <v>0.1366004667207233</v>
       </c>
       <c r="C68">
-        <v>6671.535337886424</v>
+        <v>5672.809228680351</v>
       </c>
       <c r="D68">
-        <v>45671.77140103283</v>
+        <v>45305.59432308655</v>
       </c>
       <c r="E68">
-        <v>31319.532937167</v>
+        <v>31952.0819684268</v>
       </c>
       <c r="F68">
-        <v>41748.2360631464</v>
+        <v>42380.7850944062</v>
       </c>
       <c r="G68">
         <v>2748</v>
@@ -6869,37 +6869,37 @@
         <v>4533</v>
       </c>
       <c r="M68">
-        <v>4951.340797089164</v>
+        <v>5026.361112196576</v>
       </c>
       <c r="N68">
-        <v>-418.340797089164</v>
+        <v>-493.361112196576</v>
       </c>
       <c r="O68">
-        <v>-107.9319256490043</v>
+        <v>-127.2871669467166</v>
       </c>
       <c r="P68">
-        <v>-310.4088714401597</v>
+        <v>-366.0739452498594</v>
       </c>
       <c r="Q68">
-        <v>-139.4088714401597</v>
+        <v>-195.0739452498594</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2237805099580166</v>
+        <v>0.2291738587446232</v>
       </c>
       <c r="T68">
-        <v>4.110404387021169</v>
+        <v>4.23496209571878</v>
       </c>
       <c r="U68">
         <v>0.1186</v>
       </c>
       <c r="V68">
-        <v>0.2362014751009552</v>
+        <v>0.2326760799501947</v>
       </c>
       <c r="W68">
-        <v>0.09058650505302672</v>
+        <v>0.09100461691790691</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.9155095934145552</v>
+        <v>0.9018452711247856</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6915,22 +6915,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1366004667207233</v>
+        <v>0.1373284667207233</v>
       </c>
       <c r="C69">
-        <v>5672.809228680351</v>
+        <v>4679.908125011818</v>
       </c>
       <c r="D69">
-        <v>45305.59432308655</v>
+        <v>44945.24225067781</v>
       </c>
       <c r="E69">
-        <v>31952.0819684268</v>
+        <v>32584.63099968659</v>
       </c>
       <c r="F69">
-        <v>42380.7850944062</v>
+        <v>43013.33412566599</v>
       </c>
       <c r="G69">
         <v>2748</v>
@@ -6951,37 +6951,37 @@
         <v>4533</v>
       </c>
       <c r="M69">
-        <v>5026.361112196576</v>
+        <v>5101.381427303987</v>
       </c>
       <c r="N69">
-        <v>-493.361112196576</v>
+        <v>-568.381427303987</v>
       </c>
       <c r="O69">
-        <v>-127.2871669467166</v>
+        <v>-146.6424082444287</v>
       </c>
       <c r="P69">
-        <v>-366.0739452498594</v>
+        <v>-421.7390190595584</v>
       </c>
       <c r="Q69">
-        <v>-195.0739452498594</v>
+        <v>-250.7390190595584</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2291738587446232</v>
+        <v>0.2349042918303927</v>
       </c>
       <c r="T69">
-        <v>4.23496209571878</v>
+        <v>4.367304661209992</v>
       </c>
       <c r="U69">
         <v>0.1186</v>
       </c>
       <c r="V69">
-        <v>0.2326760799501947</v>
+        <v>0.2292543728921036</v>
       </c>
       <c r="W69">
-        <v>0.09100461691790691</v>
+        <v>0.09141043137499652</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6989,7 +6989,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.9018452711247856</v>
+        <v>0.8885828406670683</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6997,22 +6997,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1373284667207233</v>
+        <v>0.1380564667207232</v>
       </c>
       <c r="C70">
-        <v>4679.908125011818</v>
+        <v>3692.694130725198</v>
       </c>
       <c r="D70">
-        <v>44945.24225067781</v>
+        <v>44590.57728765099</v>
       </c>
       <c r="E70">
-        <v>32584.63099968659</v>
+        <v>33217.18003094639</v>
       </c>
       <c r="F70">
-        <v>43013.33412566599</v>
+        <v>43645.88315692579</v>
       </c>
       <c r="G70">
         <v>2748</v>
@@ -7033,37 +7033,37 @@
         <v>4533</v>
       </c>
       <c r="M70">
-        <v>5101.381427303987</v>
+        <v>5176.401742411399</v>
       </c>
       <c r="N70">
-        <v>-568.381427303987</v>
+        <v>-643.401742411399</v>
       </c>
       <c r="O70">
-        <v>-146.6424082444287</v>
+        <v>-165.9976495421409</v>
       </c>
       <c r="P70">
-        <v>-421.7390190595584</v>
+        <v>-477.4040928692581</v>
       </c>
       <c r="Q70">
-        <v>-250.7390190595584</v>
+        <v>-306.4040928692581</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2349042918303927</v>
+        <v>0.2410044302765343</v>
       </c>
       <c r="T70">
-        <v>4.367304661209992</v>
+        <v>4.508185456732894</v>
       </c>
       <c r="U70">
         <v>0.1186</v>
       </c>
       <c r="V70">
-        <v>0.2292543728921036</v>
+        <v>0.2259318457487398</v>
       </c>
       <c r="W70">
-        <v>0.09141043137499652</v>
+        <v>0.09180448309419946</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.8885828406670683</v>
+        <v>0.8757048284834875</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7079,22 +7079,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1380564667207232</v>
+        <v>0.1387844667207233</v>
       </c>
       <c r="C71">
-        <v>3692.694130725198</v>
+        <v>2711.033668166776</v>
       </c>
       <c r="D71">
-        <v>44590.57728765099</v>
+        <v>44241.46585635236</v>
       </c>
       <c r="E71">
-        <v>33217.18003094639</v>
+        <v>33849.72906220618</v>
       </c>
       <c r="F71">
-        <v>43645.88315692579</v>
+        <v>44278.43218818559</v>
       </c>
       <c r="G71">
         <v>2748</v>
@@ -7115,37 +7115,37 @@
         <v>4533</v>
       </c>
       <c r="M71">
-        <v>5176.401742411399</v>
+        <v>5251.422057518811</v>
       </c>
       <c r="N71">
-        <v>-643.401742411399</v>
+        <v>-718.422057518811</v>
       </c>
       <c r="O71">
-        <v>-165.9976495421409</v>
+        <v>-185.3528908398532</v>
       </c>
       <c r="P71">
-        <v>-477.4040928692581</v>
+        <v>-533.0691666789578</v>
       </c>
       <c r="Q71">
-        <v>-306.4040928692581</v>
+        <v>-362.0691666789578</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2410044302765343</v>
+        <v>0.2475112446190855</v>
       </c>
       <c r="T71">
-        <v>4.508185456732894</v>
+        <v>4.658458305290658</v>
       </c>
       <c r="U71">
         <v>0.1186</v>
       </c>
       <c r="V71">
-        <v>0.2259318457487398</v>
+        <v>0.2227042479523292</v>
       </c>
       <c r="W71">
-        <v>0.09180448309419946</v>
+        <v>0.09218727619285376</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7153,7 +7153,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.8757048284834875</v>
+        <v>0.8631947595051519</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7161,22 +7161,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1387844667207233</v>
+        <v>0.1395124667207233</v>
       </c>
       <c r="C72">
-        <v>2711.033668166776</v>
+        <v>1734.797310444774</v>
       </c>
       <c r="D72">
-        <v>44241.46585635236</v>
+        <v>43897.77852989015</v>
       </c>
       <c r="E72">
-        <v>33849.72906220618</v>
+        <v>34482.27809346597</v>
       </c>
       <c r="F72">
-        <v>44278.43218818559</v>
+        <v>44910.98121944538</v>
       </c>
       <c r="G72">
         <v>2748</v>
@@ -7197,37 +7197,37 @@
         <v>4533</v>
       </c>
       <c r="M72">
-        <v>5251.422057518811</v>
+        <v>5326.442372626222</v>
       </c>
       <c r="N72">
-        <v>-718.422057518811</v>
+        <v>-793.4423726262221</v>
       </c>
       <c r="O72">
-        <v>-185.3528908398532</v>
+        <v>-204.7081321375653</v>
       </c>
       <c r="P72">
-        <v>-533.0691666789578</v>
+        <v>-588.7342404886567</v>
       </c>
       <c r="Q72">
-        <v>-362.0691666789578</v>
+        <v>-417.7342404886567</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2475112446190855</v>
+        <v>0.2544668047783643</v>
       </c>
       <c r="T72">
-        <v>4.658458305290658</v>
+        <v>4.819094798576543</v>
       </c>
       <c r="U72">
         <v>0.1186</v>
       </c>
       <c r="V72">
-        <v>0.2227042479523292</v>
+        <v>0.2195675684037049</v>
       </c>
       <c r="W72">
-        <v>0.09218727619285376</v>
+        <v>0.09255928638732061</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7235,7 +7235,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.8631947595051519</v>
+        <v>0.8510370868360653</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7243,22 +7243,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1395124667207233</v>
+        <v>0.1402404667207233</v>
       </c>
       <c r="C73">
-        <v>1734.797310444781</v>
+        <v>763.8596214471472</v>
       </c>
       <c r="D73">
-        <v>43897.77852989015</v>
+        <v>43559.38987215231</v>
       </c>
       <c r="E73">
-        <v>34482.27809346597</v>
+        <v>35114.82712472577</v>
       </c>
       <c r="F73">
-        <v>44910.98121944537</v>
+        <v>45543.53025070517</v>
       </c>
       <c r="G73">
         <v>2748</v>
@@ -7279,37 +7279,37 @@
         <v>4533</v>
       </c>
       <c r="M73">
-        <v>5326.442372626221</v>
+        <v>5401.462687733633</v>
       </c>
       <c r="N73">
-        <v>-793.4423726262212</v>
+        <v>-868.4626877336332</v>
       </c>
       <c r="O73">
-        <v>-204.7081321375651</v>
+        <v>-224.0633734352774</v>
       </c>
       <c r="P73">
-        <v>-588.7342404886562</v>
+        <v>-644.3993142983559</v>
       </c>
       <c r="Q73">
-        <v>-417.7342404886562</v>
+        <v>-473.3993142983559</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2544668047783643</v>
+        <v>0.2619191906633058</v>
       </c>
       <c r="T73">
-        <v>4.819094798576542</v>
+        <v>4.991205327097132</v>
       </c>
       <c r="U73">
         <v>0.1186</v>
       </c>
       <c r="V73">
-        <v>0.2195675684037049</v>
+        <v>0.2165180188425423</v>
       </c>
       <c r="W73">
-        <v>0.09255928638732061</v>
+        <v>0.0929209629652745</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.8510370868360655</v>
+        <v>0.8392171272966756</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7325,22 +7325,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1402404667207233</v>
+        <v>0.1409684667207233</v>
       </c>
       <c r="C74">
-        <v>763.8596214471472</v>
+        <v>-201.9009967974926</v>
       </c>
       <c r="D74">
-        <v>43559.38987215231</v>
+        <v>43226.17828516747</v>
       </c>
       <c r="E74">
-        <v>35114.82712472577</v>
+        <v>35747.37615598556</v>
       </c>
       <c r="F74">
-        <v>45543.53025070517</v>
+        <v>46176.07928196496</v>
       </c>
       <c r="G74">
         <v>2748</v>
@@ -7361,37 +7361,37 @@
         <v>4533</v>
       </c>
       <c r="M74">
-        <v>5401.462687733633</v>
+        <v>5476.483002841044</v>
       </c>
       <c r="N74">
-        <v>-868.4626877336332</v>
+        <v>-943.4830028410443</v>
       </c>
       <c r="O74">
-        <v>-224.0633734352774</v>
+        <v>-243.4186147329894</v>
       </c>
       <c r="P74">
-        <v>-644.3993142983559</v>
+        <v>-700.0643881080548</v>
       </c>
       <c r="Q74">
-        <v>-473.3993142983559</v>
+        <v>-529.0643881080548</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2619191906633058</v>
+        <v>0.2699236051323171</v>
       </c>
       <c r="T74">
-        <v>4.991205327097132</v>
+        <v>5.176064783656285</v>
       </c>
       <c r="U74">
         <v>0.1186</v>
       </c>
       <c r="V74">
-        <v>0.2165180188425423</v>
+        <v>0.2135520185844253</v>
       </c>
       <c r="W74">
-        <v>0.0929209629652745</v>
+        <v>0.09327273059588717</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.8392171272966756</v>
+        <v>0.8277210022652144</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7407,22 +7407,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1409684667207233</v>
+        <v>0.1416964667207232</v>
       </c>
       <c r="C75">
-        <v>-201.9009967974926</v>
+        <v>-1162.602449806524</v>
       </c>
       <c r="D75">
-        <v>43226.17828516747</v>
+        <v>42898.02586341823</v>
       </c>
       <c r="E75">
-        <v>35747.37615598556</v>
+        <v>36379.92518724535</v>
       </c>
       <c r="F75">
-        <v>46176.07928196496</v>
+        <v>46808.62831322476</v>
       </c>
       <c r="G75">
         <v>2748</v>
@@ -7443,37 +7443,37 @@
         <v>4533</v>
       </c>
       <c r="M75">
-        <v>5476.483002841044</v>
+        <v>5551.503317948456</v>
       </c>
       <c r="N75">
-        <v>-943.4830028410443</v>
+        <v>-1018.503317948456</v>
       </c>
       <c r="O75">
-        <v>-243.4186147329894</v>
+        <v>-262.7738560307017</v>
       </c>
       <c r="P75">
-        <v>-700.0643881080548</v>
+        <v>-755.7294619177545</v>
       </c>
       <c r="Q75">
-        <v>-529.0643881080548</v>
+        <v>-584.7294619177545</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2699236051323171</v>
+        <v>0.2785437437912524</v>
       </c>
       <c r="T75">
-        <v>5.176064783656285</v>
+        <v>5.375144198412295</v>
       </c>
       <c r="U75">
         <v>0.1186</v>
       </c>
       <c r="V75">
-        <v>0.2135520185844253</v>
+        <v>0.2106661804954466</v>
       </c>
       <c r="W75">
-        <v>0.09327273059588717</v>
+        <v>0.09361499099324004</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.8277210022652144</v>
+        <v>0.8165355833156844</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7489,22 +7489,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1416964667207232</v>
+        <v>0.1424244667207233</v>
       </c>
       <c r="C76">
-        <v>-1162.602449806524</v>
+        <v>-2118.359089744081</v>
       </c>
       <c r="D76">
-        <v>42898.02586341823</v>
+        <v>42574.81825474046</v>
       </c>
       <c r="E76">
-        <v>36379.92518724535</v>
+        <v>37012.47421850514</v>
       </c>
       <c r="F76">
-        <v>46808.62831322476</v>
+        <v>47441.17734448455</v>
       </c>
       <c r="G76">
         <v>2748</v>
@@ -7525,37 +7525,37 @@
         <v>4533</v>
       </c>
       <c r="M76">
-        <v>5551.503317948456</v>
+        <v>5626.523633055867</v>
       </c>
       <c r="N76">
-        <v>-1018.503317948456</v>
+        <v>-1093.523633055867</v>
       </c>
       <c r="O76">
-        <v>-262.7738560307017</v>
+        <v>-282.1290973284138</v>
       </c>
       <c r="P76">
-        <v>-755.7294619177545</v>
+        <v>-811.3945357274536</v>
       </c>
       <c r="Q76">
-        <v>-584.7294619177545</v>
+        <v>-640.3945357274536</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2785437437912524</v>
+        <v>0.2878534935429025</v>
       </c>
       <c r="T76">
-        <v>5.375144198412295</v>
+        <v>5.590149966348788</v>
       </c>
       <c r="U76">
         <v>0.1186</v>
       </c>
       <c r="V76">
-        <v>0.2106661804954466</v>
+        <v>0.2078572980888407</v>
       </c>
       <c r="W76">
-        <v>0.09361499099324004</v>
+        <v>0.09394812444666351</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.8165355833156844</v>
+        <v>0.8056484422048087</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7571,22 +7571,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1424244667207233</v>
+        <v>0.2101994393330938</v>
       </c>
       <c r="C77">
-        <v>-2118.359089744081</v>
+        <v>-20302.71458030263</v>
       </c>
       <c r="D77">
-        <v>42574.81825474046</v>
+        <v>25023.01179544171</v>
       </c>
       <c r="E77">
-        <v>37012.47421850514</v>
+        <v>37645.02324976494</v>
       </c>
       <c r="F77">
-        <v>47441.17734448455</v>
+        <v>48073.72637574434</v>
       </c>
       <c r="G77">
         <v>2748</v>
@@ -7607,45 +7607,45 @@
         <v>4533</v>
       </c>
       <c r="M77">
-        <v>5626.523633055867</v>
+        <v>9653.204256249464</v>
       </c>
       <c r="N77">
-        <v>-1093.523633055867</v>
+        <v>-5120.204256249464</v>
       </c>
       <c r="O77">
-        <v>-282.1290973284138</v>
+        <v>-1321.012698112362</v>
       </c>
       <c r="P77">
-        <v>-811.3945357274536</v>
+        <v>-3799.191558137102</v>
       </c>
       <c r="Q77">
-        <v>-640.3945357274536</v>
+        <v>-3628.191558137102</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2878534935429025</v>
+        <v>0.3170014416587341</v>
       </c>
       <c r="T77">
-        <v>5.590149966348788</v>
+        <v>6.263312740386468</v>
       </c>
       <c r="U77">
-        <v>0.1186</v>
+        <v>0.2008</v>
       </c>
       <c r="V77">
-        <v>0.2078572980888407</v>
+        <v>0.121152932120219</v>
       </c>
       <c r="W77">
-        <v>0.09394812444666351</v>
+        <v>0.17647249123026</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y77">
-        <v>0.8056484422048087</v>
+        <v>0.4695850082179029</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7653,22 +7653,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2101994393330938</v>
+        <v>0.2117494393330938</v>
       </c>
       <c r="C78">
-        <v>-20302.71458030263</v>
+        <v>-21168.98340259519</v>
       </c>
       <c r="D78">
-        <v>25023.01179544171</v>
+        <v>24789.29200440895</v>
       </c>
       <c r="E78">
-        <v>37645.02324976494</v>
+        <v>38277.57228102474</v>
       </c>
       <c r="F78">
-        <v>48073.72637574434</v>
+        <v>48706.27540700414</v>
       </c>
       <c r="G78">
         <v>2748</v>
@@ -7689,37 +7689,37 @@
         <v>4533</v>
       </c>
       <c r="M78">
-        <v>9653.204256249464</v>
+        <v>9780.220101726432</v>
       </c>
       <c r="N78">
-        <v>-5120.204256249464</v>
+        <v>-5247.220101726432</v>
       </c>
       <c r="O78">
-        <v>-1321.012698112362</v>
+        <v>-1353.78278624542</v>
       </c>
       <c r="P78">
-        <v>-3799.191558137102</v>
+        <v>-3893.437315481013</v>
       </c>
       <c r="Q78">
-        <v>-3628.191558137102</v>
+        <v>-3722.437315481013</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.3170014416587341</v>
+        <v>0.3287928086873746</v>
       </c>
       <c r="T78">
-        <v>6.263312740386468</v>
+        <v>6.535630685620661</v>
       </c>
       <c r="U78">
         <v>0.2008</v>
       </c>
       <c r="V78">
-        <v>0.121152932120219</v>
+        <v>0.1195795174173589</v>
       </c>
       <c r="W78">
-        <v>0.17647249123026</v>
+        <v>0.1767884329025943</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7727,7 +7727,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.4695850082179029</v>
+        <v>0.4634865016176704</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7735,22 +7735,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2117494393330938</v>
+        <v>0.2132994393330938</v>
       </c>
       <c r="C79">
-        <v>-21168.98340259519</v>
+        <v>-22030.92665009724</v>
       </c>
       <c r="D79">
-        <v>24789.29200440895</v>
+        <v>24559.89778816669</v>
       </c>
       <c r="E79">
-        <v>38277.57228102474</v>
+        <v>38910.12131228453</v>
       </c>
       <c r="F79">
-        <v>48706.27540700414</v>
+        <v>49338.82443826393</v>
       </c>
       <c r="G79">
         <v>2748</v>
@@ -7771,37 +7771,37 @@
         <v>4533</v>
       </c>
       <c r="M79">
-        <v>9780.220101726432</v>
+        <v>9907.235947203399</v>
       </c>
       <c r="N79">
-        <v>-5247.220101726432</v>
+        <v>-5374.235947203399</v>
       </c>
       <c r="O79">
-        <v>-1353.78278624542</v>
+        <v>-1386.552874378477</v>
       </c>
       <c r="P79">
-        <v>-3893.437315481013</v>
+        <v>-3987.683072824922</v>
       </c>
       <c r="Q79">
-        <v>-3722.437315481013</v>
+        <v>-3816.683072824922</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.3287928086873746</v>
+        <v>0.3416561181731644</v>
       </c>
       <c r="T79">
-        <v>6.535630685620661</v>
+        <v>6.832704807694327</v>
       </c>
       <c r="U79">
         <v>0.2008</v>
       </c>
       <c r="V79">
-        <v>0.1195795174173589</v>
+        <v>0.118046446681239</v>
       </c>
       <c r="W79">
-        <v>0.1767884329025943</v>
+        <v>0.1770962735064072</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7809,7 +7809,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.4634865016176704</v>
+        <v>0.4575443669815463</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7817,22 +7817,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2132994393330938</v>
+        <v>0.2148494393330938</v>
       </c>
       <c r="C80">
-        <v>-22030.92665009724</v>
+        <v>-22888.66330529616</v>
       </c>
       <c r="D80">
-        <v>24559.89778816669</v>
+        <v>24334.71016422757</v>
       </c>
       <c r="E80">
-        <v>38910.12131228453</v>
+        <v>39542.67034354433</v>
       </c>
       <c r="F80">
-        <v>49338.82443826393</v>
+        <v>49971.37346952373</v>
       </c>
       <c r="G80">
         <v>2748</v>
@@ -7853,37 +7853,37 @@
         <v>4533</v>
       </c>
       <c r="M80">
-        <v>9907.235947203399</v>
+        <v>10034.25179268036</v>
       </c>
       <c r="N80">
-        <v>-5374.235947203399</v>
+        <v>-5501.251792680365</v>
       </c>
       <c r="O80">
-        <v>-1386.552874378477</v>
+        <v>-1419.322962511534</v>
       </c>
       <c r="P80">
-        <v>-3987.683072824922</v>
+        <v>-4081.928830168831</v>
       </c>
       <c r="Q80">
-        <v>-3816.683072824922</v>
+        <v>-3910.928830168831</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.3416561181731644</v>
+        <v>0.3557445047528389</v>
       </c>
       <c r="T80">
-        <v>6.832704807694327</v>
+        <v>7.158071703298821</v>
       </c>
       <c r="U80">
         <v>0.2008</v>
       </c>
       <c r="V80">
-        <v>0.118046446681239</v>
+        <v>0.1165521878624891</v>
       </c>
       <c r="W80">
-        <v>0.1770962735064072</v>
+        <v>0.1773963206772122</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7891,7 +7891,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.4575443669815463</v>
+        <v>0.4517526661336787</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7899,22 +7899,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2148494393330938</v>
+        <v>0.2163994393330938</v>
       </c>
       <c r="C81">
-        <v>-22888.66330529616</v>
+        <v>-23742.30802656526</v>
       </c>
       <c r="D81">
-        <v>24334.71016422757</v>
+        <v>24113.61447421826</v>
       </c>
       <c r="E81">
-        <v>39542.67034354433</v>
+        <v>40175.21937480412</v>
       </c>
       <c r="F81">
-        <v>49971.37346952373</v>
+        <v>50603.92250078352</v>
       </c>
       <c r="G81">
         <v>2748</v>
@@ -7935,37 +7935,37 @@
         <v>4533</v>
       </c>
       <c r="M81">
-        <v>10034.25179268036</v>
+        <v>10161.26763815733</v>
       </c>
       <c r="N81">
-        <v>-5501.251792680365</v>
+        <v>-5628.267638157331</v>
       </c>
       <c r="O81">
-        <v>-1419.322962511534</v>
+        <v>-1452.093050644591</v>
       </c>
       <c r="P81">
-        <v>-4081.928830168831</v>
+        <v>-4176.17458751274</v>
       </c>
       <c r="Q81">
-        <v>-3910.928830168831</v>
+        <v>-4005.17458751274</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.3557445047528389</v>
+        <v>0.3712417299904809</v>
       </c>
       <c r="T81">
-        <v>7.158071703298821</v>
+        <v>7.515975288463761</v>
       </c>
       <c r="U81">
         <v>0.2008</v>
       </c>
       <c r="V81">
-        <v>0.1165521878624891</v>
+        <v>0.115095285514208</v>
       </c>
       <c r="W81">
-        <v>0.1773963206772122</v>
+        <v>0.177688866668747</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7973,7 +7973,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.4517526661336787</v>
+        <v>0.4461057578070078</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7981,22 +7981,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2163994393330938</v>
+        <v>0.2179494393330938</v>
       </c>
       <c r="C82">
-        <v>-23742.30802656526</v>
+        <v>-24591.97134283135</v>
       </c>
       <c r="D82">
-        <v>24113.61447421826</v>
+        <v>23896.50018921197</v>
       </c>
       <c r="E82">
-        <v>40175.21937480412</v>
+        <v>40807.76840606391</v>
       </c>
       <c r="F82">
-        <v>50603.92250078352</v>
+        <v>51236.47153204332</v>
       </c>
       <c r="G82">
         <v>2748</v>
@@ -8017,37 +8017,37 @@
         <v>4533</v>
       </c>
       <c r="M82">
-        <v>10161.26763815733</v>
+        <v>10288.2834836343</v>
       </c>
       <c r="N82">
-        <v>-5628.267638157331</v>
+        <v>-5755.283483634299</v>
       </c>
       <c r="O82">
-        <v>-1452.093050644591</v>
+        <v>-1484.863138777649</v>
       </c>
       <c r="P82">
-        <v>-4176.17458751274</v>
+        <v>-4270.42034485665</v>
       </c>
       <c r="Q82">
-        <v>-4005.17458751274</v>
+        <v>-4099.42034485665</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3712417299904809</v>
+        <v>0.388370242095243</v>
       </c>
       <c r="T82">
-        <v>7.515975288463761</v>
+        <v>7.911552935225012</v>
       </c>
       <c r="U82">
         <v>0.2008</v>
       </c>
       <c r="V82">
-        <v>0.115095285514208</v>
+        <v>0.1136743560634153</v>
       </c>
       <c r="W82">
-        <v>0.177688866668747</v>
+        <v>0.1779741893024662</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.4461057578070078</v>
+        <v>0.4405982793155632</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8063,22 +8063,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2179494393330938</v>
+        <v>0.2194994393330938</v>
       </c>
       <c r="C83">
-        <v>-24591.97134283135</v>
+        <v>-25437.75983781935</v>
       </c>
       <c r="D83">
-        <v>23896.50018921197</v>
+        <v>23683.26072548377</v>
       </c>
       <c r="E83">
-        <v>40807.76840606391</v>
+        <v>41440.31743732371</v>
       </c>
       <c r="F83">
-        <v>51236.47153204332</v>
+        <v>51869.02056330311</v>
       </c>
       <c r="G83">
         <v>2748</v>
@@ -8099,37 +8099,37 @@
         <v>4533</v>
       </c>
       <c r="M83">
-        <v>10288.2834836343</v>
+        <v>10415.29932911127</v>
       </c>
       <c r="N83">
-        <v>-5755.283483634299</v>
+        <v>-5882.299329111265</v>
       </c>
       <c r="O83">
-        <v>-1484.863138777649</v>
+        <v>-1517.633226910707</v>
       </c>
       <c r="P83">
-        <v>-4270.42034485665</v>
+        <v>-4364.666102200559</v>
       </c>
       <c r="Q83">
-        <v>-4099.42034485665</v>
+        <v>-4193.666102200559</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.388370242095243</v>
+        <v>0.4074019222116454</v>
       </c>
       <c r="T83">
-        <v>7.911552935225012</v>
+        <v>8.351083653848624</v>
       </c>
       <c r="U83">
         <v>0.2008</v>
       </c>
       <c r="V83">
-        <v>0.1136743560634153</v>
+        <v>0.1122880834284956</v>
       </c>
       <c r="W83">
-        <v>0.1779741893024662</v>
+        <v>0.1782525528475581</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.4405982793155632</v>
+        <v>0.4352251295678125</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8145,22 +8145,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2194994393330938</v>
+        <v>0.2210494393330938</v>
       </c>
       <c r="C84">
-        <v>-25437.75983781935</v>
+        <v>-26279.77632451977</v>
       </c>
       <c r="D84">
-        <v>23683.26072548377</v>
+        <v>23473.79327004314</v>
       </c>
       <c r="E84">
-        <v>41440.31743732371</v>
+        <v>42072.8664685835</v>
       </c>
       <c r="F84">
-        <v>51869.02056330311</v>
+        <v>52501.5695945629</v>
       </c>
       <c r="G84">
         <v>2748</v>
@@ -8181,37 +8181,37 @@
         <v>4533</v>
       </c>
       <c r="M84">
-        <v>10415.29932911127</v>
+        <v>10542.31517458823</v>
       </c>
       <c r="N84">
-        <v>-5882.299329111265</v>
+        <v>-6009.315174588231</v>
       </c>
       <c r="O84">
-        <v>-1517.633226910707</v>
+        <v>-1550.403315043764</v>
       </c>
       <c r="P84">
-        <v>-4364.666102200559</v>
+        <v>-4458.911859544468</v>
       </c>
       <c r="Q84">
-        <v>-4193.666102200559</v>
+        <v>-4287.911859544468</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.4074019222116454</v>
+        <v>0.4286726235182129</v>
       </c>
       <c r="T84">
-        <v>8.351083653848624</v>
+        <v>8.842323868780898</v>
       </c>
       <c r="U84">
         <v>0.2008</v>
       </c>
       <c r="V84">
-        <v>0.1122880834284956</v>
+        <v>0.1109352149534535</v>
       </c>
       <c r="W84">
-        <v>0.1782525528475581</v>
+        <v>0.1785242088373465</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.4352251295678125</v>
+        <v>0.4299814533079592</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8227,22 +8227,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2210494393330938</v>
+        <v>0.2225994393330938</v>
       </c>
       <c r="C85">
-        <v>-26279.77632451977</v>
+        <v>-27118.12001047877</v>
       </c>
       <c r="D85">
-        <v>23473.79327004314</v>
+        <v>23267.99861534393</v>
       </c>
       <c r="E85">
-        <v>42072.8664685835</v>
+        <v>42705.4154998433</v>
       </c>
       <c r="F85">
-        <v>52501.5695945629</v>
+        <v>53134.1186258227</v>
       </c>
       <c r="G85">
         <v>2748</v>
@@ -8263,37 +8263,37 @@
         <v>4533</v>
       </c>
       <c r="M85">
-        <v>10542.31517458823</v>
+        <v>10669.3310200652</v>
       </c>
       <c r="N85">
-        <v>-6009.315174588231</v>
+        <v>-6136.331020065199</v>
       </c>
       <c r="O85">
-        <v>-1550.403315043764</v>
+        <v>-1583.173403176821</v>
       </c>
       <c r="P85">
-        <v>-4458.911859544468</v>
+        <v>-4553.157616888378</v>
       </c>
       <c r="Q85">
-        <v>-4287.911859544468</v>
+        <v>-4382.157616888378</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.4286726235182129</v>
+        <v>0.4526021624881013</v>
       </c>
       <c r="T85">
-        <v>8.842323868780898</v>
+        <v>9.394969110579707</v>
       </c>
       <c r="U85">
         <v>0.2008</v>
       </c>
       <c r="V85">
-        <v>0.1109352149534535</v>
+        <v>0.109614557632579</v>
       </c>
       <c r="W85">
-        <v>0.1785242088373465</v>
+        <v>0.1787893968273782</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8301,7 +8301,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.4299814533079592</v>
+        <v>0.4248626264828644</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8309,22 +8309,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2225994393330938</v>
+        <v>0.2241494393330938</v>
       </c>
       <c r="C86">
-        <v>-27118.12001047876</v>
+        <v>-27952.88665446917</v>
       </c>
       <c r="D86">
-        <v>23267.99861534394</v>
+        <v>23065.78100261331</v>
       </c>
       <c r="E86">
-        <v>42705.41549984329</v>
+        <v>43337.96453110308</v>
       </c>
       <c r="F86">
-        <v>53134.1186258227</v>
+        <v>53766.66765708249</v>
       </c>
       <c r="G86">
         <v>2748</v>
@@ -8345,37 +8345,37 @@
         <v>4533</v>
       </c>
       <c r="M86">
-        <v>10669.3310200652</v>
+        <v>10796.34686554216</v>
       </c>
       <c r="N86">
-        <v>-6136.331020065198</v>
+        <v>-6263.346865542164</v>
       </c>
       <c r="O86">
-        <v>-1583.173403176821</v>
+        <v>-1615.943491309878</v>
       </c>
       <c r="P86">
-        <v>-4553.157616888377</v>
+        <v>-4647.403374232285</v>
       </c>
       <c r="Q86">
-        <v>-4382.157616888377</v>
+        <v>-4476.403374232285</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.4526021624881009</v>
+        <v>0.4797223066539744</v>
       </c>
       <c r="T86">
-        <v>9.394969110579698</v>
+        <v>10.02130038461835</v>
       </c>
       <c r="U86">
         <v>0.2008</v>
       </c>
       <c r="V86">
-        <v>0.1096145576325791</v>
+        <v>0.1083249746016075</v>
       </c>
       <c r="W86">
-        <v>0.1787893968273781</v>
+        <v>0.1790483450999972</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.4248626264828645</v>
+        <v>0.4198642426418897</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8391,22 +8391,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2241494393330938</v>
+        <v>0.2256994393330938</v>
       </c>
       <c r="C87">
-        <v>-27952.88665446917</v>
+        <v>-28784.16871506239</v>
       </c>
       <c r="D87">
-        <v>23065.78100261331</v>
+        <v>22867.04797327989</v>
       </c>
       <c r="E87">
-        <v>43337.96453110308</v>
+        <v>43970.51356236288</v>
       </c>
       <c r="F87">
-        <v>53766.66765708249</v>
+        <v>54399.21668834228</v>
       </c>
       <c r="G87">
         <v>2748</v>
@@ -8427,37 +8427,37 @@
         <v>4533</v>
       </c>
       <c r="M87">
-        <v>10796.34686554216</v>
+        <v>10923.36271101913</v>
       </c>
       <c r="N87">
-        <v>-6263.346865542164</v>
+        <v>-6390.36271101913</v>
       </c>
       <c r="O87">
-        <v>-1615.943491309878</v>
+        <v>-1648.713579442935</v>
       </c>
       <c r="P87">
-        <v>-4647.403374232285</v>
+        <v>-4741.649131576194</v>
       </c>
       <c r="Q87">
-        <v>-4476.403374232285</v>
+        <v>-4570.649131576194</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.4797223066539744</v>
+        <v>0.5107167571292582</v>
       </c>
       <c r="T87">
-        <v>10.02130038461835</v>
+        <v>10.73710755494823</v>
       </c>
       <c r="U87">
         <v>0.2008</v>
       </c>
       <c r="V87">
-        <v>0.1083249746016075</v>
+        <v>0.1070653818736819</v>
       </c>
       <c r="W87">
-        <v>0.1790483450999972</v>
+        <v>0.1793012713197647</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8465,7 +8465,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.4198642426418897</v>
+        <v>0.4149821002855887</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8473,22 +8473,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2256994393330938</v>
+        <v>0.2272494393330938</v>
       </c>
       <c r="C88">
-        <v>-28784.16871506239</v>
+        <v>-29612.0554915853</v>
       </c>
       <c r="D88">
-        <v>22867.04797327989</v>
+        <v>22671.71022801677</v>
       </c>
       <c r="E88">
-        <v>43970.51356236288</v>
+        <v>44603.06259362267</v>
       </c>
       <c r="F88">
-        <v>54399.21668834228</v>
+        <v>55031.76571960207</v>
       </c>
       <c r="G88">
         <v>2748</v>
@@ -8509,37 +8509,37 @@
         <v>4533</v>
       </c>
       <c r="M88">
-        <v>10923.36271101913</v>
+        <v>11050.3785564961</v>
       </c>
       <c r="N88">
-        <v>-6390.36271101913</v>
+        <v>-6517.378556496096</v>
       </c>
       <c r="O88">
-        <v>-1648.713579442935</v>
+        <v>-1681.483667575993</v>
       </c>
       <c r="P88">
-        <v>-4741.649131576194</v>
+        <v>-4835.894888920104</v>
       </c>
       <c r="Q88">
-        <v>-4570.649131576194</v>
+        <v>-4664.894888920104</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.5107167571292582</v>
+        <v>0.5464795846007396</v>
       </c>
       <c r="T88">
-        <v>10.73710755494823</v>
+        <v>11.56303890532886</v>
       </c>
       <c r="U88">
         <v>0.2008</v>
       </c>
       <c r="V88">
-        <v>0.1070653818736819</v>
+        <v>0.1058347453004212</v>
       </c>
       <c r="W88">
-        <v>0.1793012713197647</v>
+        <v>0.1795483831436754</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.4149821002855887</v>
+        <v>0.4102121910869038</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8555,22 +8555,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2272494393330938</v>
+        <v>0.2287994393330938</v>
       </c>
       <c r="C89">
-        <v>-29612.0554915853</v>
+        <v>-30436.63325791387</v>
       </c>
       <c r="D89">
-        <v>22671.71022801677</v>
+        <v>22479.68149294801</v>
       </c>
       <c r="E89">
-        <v>44603.06259362267</v>
+        <v>45235.61162488247</v>
       </c>
       <c r="F89">
-        <v>55031.76571960207</v>
+        <v>55664.31475086187</v>
       </c>
       <c r="G89">
         <v>2748</v>
@@ -8591,37 +8591,37 @@
         <v>4533</v>
       </c>
       <c r="M89">
-        <v>11050.3785564961</v>
+        <v>11177.39440197306</v>
       </c>
       <c r="N89">
-        <v>-6517.378556496096</v>
+        <v>-6644.394401973064</v>
       </c>
       <c r="O89">
-        <v>-1681.483667575993</v>
+        <v>-1714.253755709051</v>
       </c>
       <c r="P89">
-        <v>-4835.894888920104</v>
+        <v>-4930.140646264013</v>
       </c>
       <c r="Q89">
-        <v>-4664.894888920104</v>
+        <v>-4759.140646264013</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.5464795846007396</v>
+        <v>0.588202883317468</v>
       </c>
       <c r="T89">
-        <v>11.56303890532886</v>
+        <v>12.52662548077293</v>
       </c>
       <c r="U89">
         <v>0.2008</v>
       </c>
       <c r="V89">
-        <v>0.1058347453004212</v>
+        <v>0.1046320777401891</v>
       </c>
       <c r="W89">
-        <v>0.1795483831436754</v>
+        <v>0.17978987878977</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8629,7 +8629,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.4102121910869038</v>
+        <v>0.4055506889154615</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8637,22 +8637,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2287994393330938</v>
+        <v>0.2303494393330938</v>
       </c>
       <c r="C90">
-        <v>-30436.63325791387</v>
+        <v>-31257.98538952435</v>
       </c>
       <c r="D90">
-        <v>22479.68149294801</v>
+        <v>22290.87839259732</v>
       </c>
       <c r="E90">
-        <v>45235.61162488247</v>
+        <v>45868.16065614227</v>
       </c>
       <c r="F90">
-        <v>55664.31475086187</v>
+        <v>56296.86378212167</v>
       </c>
       <c r="G90">
         <v>2748</v>
@@ -8673,37 +8673,37 @@
         <v>4533</v>
       </c>
       <c r="M90">
-        <v>11177.39440197306</v>
+        <v>11304.41024745003</v>
       </c>
       <c r="N90">
-        <v>-6644.394401973064</v>
+        <v>-6771.410247450032</v>
       </c>
       <c r="O90">
-        <v>-1714.253755709051</v>
+        <v>-1747.023843842108</v>
       </c>
       <c r="P90">
-        <v>-4930.140646264013</v>
+        <v>-5024.386403607924</v>
       </c>
       <c r="Q90">
-        <v>-4759.140646264013</v>
+        <v>-4853.386403607924</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.588202883317468</v>
+        <v>0.6375122363463287</v>
       </c>
       <c r="T90">
-        <v>12.52662548077293</v>
+        <v>13.66540961538865</v>
       </c>
       <c r="U90">
         <v>0.2008</v>
       </c>
       <c r="V90">
-        <v>0.1046320777401891</v>
+        <v>0.1034564364172656</v>
       </c>
       <c r="W90">
-        <v>0.17978987878977</v>
+        <v>0.1800259475674131</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.4055506889154615</v>
+        <v>0.4009939396018046</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8719,22 +8719,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2303494393330938</v>
+        <v>0.2318994393330938</v>
       </c>
       <c r="C91">
-        <v>-31257.98538952435</v>
+        <v>-32076.19248419552</v>
       </c>
       <c r="D91">
-        <v>22290.87839259732</v>
+        <v>22105.22032918594</v>
       </c>
       <c r="E91">
-        <v>45868.16065614227</v>
+        <v>46500.70968740206</v>
       </c>
       <c r="F91">
-        <v>56296.86378212167</v>
+        <v>56929.41281338146</v>
       </c>
       <c r="G91">
         <v>2748</v>
@@ -8755,37 +8755,37 @@
         <v>4533</v>
       </c>
       <c r="M91">
-        <v>11304.41024745003</v>
+        <v>11431.426092927</v>
       </c>
       <c r="N91">
-        <v>-6771.410247450032</v>
+        <v>-6898.426092926997</v>
       </c>
       <c r="O91">
-        <v>-1747.023843842108</v>
+        <v>-1779.793931975165</v>
       </c>
       <c r="P91">
-        <v>-5024.386403607924</v>
+        <v>-5118.632160951832</v>
       </c>
       <c r="Q91">
-        <v>-4853.386403607924</v>
+        <v>-4947.632160951832</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.6375122363463287</v>
+        <v>0.6966834599809617</v>
       </c>
       <c r="T91">
-        <v>13.66540961538865</v>
+        <v>15.03195057692752</v>
       </c>
       <c r="U91">
         <v>0.2008</v>
       </c>
       <c r="V91">
-        <v>0.1034564364172656</v>
+        <v>0.1023069204570738</v>
       </c>
       <c r="W91">
-        <v>0.1800259475674131</v>
+        <v>0.1802567703722196</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.4009939396018046</v>
+        <v>0.3965384513840069</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8801,22 +8801,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2318994393330938</v>
+        <v>0.2334494393330938</v>
       </c>
       <c r="C92">
-        <v>-32076.19248419552</v>
+        <v>-32891.33247672868</v>
       </c>
       <c r="D92">
-        <v>22105.22032918594</v>
+        <v>21922.62936791258</v>
       </c>
       <c r="E92">
-        <v>46500.70968740206</v>
+        <v>47133.25871866185</v>
       </c>
       <c r="F92">
-        <v>56929.41281338146</v>
+        <v>57561.96184464126</v>
       </c>
       <c r="G92">
         <v>2748</v>
@@ -8837,37 +8837,37 @@
         <v>4533</v>
       </c>
       <c r="M92">
-        <v>11431.426092927</v>
+        <v>11558.44193840396</v>
       </c>
       <c r="N92">
-        <v>-6898.426092926997</v>
+        <v>-7025.441938403965</v>
       </c>
       <c r="O92">
-        <v>-1779.793931975165</v>
+        <v>-1812.564020108223</v>
       </c>
       <c r="P92">
-        <v>-5118.632160951832</v>
+        <v>-5212.877918295742</v>
       </c>
       <c r="Q92">
-        <v>-4947.632160951832</v>
+        <v>-5041.877918295742</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.6966834599809617</v>
+        <v>0.7690038444232907</v>
       </c>
       <c r="T92">
-        <v>15.03195057692752</v>
+        <v>16.70216730769725</v>
       </c>
       <c r="U92">
         <v>0.2008</v>
       </c>
       <c r="V92">
-        <v>0.1023069204570738</v>
+        <v>0.1011826685839191</v>
       </c>
       <c r="W92">
-        <v>0.1802567703722196</v>
+        <v>0.180482520148349</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3965384513840069</v>
+        <v>0.3921808859841827</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8883,22 +8883,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2334494393330938</v>
+        <v>0.2349994393330938</v>
       </c>
       <c r="C93">
-        <v>-32891.33247672868</v>
+        <v>-33703.48074802872</v>
       </c>
       <c r="D93">
-        <v>21922.62936791258</v>
+        <v>21743.03012787233</v>
       </c>
       <c r="E93">
-        <v>47133.25871866185</v>
+        <v>47765.80774992165</v>
       </c>
       <c r="F93">
-        <v>57561.96184464126</v>
+        <v>58194.51087590105</v>
       </c>
       <c r="G93">
         <v>2748</v>
@@ -8919,37 +8919,37 @@
         <v>4533</v>
       </c>
       <c r="M93">
-        <v>11558.44193840396</v>
+        <v>11685.45778388093</v>
       </c>
       <c r="N93">
-        <v>-7025.441938403965</v>
+        <v>-7152.457783880931</v>
       </c>
       <c r="O93">
-        <v>-1812.564020108223</v>
+        <v>-1845.33410824128</v>
       </c>
       <c r="P93">
-        <v>-5212.877918295742</v>
+        <v>-5307.12367563965</v>
       </c>
       <c r="Q93">
-        <v>-5041.877918295742</v>
+        <v>-5136.12367563965</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.7690038444232907</v>
+        <v>0.8594043249762026</v>
       </c>
       <c r="T93">
-        <v>16.70216730769725</v>
+        <v>18.78993822115941</v>
       </c>
       <c r="U93">
         <v>0.2008</v>
       </c>
       <c r="V93">
-        <v>0.1011826685839191</v>
+        <v>0.1000828569688765</v>
       </c>
       <c r="W93">
-        <v>0.180482520148349</v>
+        <v>0.1807033623206496</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8957,7 +8957,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3921808859841827</v>
+        <v>0.3879180502669632</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8965,22 +8965,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2349994393330938</v>
+        <v>0.2365494393330938</v>
       </c>
       <c r="C94">
-        <v>-33703.48074802872</v>
+        <v>-34512.71022886694</v>
       </c>
       <c r="D94">
-        <v>21743.03012787233</v>
+        <v>21566.3496782939</v>
       </c>
       <c r="E94">
-        <v>47765.80774992165</v>
+        <v>48398.35678118144</v>
       </c>
       <c r="F94">
-        <v>58194.51087590105</v>
+        <v>58827.05990716084</v>
       </c>
       <c r="G94">
         <v>2748</v>
@@ -9001,37 +9001,37 @@
         <v>4533</v>
       </c>
       <c r="M94">
-        <v>11685.45778388093</v>
+        <v>11812.4736293579</v>
       </c>
       <c r="N94">
-        <v>-7152.457783880931</v>
+        <v>-7279.473629357897</v>
       </c>
       <c r="O94">
-        <v>-1845.33410824128</v>
+        <v>-1878.104196374338</v>
       </c>
       <c r="P94">
-        <v>-5307.12367563965</v>
+        <v>-5401.36943298356</v>
       </c>
       <c r="Q94">
-        <v>-5136.12367563965</v>
+        <v>-5230.36943298356</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.8594043249762026</v>
+        <v>0.9756335142585171</v>
       </c>
       <c r="T94">
-        <v>18.78993822115941</v>
+        <v>21.47421510989647</v>
       </c>
       <c r="U94">
         <v>0.2008</v>
       </c>
       <c r="V94">
-        <v>0.1000828569688765</v>
+        <v>0.09900669721652301</v>
       </c>
       <c r="W94">
-        <v>0.1807033623206496</v>
+        <v>0.1809194551989222</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3879180502669632</v>
+        <v>0.3837468884361357</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9047,22 +9047,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2365494393330938</v>
+        <v>0.2380994393330938</v>
       </c>
       <c r="C95">
-        <v>-34512.71022886694</v>
+        <v>-35319.09149862564</v>
       </c>
       <c r="D95">
-        <v>21566.3496782939</v>
+        <v>21392.517439795</v>
       </c>
       <c r="E95">
-        <v>48398.35678118144</v>
+        <v>49030.90581244124</v>
       </c>
       <c r="F95">
-        <v>58827.05990716084</v>
+        <v>59459.60893842064</v>
       </c>
       <c r="G95">
         <v>2748</v>
@@ -9083,37 +9083,37 @@
         <v>4533</v>
       </c>
       <c r="M95">
-        <v>11812.4736293579</v>
+        <v>11939.48947483487</v>
       </c>
       <c r="N95">
-        <v>-7279.473629357897</v>
+        <v>-7406.489474834865</v>
       </c>
       <c r="O95">
-        <v>-1878.104196374338</v>
+        <v>-1910.874284507395</v>
       </c>
       <c r="P95">
-        <v>-5401.36943298356</v>
+        <v>-5495.615190327469</v>
       </c>
       <c r="Q95">
-        <v>-5230.36943298356</v>
+        <v>-5324.615190327469</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.9756335142585171</v>
+        <v>1.130605766634937</v>
       </c>
       <c r="T95">
-        <v>21.47421510989647</v>
+        <v>25.05325096154589</v>
       </c>
       <c r="U95">
         <v>0.2008</v>
       </c>
       <c r="V95">
-        <v>0.09900669721652301</v>
+        <v>0.09795343448017702</v>
       </c>
       <c r="W95">
-        <v>0.1809194551989222</v>
+        <v>0.1811309503563805</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9121,7 +9121,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3837468884361357</v>
+        <v>0.3796644747293683</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9129,22 +9129,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2380994393330938</v>
+        <v>0.2396494393330938</v>
       </c>
       <c r="C96">
-        <v>-35319.09149862564</v>
+        <v>-36122.69287930547</v>
       </c>
       <c r="D96">
-        <v>21392.517439795</v>
+        <v>21221.46509037496</v>
       </c>
       <c r="E96">
-        <v>49030.90581244124</v>
+        <v>49663.45484370103</v>
       </c>
       <c r="F96">
-        <v>59459.60893842064</v>
+        <v>60092.15796968043</v>
       </c>
       <c r="G96">
         <v>2748</v>
@@ -9165,37 +9165,37 @@
         <v>4533</v>
       </c>
       <c r="M96">
-        <v>11939.48947483487</v>
+        <v>12066.50532031183</v>
       </c>
       <c r="N96">
-        <v>-7406.489474834865</v>
+        <v>-7533.505320311831</v>
       </c>
       <c r="O96">
-        <v>-1910.874284507395</v>
+        <v>-1943.644372640453</v>
       </c>
       <c r="P96">
-        <v>-5495.615190327469</v>
+        <v>-5589.860947671379</v>
       </c>
       <c r="Q96">
-        <v>-5324.615190327469</v>
+        <v>-5418.860947671379</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.130605766634937</v>
+        <v>1.347566919961925</v>
       </c>
       <c r="T96">
-        <v>25.05325096154589</v>
+        <v>30.06390115385508</v>
       </c>
       <c r="U96">
         <v>0.2008</v>
       </c>
       <c r="V96">
-        <v>0.09795343448017702</v>
+        <v>0.09692234569617515</v>
       </c>
       <c r="W96">
-        <v>0.1811309503563805</v>
+        <v>0.181337992984208</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3796644747293683</v>
+        <v>0.3756680065743223</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9211,22 +9211,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2396494393330938</v>
+        <v>0.2411994393330938</v>
       </c>
       <c r="C97">
-        <v>-36122.69287930547</v>
+        <v>-36923.58052505847</v>
       </c>
       <c r="D97">
-        <v>21221.46509037496</v>
+        <v>21053.12647588176</v>
       </c>
       <c r="E97">
-        <v>49663.45484370103</v>
+        <v>50296.00387496083</v>
       </c>
       <c r="F97">
-        <v>60092.15796968043</v>
+        <v>60724.70700094023</v>
       </c>
       <c r="G97">
         <v>2748</v>
@@ -9247,37 +9247,37 @@
         <v>4533</v>
       </c>
       <c r="M97">
-        <v>12066.50532031183</v>
+        <v>12193.5211657888</v>
       </c>
       <c r="N97">
-        <v>-7533.505320311831</v>
+        <v>-7660.521165788799</v>
       </c>
       <c r="O97">
-        <v>-1943.644372640453</v>
+        <v>-1976.41446077351</v>
       </c>
       <c r="P97">
-        <v>-5589.860947671379</v>
+        <v>-5684.106705015289</v>
       </c>
       <c r="Q97">
-        <v>-5418.860947671379</v>
+        <v>-5513.106705015289</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.347566919961925</v>
+        <v>1.673008649952407</v>
       </c>
       <c r="T97">
-        <v>30.06390115385508</v>
+        <v>37.57987644231887</v>
       </c>
       <c r="U97">
         <v>0.2008</v>
       </c>
       <c r="V97">
-        <v>0.09692234569617515</v>
+        <v>0.09591273792850666</v>
       </c>
       <c r="W97">
-        <v>0.181337992984208</v>
+        <v>0.1815407222239559</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3756680065743223</v>
+        <v>0.3717547981725063</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9293,22 +9293,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2411994393330938</v>
+        <v>0.2427494393330938</v>
       </c>
       <c r="C98">
-        <v>-36923.58052505846</v>
+        <v>-37721.81850749331</v>
       </c>
       <c r="D98">
-        <v>21053.12647588176</v>
+        <v>20887.43752470671</v>
       </c>
       <c r="E98">
-        <v>50296.00387496082</v>
+        <v>50928.55290622061</v>
       </c>
       <c r="F98">
-        <v>60724.70700094022</v>
+        <v>61357.25603220001</v>
       </c>
       <c r="G98">
         <v>2748</v>
@@ -9329,37 +9329,37 @@
         <v>4533</v>
       </c>
       <c r="M98">
-        <v>12193.5211657888</v>
+        <v>12320.53701126576</v>
       </c>
       <c r="N98">
-        <v>-7660.521165788798</v>
+        <v>-7787.537011265764</v>
       </c>
       <c r="O98">
-        <v>-1976.41446077351</v>
+        <v>-2009.184548906567</v>
       </c>
       <c r="P98">
-        <v>-5684.106705015288</v>
+        <v>-5778.352462359197</v>
       </c>
       <c r="Q98">
-        <v>-5513.106705015288</v>
+        <v>-5607.352462359197</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.673008649952403</v>
+        <v>2.215411533269871</v>
       </c>
       <c r="T98">
-        <v>37.57987644231877</v>
+        <v>50.1065019230917</v>
       </c>
       <c r="U98">
         <v>0.2008</v>
       </c>
       <c r="V98">
-        <v>0.09591273792850667</v>
+        <v>0.09492394681584165</v>
       </c>
       <c r="W98">
-        <v>0.1815407222239559</v>
+        <v>0.181739271479379</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.3717547981725065</v>
+        <v>0.3679222744800064</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9375,22 +9375,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2427494393330938</v>
+        <v>0.2442994393330938</v>
       </c>
       <c r="C99">
-        <v>-37721.81850749331</v>
+        <v>-38517.46889698398</v>
       </c>
       <c r="D99">
-        <v>20887.43752470671</v>
+        <v>20724.33616647583</v>
       </c>
       <c r="E99">
-        <v>50928.55290622061</v>
+        <v>51561.10193748041</v>
       </c>
       <c r="F99">
-        <v>61357.25603220001</v>
+        <v>61989.80506345981</v>
       </c>
       <c r="G99">
         <v>2748</v>
@@ -9411,37 +9411,37 @@
         <v>4533</v>
       </c>
       <c r="M99">
-        <v>12320.53701126576</v>
+        <v>12447.55285674273</v>
       </c>
       <c r="N99">
-        <v>-7787.537011265764</v>
+        <v>-7914.55285674273</v>
       </c>
       <c r="O99">
-        <v>-2009.184548906567</v>
+        <v>-2041.954637039624</v>
       </c>
       <c r="P99">
-        <v>-5778.352462359197</v>
+        <v>-5872.598219703105</v>
       </c>
       <c r="Q99">
-        <v>-5607.352462359197</v>
+        <v>-5701.598219703105</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>2.215411533269871</v>
+        <v>3.300217299904805</v>
       </c>
       <c r="T99">
-        <v>50.1065019230917</v>
+        <v>75.15975288463754</v>
       </c>
       <c r="U99">
         <v>0.2008</v>
       </c>
       <c r="V99">
-        <v>0.09492394681584165</v>
+        <v>0.09395533511363918</v>
       </c>
       <c r="W99">
-        <v>0.181739271479379</v>
+        <v>0.1819337687091813</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.3679222744800064</v>
+        <v>0.364167965556741</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9457,22 +9457,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2442994393330938</v>
+        <v>0.2458494393330938</v>
       </c>
       <c r="C100">
-        <v>-38517.46889698398</v>
+        <v>-39310.59184019837</v>
       </c>
       <c r="D100">
-        <v>20724.33616647583</v>
+        <v>20563.76225452123</v>
       </c>
       <c r="E100">
-        <v>51561.10193748041</v>
+        <v>52193.6509687402</v>
       </c>
       <c r="F100">
-        <v>61989.80506345981</v>
+        <v>62622.3540947196</v>
       </c>
       <c r="G100">
         <v>2748</v>
@@ -9493,37 +9493,37 @@
         <v>4533</v>
       </c>
       <c r="M100">
-        <v>12447.55285674273</v>
+        <v>12574.5687022197</v>
       </c>
       <c r="N100">
-        <v>-7914.55285674273</v>
+        <v>-8041.568702219696</v>
       </c>
       <c r="O100">
-        <v>-2041.954637039624</v>
+        <v>-2074.724725172682</v>
       </c>
       <c r="P100">
-        <v>-5872.598219703105</v>
+        <v>-5966.843977047014</v>
       </c>
       <c r="Q100">
-        <v>-5701.598219703105</v>
+        <v>-5795.843977047014</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>3.300217299904805</v>
+        <v>6.554634599809609</v>
       </c>
       <c r="T100">
-        <v>75.15975288463754</v>
+        <v>150.3195057692751</v>
       </c>
       <c r="U100">
         <v>0.2008</v>
       </c>
       <c r="V100">
-        <v>0.09395533511363918</v>
+        <v>0.09300629132461254</v>
       </c>
       <c r="W100">
-        <v>0.1819337687091813</v>
+        <v>0.1821243367020178</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9531,91 +9531,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.364167965556741</v>
+        <v>0.3604895012581881</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2458494393330938</v>
-      </c>
-      <c r="C101">
-        <v>-39310.59184019837</v>
-      </c>
-      <c r="D101">
-        <v>20563.76225452123</v>
-      </c>
-      <c r="E101">
-        <v>52193.6509687402</v>
-      </c>
-      <c r="F101">
-        <v>62622.3540947196</v>
-      </c>
-      <c r="G101">
-        <v>2748</v>
-      </c>
-      <c r="H101">
-        <v>52826.2</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>4704</v>
-      </c>
-      <c r="K101">
-        <v>171</v>
-      </c>
-      <c r="L101">
-        <v>4533</v>
-      </c>
-      <c r="M101">
-        <v>12574.5687022197</v>
-      </c>
-      <c r="N101">
-        <v>-8041.568702219696</v>
-      </c>
-      <c r="O101">
-        <v>-2074.724725172682</v>
-      </c>
-      <c r="P101">
-        <v>-5966.843977047014</v>
-      </c>
-      <c r="Q101">
-        <v>-5795.843977047014</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>6.554634599809609</v>
-      </c>
-      <c r="T101">
-        <v>150.3195057692751</v>
-      </c>
-      <c r="U101">
-        <v>0.2008</v>
-      </c>
-      <c r="V101">
-        <v>0.09300629132461254</v>
-      </c>
-      <c r="W101">
-        <v>0.1821243367020178</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>C2/C</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.3604895012581881</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
